--- a/cert_tracker/Contractor Certifications Tracker Demo.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C816EC4-BD14-4B6D-BB32-43A3AF89DC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC5C4BC-EE37-4703-847D-98BD12245E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -824,23 +824,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -858,28 +858,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -940,7 +919,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="6">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -1259,7 +1238,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="15"/>
@@ -1388,7 +1367,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B1" s="15"/>
@@ -1398,42 +1377,42 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="15"/>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="15"/>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>61</v>
       </c>
       <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="18">
         <f>COUNTA(Contractors!A2:A50)</f>
         <v>12</v>
       </c>
       <c r="B4" s="15"/>
-      <c r="C4" s="16">
+      <c r="C4" s="18">
         <f>COUNTA(Workers!A2:A200)</f>
         <v>33</v>
       </c>
       <c r="D4" s="15"/>
-      <c r="E4" s="16">
+      <c r="E4" s="18">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
         <v>27</v>
       </c>
       <c r="F4" s="15"/>
-      <c r="G4" s="16" t="str">
+      <c r="G4" s="18" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/24/2026</v>
+        <v>04/27/2026</v>
       </c>
       <c r="H4" s="15"/>
     </row>
@@ -1448,7 +1427,7 @@
       <c r="H5" s="15"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="19" t="s">
         <v>62</v>
       </c>
       <c r="B7" s="15"/>
@@ -2099,26 +2078,26 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="G4:H5"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
       <formula>0.7</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4130,6 +4109,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4142,7 +4122,7 @@
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="14" t="s">
         <v>205</v>
       </c>
       <c r="D1" s="15"/>
@@ -4157,7 +4137,7 @@
       <c r="M1" s="15"/>
       <c r="N1" s="15"/>
       <c r="O1" s="15"/>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="14" t="s">
         <v>83</v>
       </c>
       <c r="Q1" s="15"/>
@@ -4275,7 +4255,7 @@
         <v>Concrete &amp; Masonry</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -4343,7 +4323,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4409,7 +4389,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4469,7 +4449,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4509,7 +4489,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4579,7 +4559,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -4643,7 +4623,7 @@
         <v>45455</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4683,7 +4663,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -4739,7 +4719,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -4791,7 +4771,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4833,7 +4813,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -4895,7 +4875,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4953,7 +4933,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -5001,7 +4981,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -5057,7 +5037,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5091,7 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5311,7 +5291,7 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -5369,7 +5349,7 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -5419,7 +5399,7 @@
       </c>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -5483,7 +5463,7 @@
         <v>43172</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -5543,7 +5523,7 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -5595,7 +5575,7 @@
         <v>43152</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -5637,7 +5617,7 @@
       </c>
       <c r="Z27" s="9"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -5693,7 +5673,7 @@
         <v>44639</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -5757,7 +5737,7 @@
       </c>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -5821,7 +5801,7 @@
         <v>44660</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -5877,7 +5857,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -5933,7 +5913,7 @@
         <v>43239</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -5973,7 +5953,7 @@
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -6007,7 +5987,7 @@
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -6051,7 +6031,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -6077,7 +6057,7 @@
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -6103,7 +6083,7 @@
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -6129,7 +6109,7 @@
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -6155,7 +6135,7 @@
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -6181,7 +6161,7 @@
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -6207,7 +6187,7 @@
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -6233,7 +6213,7 @@
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -6259,7 +6239,7 @@
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -6285,7 +6265,7 @@
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -6311,7 +6291,7 @@
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -6337,7 +6317,7 @@
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -6363,7 +6343,7 @@
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -6389,7 +6369,7 @@
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -6415,7 +6395,7 @@
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -6441,7 +6421,7 @@
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
     </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -6467,7 +6447,7 @@
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
     </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -6493,7 +6473,7 @@
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -6519,7 +6499,7 @@
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
     </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -6545,7 +6525,7 @@
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -6571,7 +6551,7 @@
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -6597,7 +6577,7 @@
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -6623,7 +6603,7 @@
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -6649,7 +6629,7 @@
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -6675,7 +6655,7 @@
       <c r="Y59" s="9"/>
       <c r="Z59" s="9"/>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -6701,7 +6681,7 @@
       <c r="Y60" s="9"/>
       <c r="Z60" s="9"/>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -6727,7 +6707,7 @@
       <c r="Y61" s="9"/>
       <c r="Z61" s="9"/>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -6753,7 +6733,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -6779,7 +6759,7 @@
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
     </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -6805,7 +6785,7 @@
       <c r="Y64" s="9"/>
       <c r="Z64" s="9"/>
     </row>
-    <row r="65" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -6831,7 +6811,7 @@
       <c r="Y65" s="9"/>
       <c r="Z65" s="9"/>
     </row>
-    <row r="66" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -6857,7 +6837,7 @@
       <c r="Y66" s="9"/>
       <c r="Z66" s="9"/>
     </row>
-    <row r="67" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -6883,7 +6863,7 @@
       <c r="Y67" s="9"/>
       <c r="Z67" s="9"/>
     </row>
-    <row r="68" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -6909,7 +6889,7 @@
       <c r="Y68" s="9"/>
       <c r="Z68" s="9"/>
     </row>
-    <row r="69" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -6935,7 +6915,7 @@
       <c r="Y69" s="9"/>
       <c r="Z69" s="9"/>
     </row>
-    <row r="70" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
@@ -6961,7 +6941,7 @@
       <c r="Y70" s="9"/>
       <c r="Z70" s="9"/>
     </row>
-    <row r="71" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -6987,7 +6967,7 @@
       <c r="Y71" s="9"/>
       <c r="Z71" s="9"/>
     </row>
-    <row r="72" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -7013,7 +6993,7 @@
       <c r="Y72" s="9"/>
       <c r="Z72" s="9"/>
     </row>
-    <row r="73" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -7039,7 +7019,7 @@
       <c r="Y73" s="9"/>
       <c r="Z73" s="9"/>
     </row>
-    <row r="74" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -7065,7 +7045,7 @@
       <c r="Y74" s="9"/>
       <c r="Z74" s="9"/>
     </row>
-    <row r="75" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -7091,7 +7071,7 @@
       <c r="Y75" s="9"/>
       <c r="Z75" s="9"/>
     </row>
-    <row r="76" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -7117,7 +7097,7 @@
       <c r="Y76" s="9"/>
       <c r="Z76" s="9"/>
     </row>
-    <row r="77" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -7143,7 +7123,7 @@
       <c r="Y77" s="9"/>
       <c r="Z77" s="9"/>
     </row>
-    <row r="78" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -7169,7 +7149,7 @@
       <c r="Y78" s="9"/>
       <c r="Z78" s="9"/>
     </row>
-    <row r="79" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -7195,7 +7175,7 @@
       <c r="Y79" s="9"/>
       <c r="Z79" s="9"/>
     </row>
-    <row r="80" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -7221,7 +7201,7 @@
       <c r="Y80" s="9"/>
       <c r="Z80" s="9"/>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -7247,7 +7227,7 @@
       <c r="Y81" s="9"/>
       <c r="Z81" s="9"/>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -7273,7 +7253,7 @@
       <c r="Y82" s="9"/>
       <c r="Z82" s="9"/>
     </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -7299,7 +7279,7 @@
       <c r="Y83" s="9"/>
       <c r="Z83" s="9"/>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -7325,7 +7305,7 @@
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
     </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -7351,7 +7331,7 @@
       <c r="Y85" s="9"/>
       <c r="Z85" s="9"/>
     </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -7377,7 +7357,7 @@
       <c r="Y86" s="9"/>
       <c r="Z86" s="9"/>
     </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -7403,7 +7383,7 @@
       <c r="Y87" s="9"/>
       <c r="Z87" s="9"/>
     </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -7429,7 +7409,7 @@
       <c r="Y88" s="9"/>
       <c r="Z88" s="9"/>
     </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -7455,7 +7435,7 @@
       <c r="Y89" s="9"/>
       <c r="Z89" s="9"/>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -7481,7 +7461,7 @@
       <c r="Y90" s="9"/>
       <c r="Z90" s="9"/>
     </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -7507,7 +7487,7 @@
       <c r="Y91" s="9"/>
       <c r="Z91" s="9"/>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -7533,7 +7513,7 @@
       <c r="Y92" s="9"/>
       <c r="Z92" s="9"/>
     </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -7559,7 +7539,7 @@
       <c r="Y93" s="9"/>
       <c r="Z93" s="9"/>
     </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -7585,7 +7565,7 @@
       <c r="Y94" s="9"/>
       <c r="Z94" s="9"/>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -7611,7 +7591,7 @@
       <c r="Y95" s="9"/>
       <c r="Z95" s="9"/>
     </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -7637,7 +7617,7 @@
       <c r="Y96" s="9"/>
       <c r="Z96" s="9"/>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -7663,7 +7643,7 @@
       <c r="Y97" s="9"/>
       <c r="Z97" s="9"/>
     </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -7689,7 +7669,7 @@
       <c r="Y98" s="9"/>
       <c r="Z98" s="9"/>
     </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -7715,7 +7695,7 @@
       <c r="Y99" s="9"/>
       <c r="Z99" s="9"/>
     </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -7741,7 +7721,7 @@
       <c r="Y100" s="9"/>
       <c r="Z100" s="9"/>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -7767,7 +7747,7 @@
       <c r="Y101" s="9"/>
       <c r="Z101" s="9"/>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -7793,7 +7773,7 @@
       <c r="Y102" s="9"/>
       <c r="Z102" s="9"/>
     </row>
-    <row r="103" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -7819,7 +7799,7 @@
       <c r="Y103" s="9"/>
       <c r="Z103" s="9"/>
     </row>
-    <row r="104" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -7845,7 +7825,7 @@
       <c r="Y104" s="9"/>
       <c r="Z104" s="9"/>
     </row>
-    <row r="105" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -7871,7 +7851,7 @@
       <c r="Y105" s="9"/>
       <c r="Z105" s="9"/>
     </row>
-    <row r="106" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -7897,7 +7877,7 @@
       <c r="Y106" s="9"/>
       <c r="Z106" s="9"/>
     </row>
-    <row r="107" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -7923,7 +7903,7 @@
       <c r="Y107" s="9"/>
       <c r="Z107" s="9"/>
     </row>
-    <row r="108" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -7949,7 +7929,7 @@
       <c r="Y108" s="9"/>
       <c r="Z108" s="9"/>
     </row>
-    <row r="109" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -7975,7 +7955,7 @@
       <c r="Y109" s="9"/>
       <c r="Z109" s="9"/>
     </row>
-    <row r="110" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -8001,7 +7981,7 @@
       <c r="Y110" s="9"/>
       <c r="Z110" s="9"/>
     </row>
-    <row r="111" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -8027,7 +8007,7 @@
       <c r="Y111" s="9"/>
       <c r="Z111" s="9"/>
     </row>
-    <row r="112" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -8053,7 +8033,7 @@
       <c r="Y112" s="9"/>
       <c r="Z112" s="9"/>
     </row>
-    <row r="113" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -8079,7 +8059,7 @@
       <c r="Y113" s="9"/>
       <c r="Z113" s="9"/>
     </row>
-    <row r="114" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -8105,7 +8085,7 @@
       <c r="Y114" s="9"/>
       <c r="Z114" s="9"/>
     </row>
-    <row r="115" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -8131,7 +8111,7 @@
       <c r="Y115" s="9"/>
       <c r="Z115" s="9"/>
     </row>
-    <row r="116" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -8157,7 +8137,7 @@
       <c r="Y116" s="9"/>
       <c r="Z116" s="9"/>
     </row>
-    <row r="117" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -8183,7 +8163,7 @@
       <c r="Y117" s="9"/>
       <c r="Z117" s="9"/>
     </row>
-    <row r="118" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -8209,7 +8189,7 @@
       <c r="Y118" s="9"/>
       <c r="Z118" s="9"/>
     </row>
-    <row r="119" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -8235,7 +8215,7 @@
       <c r="Y119" s="9"/>
       <c r="Z119" s="9"/>
     </row>
-    <row r="120" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -8261,7 +8241,7 @@
       <c r="Y120" s="9"/>
       <c r="Z120" s="9"/>
     </row>
-    <row r="121" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -8287,7 +8267,7 @@
       <c r="Y121" s="9"/>
       <c r="Z121" s="9"/>
     </row>
-    <row r="122" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -8313,7 +8293,7 @@
       <c r="Y122" s="9"/>
       <c r="Z122" s="9"/>
     </row>
-    <row r="123" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -8339,7 +8319,7 @@
       <c r="Y123" s="9"/>
       <c r="Z123" s="9"/>
     </row>
-    <row r="124" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -8365,7 +8345,7 @@
       <c r="Y124" s="9"/>
       <c r="Z124" s="9"/>
     </row>
-    <row r="125" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -8391,7 +8371,7 @@
       <c r="Y125" s="9"/>
       <c r="Z125" s="9"/>
     </row>
-    <row r="126" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -8417,7 +8397,7 @@
       <c r="Y126" s="9"/>
       <c r="Z126" s="9"/>
     </row>
-    <row r="127" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -8443,7 +8423,7 @@
       <c r="Y127" s="9"/>
       <c r="Z127" s="9"/>
     </row>
-    <row r="128" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -8469,7 +8449,7 @@
       <c r="Y128" s="9"/>
       <c r="Z128" s="9"/>
     </row>
-    <row r="129" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -8495,7 +8475,7 @@
       <c r="Y129" s="9"/>
       <c r="Z129" s="9"/>
     </row>
-    <row r="130" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -8521,7 +8501,7 @@
       <c r="Y130" s="9"/>
       <c r="Z130" s="9"/>
     </row>
-    <row r="131" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -8547,7 +8527,7 @@
       <c r="Y131" s="9"/>
       <c r="Z131" s="9"/>
     </row>
-    <row r="132" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -8573,7 +8553,7 @@
       <c r="Y132" s="9"/>
       <c r="Z132" s="9"/>
     </row>
-    <row r="133" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -8599,7 +8579,7 @@
       <c r="Y133" s="9"/>
       <c r="Z133" s="9"/>
     </row>
-    <row r="134" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -8625,7 +8605,7 @@
       <c r="Y134" s="9"/>
       <c r="Z134" s="9"/>
     </row>
-    <row r="135" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -8651,7 +8631,7 @@
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
     </row>
-    <row r="136" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -8677,7 +8657,7 @@
       <c r="Y136" s="9"/>
       <c r="Z136" s="9"/>
     </row>
-    <row r="137" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -8703,7 +8683,7 @@
       <c r="Y137" s="9"/>
       <c r="Z137" s="9"/>
     </row>
-    <row r="138" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -8729,7 +8709,7 @@
       <c r="Y138" s="9"/>
       <c r="Z138" s="9"/>
     </row>
-    <row r="139" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -8755,7 +8735,7 @@
       <c r="Y139" s="9"/>
       <c r="Z139" s="9"/>
     </row>
-    <row r="140" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -8781,7 +8761,7 @@
       <c r="Y140" s="9"/>
       <c r="Z140" s="9"/>
     </row>
-    <row r="141" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -8807,7 +8787,7 @@
       <c r="Y141" s="9"/>
       <c r="Z141" s="9"/>
     </row>
-    <row r="142" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -8833,7 +8813,7 @@
       <c r="Y142" s="9"/>
       <c r="Z142" s="9"/>
     </row>
-    <row r="143" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -8859,7 +8839,7 @@
       <c r="Y143" s="9"/>
       <c r="Z143" s="9"/>
     </row>
-    <row r="144" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -8885,7 +8865,7 @@
       <c r="Y144" s="9"/>
       <c r="Z144" s="9"/>
     </row>
-    <row r="145" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -8911,7 +8891,7 @@
       <c r="Y145" s="9"/>
       <c r="Z145" s="9"/>
     </row>
-    <row r="146" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -8937,7 +8917,7 @@
       <c r="Y146" s="9"/>
       <c r="Z146" s="9"/>
     </row>
-    <row r="147" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -8963,7 +8943,7 @@
       <c r="Y147" s="9"/>
       <c r="Z147" s="9"/>
     </row>
-    <row r="148" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -8989,7 +8969,7 @@
       <c r="Y148" s="9"/>
       <c r="Z148" s="9"/>
     </row>
-    <row r="149" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -9015,7 +8995,7 @@
       <c r="Y149" s="9"/>
       <c r="Z149" s="9"/>
     </row>
-    <row r="150" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -9041,7 +9021,7 @@
       <c r="Y150" s="9"/>
       <c r="Z150" s="9"/>
     </row>
-    <row r="151" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -9067,7 +9047,7 @@
       <c r="Y151" s="9"/>
       <c r="Z151" s="9"/>
     </row>
-    <row r="152" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -9093,7 +9073,7 @@
       <c r="Y152" s="9"/>
       <c r="Z152" s="9"/>
     </row>
-    <row r="153" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -9119,7 +9099,7 @@
       <c r="Y153" s="9"/>
       <c r="Z153" s="9"/>
     </row>
-    <row r="154" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -9145,7 +9125,7 @@
       <c r="Y154" s="9"/>
       <c r="Z154" s="9"/>
     </row>
-    <row r="155" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -9171,7 +9151,7 @@
       <c r="Y155" s="9"/>
       <c r="Z155" s="9"/>
     </row>
-    <row r="156" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -9197,7 +9177,7 @@
       <c r="Y156" s="9"/>
       <c r="Z156" s="9"/>
     </row>
-    <row r="157" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -9223,7 +9203,7 @@
       <c r="Y157" s="9"/>
       <c r="Z157" s="9"/>
     </row>
-    <row r="158" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -9249,7 +9229,7 @@
       <c r="Y158" s="9"/>
       <c r="Z158" s="9"/>
     </row>
-    <row r="159" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -9275,7 +9255,7 @@
       <c r="Y159" s="9"/>
       <c r="Z159" s="9"/>
     </row>
-    <row r="160" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -9301,7 +9281,7 @@
       <c r="Y160" s="9"/>
       <c r="Z160" s="9"/>
     </row>
-    <row r="161" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -9327,7 +9307,7 @@
       <c r="Y161" s="9"/>
       <c r="Z161" s="9"/>
     </row>
-    <row r="162" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -9353,7 +9333,7 @@
       <c r="Y162" s="9"/>
       <c r="Z162" s="9"/>
     </row>
-    <row r="163" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -9379,7 +9359,7 @@
       <c r="Y163" s="9"/>
       <c r="Z163" s="9"/>
     </row>
-    <row r="164" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -9405,7 +9385,7 @@
       <c r="Y164" s="9"/>
       <c r="Z164" s="9"/>
     </row>
-    <row r="165" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -9431,7 +9411,7 @@
       <c r="Y165" s="9"/>
       <c r="Z165" s="9"/>
     </row>
-    <row r="166" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -9457,7 +9437,7 @@
       <c r="Y166" s="9"/>
       <c r="Z166" s="9"/>
     </row>
-    <row r="167" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -9483,7 +9463,7 @@
       <c r="Y167" s="9"/>
       <c r="Z167" s="9"/>
     </row>
-    <row r="168" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -9509,7 +9489,7 @@
       <c r="Y168" s="9"/>
       <c r="Z168" s="9"/>
     </row>
-    <row r="169" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -9535,7 +9515,7 @@
       <c r="Y169" s="9"/>
       <c r="Z169" s="9"/>
     </row>
-    <row r="170" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -9561,7 +9541,7 @@
       <c r="Y170" s="9"/>
       <c r="Z170" s="9"/>
     </row>
-    <row r="171" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -9587,7 +9567,7 @@
       <c r="Y171" s="9"/>
       <c r="Z171" s="9"/>
     </row>
-    <row r="172" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -9613,7 +9593,7 @@
       <c r="Y172" s="9"/>
       <c r="Z172" s="9"/>
     </row>
-    <row r="173" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -9639,7 +9619,7 @@
       <c r="Y173" s="9"/>
       <c r="Z173" s="9"/>
     </row>
-    <row r="174" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -9665,7 +9645,7 @@
       <c r="Y174" s="9"/>
       <c r="Z174" s="9"/>
     </row>
-    <row r="175" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -9691,7 +9671,7 @@
       <c r="Y175" s="9"/>
       <c r="Z175" s="9"/>
     </row>
-    <row r="176" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -9717,7 +9697,7 @@
       <c r="Y176" s="9"/>
       <c r="Z176" s="9"/>
     </row>
-    <row r="177" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -9743,7 +9723,7 @@
       <c r="Y177" s="9"/>
       <c r="Z177" s="9"/>
     </row>
-    <row r="178" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -9769,7 +9749,7 @@
       <c r="Y178" s="9"/>
       <c r="Z178" s="9"/>
     </row>
-    <row r="179" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -9795,7 +9775,7 @@
       <c r="Y179" s="9"/>
       <c r="Z179" s="9"/>
     </row>
-    <row r="180" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -9821,7 +9801,7 @@
       <c r="Y180" s="9"/>
       <c r="Z180" s="9"/>
     </row>
-    <row r="181" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -9847,7 +9827,7 @@
       <c r="Y181" s="9"/>
       <c r="Z181" s="9"/>
     </row>
-    <row r="182" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -9873,7 +9853,7 @@
       <c r="Y182" s="9"/>
       <c r="Z182" s="9"/>
     </row>
-    <row r="183" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -9899,7 +9879,7 @@
       <c r="Y183" s="9"/>
       <c r="Z183" s="9"/>
     </row>
-    <row r="184" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -9925,7 +9905,7 @@
       <c r="Y184" s="9"/>
       <c r="Z184" s="9"/>
     </row>
-    <row r="185" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -9951,7 +9931,7 @@
       <c r="Y185" s="9"/>
       <c r="Z185" s="9"/>
     </row>
-    <row r="186" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -9977,7 +9957,7 @@
       <c r="Y186" s="9"/>
       <c r="Z186" s="9"/>
     </row>
-    <row r="187" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -10003,7 +9983,7 @@
       <c r="Y187" s="9"/>
       <c r="Z187" s="9"/>
     </row>
-    <row r="188" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -10029,7 +10009,7 @@
       <c r="Y188" s="9"/>
       <c r="Z188" s="9"/>
     </row>
-    <row r="189" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -10055,7 +10035,7 @@
       <c r="Y189" s="9"/>
       <c r="Z189" s="9"/>
     </row>
-    <row r="190" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -10081,7 +10061,7 @@
       <c r="Y190" s="9"/>
       <c r="Z190" s="9"/>
     </row>
-    <row r="191" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -10107,7 +10087,7 @@
       <c r="Y191" s="9"/>
       <c r="Z191" s="9"/>
     </row>
-    <row r="192" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -10133,7 +10113,7 @@
       <c r="Y192" s="9"/>
       <c r="Z192" s="9"/>
     </row>
-    <row r="193" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -10159,7 +10139,7 @@
       <c r="Y193" s="9"/>
       <c r="Z193" s="9"/>
     </row>
-    <row r="194" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -10185,7 +10165,7 @@
       <c r="Y194" s="9"/>
       <c r="Z194" s="9"/>
     </row>
-    <row r="195" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -10211,7 +10191,7 @@
       <c r="Y195" s="9"/>
       <c r="Z195" s="9"/>
     </row>
-    <row r="196" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -10237,7 +10217,7 @@
       <c r="Y196" s="9"/>
       <c r="Z196" s="9"/>
     </row>
-    <row r="197" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -10263,7 +10243,7 @@
       <c r="Y197" s="9"/>
       <c r="Z197" s="9"/>
     </row>
-    <row r="198" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -10289,7 +10269,7 @@
       <c r="Y198" s="9"/>
       <c r="Z198" s="9"/>
     </row>
-    <row r="199" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -10315,7 +10295,7 @@
       <c r="Y199" s="9"/>
       <c r="Z199" s="9"/>
     </row>
-    <row r="200" spans="3:26" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -10342,19 +10322,25 @@
       <c r="Z200" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Atlantic Safety Builders, LLC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="P1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:AZ200">
-    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/cert_tracker/Contractor Certifications Tracker Demo.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC5C4BC-EE37-4703-847D-98BD12245E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528B7203-3DA0-4E1E-8547-6A892205B245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -840,7 +840,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -859,6 +859,34 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -919,7 +947,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="10">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -1412,7 +1440,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="18" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/27/2026</v>
+        <v>04/28/2026</v>
       </c>
       <c r="H4" s="15"/>
     </row>
@@ -2090,14 +2118,14 @@
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="between">
       <formula>0.7</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4109,7 +4137,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4255,7 +4282,7 @@
         <v>Concrete &amp; Masonry</v>
       </c>
     </row>
-    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -4323,7 +4350,7 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4389,7 +4416,7 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4449,7 +4476,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4489,7 +4516,7 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4559,7 +4586,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -4623,7 +4650,7 @@
         <v>45455</v>
       </c>
     </row>
-    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4663,7 +4690,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -4719,7 +4746,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -4771,7 +4798,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4813,7 +4840,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -4875,7 +4902,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4933,7 +4960,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4981,7 +5008,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -5037,7 +5064,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -5091,7 +5118,7 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5291,7 +5318,7 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -5349,7 +5376,7 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -5399,7 +5426,7 @@
       </c>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -5463,7 +5490,7 @@
         <v>43172</v>
       </c>
     </row>
-    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -5523,7 +5550,7 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -5575,7 +5602,7 @@
         <v>43152</v>
       </c>
     </row>
-    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -5617,7 +5644,7 @@
       </c>
       <c r="Z27" s="9"/>
     </row>
-    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -5673,7 +5700,7 @@
         <v>44639</v>
       </c>
     </row>
-    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -5737,7 +5764,7 @@
       </c>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -5801,7 +5828,7 @@
         <v>44660</v>
       </c>
     </row>
-    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -5857,7 +5884,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -5913,7 +5940,7 @@
         <v>43239</v>
       </c>
     </row>
-    <row r="33" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -5953,7 +5980,7 @@
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -5987,7 +6014,7 @@
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
     </row>
-    <row r="35" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -6031,7 +6058,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="36" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -6057,7 +6084,7 @@
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
     </row>
-    <row r="37" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -6083,7 +6110,7 @@
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
     </row>
-    <row r="38" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -6109,7 +6136,7 @@
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
     </row>
-    <row r="39" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -6135,7 +6162,7 @@
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
     </row>
-    <row r="40" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -6161,7 +6188,7 @@
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
     </row>
-    <row r="41" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -6187,7 +6214,7 @@
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -6213,7 +6240,7 @@
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -6239,7 +6266,7 @@
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
     </row>
-    <row r="44" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -6265,7 +6292,7 @@
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
     </row>
-    <row r="45" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -6291,7 +6318,7 @@
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
     </row>
-    <row r="46" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -6317,7 +6344,7 @@
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
     </row>
-    <row r="47" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -6343,7 +6370,7 @@
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
     </row>
-    <row r="48" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -6369,7 +6396,7 @@
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
     </row>
-    <row r="49" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -6395,7 +6422,7 @@
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
     </row>
-    <row r="50" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -6421,7 +6448,7 @@
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
     </row>
-    <row r="51" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -6447,7 +6474,7 @@
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
     </row>
-    <row r="52" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -6473,7 +6500,7 @@
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -6499,7 +6526,7 @@
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
     </row>
-    <row r="54" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -6525,7 +6552,7 @@
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -6551,7 +6578,7 @@
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -6577,7 +6604,7 @@
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -6603,7 +6630,7 @@
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
     </row>
-    <row r="58" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -6629,7 +6656,7 @@
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
     </row>
-    <row r="59" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -6655,7 +6682,7 @@
       <c r="Y59" s="9"/>
       <c r="Z59" s="9"/>
     </row>
-    <row r="60" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -6681,7 +6708,7 @@
       <c r="Y60" s="9"/>
       <c r="Z60" s="9"/>
     </row>
-    <row r="61" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -6707,7 +6734,7 @@
       <c r="Y61" s="9"/>
       <c r="Z61" s="9"/>
     </row>
-    <row r="62" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -6733,7 +6760,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -6759,7 +6786,7 @@
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
     </row>
-    <row r="64" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -6785,7 +6812,7 @@
       <c r="Y64" s="9"/>
       <c r="Z64" s="9"/>
     </row>
-    <row r="65" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -6811,7 +6838,7 @@
       <c r="Y65" s="9"/>
       <c r="Z65" s="9"/>
     </row>
-    <row r="66" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -6837,7 +6864,7 @@
       <c r="Y66" s="9"/>
       <c r="Z66" s="9"/>
     </row>
-    <row r="67" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -6863,7 +6890,7 @@
       <c r="Y67" s="9"/>
       <c r="Z67" s="9"/>
     </row>
-    <row r="68" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -6889,7 +6916,7 @@
       <c r="Y68" s="9"/>
       <c r="Z68" s="9"/>
     </row>
-    <row r="69" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -6915,7 +6942,7 @@
       <c r="Y69" s="9"/>
       <c r="Z69" s="9"/>
     </row>
-    <row r="70" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
@@ -6941,7 +6968,7 @@
       <c r="Y70" s="9"/>
       <c r="Z70" s="9"/>
     </row>
-    <row r="71" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -6967,7 +6994,7 @@
       <c r="Y71" s="9"/>
       <c r="Z71" s="9"/>
     </row>
-    <row r="72" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -6993,7 +7020,7 @@
       <c r="Y72" s="9"/>
       <c r="Z72" s="9"/>
     </row>
-    <row r="73" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -7019,7 +7046,7 @@
       <c r="Y73" s="9"/>
       <c r="Z73" s="9"/>
     </row>
-    <row r="74" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -7045,7 +7072,7 @@
       <c r="Y74" s="9"/>
       <c r="Z74" s="9"/>
     </row>
-    <row r="75" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -7071,7 +7098,7 @@
       <c r="Y75" s="9"/>
       <c r="Z75" s="9"/>
     </row>
-    <row r="76" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -7097,7 +7124,7 @@
       <c r="Y76" s="9"/>
       <c r="Z76" s="9"/>
     </row>
-    <row r="77" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -7123,7 +7150,7 @@
       <c r="Y77" s="9"/>
       <c r="Z77" s="9"/>
     </row>
-    <row r="78" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -7149,7 +7176,7 @@
       <c r="Y78" s="9"/>
       <c r="Z78" s="9"/>
     </row>
-    <row r="79" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -7175,7 +7202,7 @@
       <c r="Y79" s="9"/>
       <c r="Z79" s="9"/>
     </row>
-    <row r="80" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -7201,7 +7228,7 @@
       <c r="Y80" s="9"/>
       <c r="Z80" s="9"/>
     </row>
-    <row r="81" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -7227,7 +7254,7 @@
       <c r="Y81" s="9"/>
       <c r="Z81" s="9"/>
     </row>
-    <row r="82" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -7253,7 +7280,7 @@
       <c r="Y82" s="9"/>
       <c r="Z82" s="9"/>
     </row>
-    <row r="83" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -7279,7 +7306,7 @@
       <c r="Y83" s="9"/>
       <c r="Z83" s="9"/>
     </row>
-    <row r="84" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -7305,7 +7332,7 @@
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
     </row>
-    <row r="85" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -7331,7 +7358,7 @@
       <c r="Y85" s="9"/>
       <c r="Z85" s="9"/>
     </row>
-    <row r="86" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -7357,7 +7384,7 @@
       <c r="Y86" s="9"/>
       <c r="Z86" s="9"/>
     </row>
-    <row r="87" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -7383,7 +7410,7 @@
       <c r="Y87" s="9"/>
       <c r="Z87" s="9"/>
     </row>
-    <row r="88" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -7409,7 +7436,7 @@
       <c r="Y88" s="9"/>
       <c r="Z88" s="9"/>
     </row>
-    <row r="89" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -7435,7 +7462,7 @@
       <c r="Y89" s="9"/>
       <c r="Z89" s="9"/>
     </row>
-    <row r="90" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -7461,7 +7488,7 @@
       <c r="Y90" s="9"/>
       <c r="Z90" s="9"/>
     </row>
-    <row r="91" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -7487,7 +7514,7 @@
       <c r="Y91" s="9"/>
       <c r="Z91" s="9"/>
     </row>
-    <row r="92" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -7513,7 +7540,7 @@
       <c r="Y92" s="9"/>
       <c r="Z92" s="9"/>
     </row>
-    <row r="93" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -7539,7 +7566,7 @@
       <c r="Y93" s="9"/>
       <c r="Z93" s="9"/>
     </row>
-    <row r="94" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -7565,7 +7592,7 @@
       <c r="Y94" s="9"/>
       <c r="Z94" s="9"/>
     </row>
-    <row r="95" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -7591,7 +7618,7 @@
       <c r="Y95" s="9"/>
       <c r="Z95" s="9"/>
     </row>
-    <row r="96" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -7617,7 +7644,7 @@
       <c r="Y96" s="9"/>
       <c r="Z96" s="9"/>
     </row>
-    <row r="97" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -7643,7 +7670,7 @@
       <c r="Y97" s="9"/>
       <c r="Z97" s="9"/>
     </row>
-    <row r="98" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -7669,7 +7696,7 @@
       <c r="Y98" s="9"/>
       <c r="Z98" s="9"/>
     </row>
-    <row r="99" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -7695,7 +7722,7 @@
       <c r="Y99" s="9"/>
       <c r="Z99" s="9"/>
     </row>
-    <row r="100" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -7721,7 +7748,7 @@
       <c r="Y100" s="9"/>
       <c r="Z100" s="9"/>
     </row>
-    <row r="101" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -7747,7 +7774,7 @@
       <c r="Y101" s="9"/>
       <c r="Z101" s="9"/>
     </row>
-    <row r="102" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -7773,7 +7800,7 @@
       <c r="Y102" s="9"/>
       <c r="Z102" s="9"/>
     </row>
-    <row r="103" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -7799,7 +7826,7 @@
       <c r="Y103" s="9"/>
       <c r="Z103" s="9"/>
     </row>
-    <row r="104" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -7825,7 +7852,7 @@
       <c r="Y104" s="9"/>
       <c r="Z104" s="9"/>
     </row>
-    <row r="105" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -7851,7 +7878,7 @@
       <c r="Y105" s="9"/>
       <c r="Z105" s="9"/>
     </row>
-    <row r="106" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -7877,7 +7904,7 @@
       <c r="Y106" s="9"/>
       <c r="Z106" s="9"/>
     </row>
-    <row r="107" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -7903,7 +7930,7 @@
       <c r="Y107" s="9"/>
       <c r="Z107" s="9"/>
     </row>
-    <row r="108" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -7929,7 +7956,7 @@
       <c r="Y108" s="9"/>
       <c r="Z108" s="9"/>
     </row>
-    <row r="109" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -7955,7 +7982,7 @@
       <c r="Y109" s="9"/>
       <c r="Z109" s="9"/>
     </row>
-    <row r="110" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -7981,7 +8008,7 @@
       <c r="Y110" s="9"/>
       <c r="Z110" s="9"/>
     </row>
-    <row r="111" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -8007,7 +8034,7 @@
       <c r="Y111" s="9"/>
       <c r="Z111" s="9"/>
     </row>
-    <row r="112" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -8033,7 +8060,7 @@
       <c r="Y112" s="9"/>
       <c r="Z112" s="9"/>
     </row>
-    <row r="113" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -8059,7 +8086,7 @@
       <c r="Y113" s="9"/>
       <c r="Z113" s="9"/>
     </row>
-    <row r="114" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -8085,7 +8112,7 @@
       <c r="Y114" s="9"/>
       <c r="Z114" s="9"/>
     </row>
-    <row r="115" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -8111,7 +8138,7 @@
       <c r="Y115" s="9"/>
       <c r="Z115" s="9"/>
     </row>
-    <row r="116" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -8137,7 +8164,7 @@
       <c r="Y116" s="9"/>
       <c r="Z116" s="9"/>
     </row>
-    <row r="117" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -8163,7 +8190,7 @@
       <c r="Y117" s="9"/>
       <c r="Z117" s="9"/>
     </row>
-    <row r="118" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -8189,7 +8216,7 @@
       <c r="Y118" s="9"/>
       <c r="Z118" s="9"/>
     </row>
-    <row r="119" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -8215,7 +8242,7 @@
       <c r="Y119" s="9"/>
       <c r="Z119" s="9"/>
     </row>
-    <row r="120" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -8241,7 +8268,7 @@
       <c r="Y120" s="9"/>
       <c r="Z120" s="9"/>
     </row>
-    <row r="121" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -8267,7 +8294,7 @@
       <c r="Y121" s="9"/>
       <c r="Z121" s="9"/>
     </row>
-    <row r="122" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -8293,7 +8320,7 @@
       <c r="Y122" s="9"/>
       <c r="Z122" s="9"/>
     </row>
-    <row r="123" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -8319,7 +8346,7 @@
       <c r="Y123" s="9"/>
       <c r="Z123" s="9"/>
     </row>
-    <row r="124" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -8345,7 +8372,7 @@
       <c r="Y124" s="9"/>
       <c r="Z124" s="9"/>
     </row>
-    <row r="125" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -8371,7 +8398,7 @@
       <c r="Y125" s="9"/>
       <c r="Z125" s="9"/>
     </row>
-    <row r="126" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -8397,7 +8424,7 @@
       <c r="Y126" s="9"/>
       <c r="Z126" s="9"/>
     </row>
-    <row r="127" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -8423,7 +8450,7 @@
       <c r="Y127" s="9"/>
       <c r="Z127" s="9"/>
     </row>
-    <row r="128" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -8449,7 +8476,7 @@
       <c r="Y128" s="9"/>
       <c r="Z128" s="9"/>
     </row>
-    <row r="129" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -8475,7 +8502,7 @@
       <c r="Y129" s="9"/>
       <c r="Z129" s="9"/>
     </row>
-    <row r="130" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -8501,7 +8528,7 @@
       <c r="Y130" s="9"/>
       <c r="Z130" s="9"/>
     </row>
-    <row r="131" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -8527,7 +8554,7 @@
       <c r="Y131" s="9"/>
       <c r="Z131" s="9"/>
     </row>
-    <row r="132" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -8553,7 +8580,7 @@
       <c r="Y132" s="9"/>
       <c r="Z132" s="9"/>
     </row>
-    <row r="133" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -8579,7 +8606,7 @@
       <c r="Y133" s="9"/>
       <c r="Z133" s="9"/>
     </row>
-    <row r="134" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -8605,7 +8632,7 @@
       <c r="Y134" s="9"/>
       <c r="Z134" s="9"/>
     </row>
-    <row r="135" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -8631,7 +8658,7 @@
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
     </row>
-    <row r="136" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -8657,7 +8684,7 @@
       <c r="Y136" s="9"/>
       <c r="Z136" s="9"/>
     </row>
-    <row r="137" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -8683,7 +8710,7 @@
       <c r="Y137" s="9"/>
       <c r="Z137" s="9"/>
     </row>
-    <row r="138" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -8709,7 +8736,7 @@
       <c r="Y138" s="9"/>
       <c r="Z138" s="9"/>
     </row>
-    <row r="139" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -8735,7 +8762,7 @@
       <c r="Y139" s="9"/>
       <c r="Z139" s="9"/>
     </row>
-    <row r="140" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -8761,7 +8788,7 @@
       <c r="Y140" s="9"/>
       <c r="Z140" s="9"/>
     </row>
-    <row r="141" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -8787,7 +8814,7 @@
       <c r="Y141" s="9"/>
       <c r="Z141" s="9"/>
     </row>
-    <row r="142" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -8813,7 +8840,7 @@
       <c r="Y142" s="9"/>
       <c r="Z142" s="9"/>
     </row>
-    <row r="143" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -8839,7 +8866,7 @@
       <c r="Y143" s="9"/>
       <c r="Z143" s="9"/>
     </row>
-    <row r="144" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -8865,7 +8892,7 @@
       <c r="Y144" s="9"/>
       <c r="Z144" s="9"/>
     </row>
-    <row r="145" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -8891,7 +8918,7 @@
       <c r="Y145" s="9"/>
       <c r="Z145" s="9"/>
     </row>
-    <row r="146" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -8917,7 +8944,7 @@
       <c r="Y146" s="9"/>
       <c r="Z146" s="9"/>
     </row>
-    <row r="147" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -8943,7 +8970,7 @@
       <c r="Y147" s="9"/>
       <c r="Z147" s="9"/>
     </row>
-    <row r="148" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -8969,7 +8996,7 @@
       <c r="Y148" s="9"/>
       <c r="Z148" s="9"/>
     </row>
-    <row r="149" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -8995,7 +9022,7 @@
       <c r="Y149" s="9"/>
       <c r="Z149" s="9"/>
     </row>
-    <row r="150" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -9021,7 +9048,7 @@
       <c r="Y150" s="9"/>
       <c r="Z150" s="9"/>
     </row>
-    <row r="151" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -9047,7 +9074,7 @@
       <c r="Y151" s="9"/>
       <c r="Z151" s="9"/>
     </row>
-    <row r="152" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -9073,7 +9100,7 @@
       <c r="Y152" s="9"/>
       <c r="Z152" s="9"/>
     </row>
-    <row r="153" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -9099,7 +9126,7 @@
       <c r="Y153" s="9"/>
       <c r="Z153" s="9"/>
     </row>
-    <row r="154" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -9125,7 +9152,7 @@
       <c r="Y154" s="9"/>
       <c r="Z154" s="9"/>
     </row>
-    <row r="155" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -9151,7 +9178,7 @@
       <c r="Y155" s="9"/>
       <c r="Z155" s="9"/>
     </row>
-    <row r="156" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -9177,7 +9204,7 @@
       <c r="Y156" s="9"/>
       <c r="Z156" s="9"/>
     </row>
-    <row r="157" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -9203,7 +9230,7 @@
       <c r="Y157" s="9"/>
       <c r="Z157" s="9"/>
     </row>
-    <row r="158" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -9229,7 +9256,7 @@
       <c r="Y158" s="9"/>
       <c r="Z158" s="9"/>
     </row>
-    <row r="159" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -9255,7 +9282,7 @@
       <c r="Y159" s="9"/>
       <c r="Z159" s="9"/>
     </row>
-    <row r="160" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -9281,7 +9308,7 @@
       <c r="Y160" s="9"/>
       <c r="Z160" s="9"/>
     </row>
-    <row r="161" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -9307,7 +9334,7 @@
       <c r="Y161" s="9"/>
       <c r="Z161" s="9"/>
     </row>
-    <row r="162" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -9333,7 +9360,7 @@
       <c r="Y162" s="9"/>
       <c r="Z162" s="9"/>
     </row>
-    <row r="163" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -9359,7 +9386,7 @@
       <c r="Y163" s="9"/>
       <c r="Z163" s="9"/>
     </row>
-    <row r="164" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -9385,7 +9412,7 @@
       <c r="Y164" s="9"/>
       <c r="Z164" s="9"/>
     </row>
-    <row r="165" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -9411,7 +9438,7 @@
       <c r="Y165" s="9"/>
       <c r="Z165" s="9"/>
     </row>
-    <row r="166" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -9437,7 +9464,7 @@
       <c r="Y166" s="9"/>
       <c r="Z166" s="9"/>
     </row>
-    <row r="167" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -9463,7 +9490,7 @@
       <c r="Y167" s="9"/>
       <c r="Z167" s="9"/>
     </row>
-    <row r="168" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -9489,7 +9516,7 @@
       <c r="Y168" s="9"/>
       <c r="Z168" s="9"/>
     </row>
-    <row r="169" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -9515,7 +9542,7 @@
       <c r="Y169" s="9"/>
       <c r="Z169" s="9"/>
     </row>
-    <row r="170" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -9541,7 +9568,7 @@
       <c r="Y170" s="9"/>
       <c r="Z170" s="9"/>
     </row>
-    <row r="171" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -9567,7 +9594,7 @@
       <c r="Y171" s="9"/>
       <c r="Z171" s="9"/>
     </row>
-    <row r="172" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -9593,7 +9620,7 @@
       <c r="Y172" s="9"/>
       <c r="Z172" s="9"/>
     </row>
-    <row r="173" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -9619,7 +9646,7 @@
       <c r="Y173" s="9"/>
       <c r="Z173" s="9"/>
     </row>
-    <row r="174" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -9645,7 +9672,7 @@
       <c r="Y174" s="9"/>
       <c r="Z174" s="9"/>
     </row>
-    <row r="175" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -9671,7 +9698,7 @@
       <c r="Y175" s="9"/>
       <c r="Z175" s="9"/>
     </row>
-    <row r="176" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -9697,7 +9724,7 @@
       <c r="Y176" s="9"/>
       <c r="Z176" s="9"/>
     </row>
-    <row r="177" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -9723,7 +9750,7 @@
       <c r="Y177" s="9"/>
       <c r="Z177" s="9"/>
     </row>
-    <row r="178" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -9749,7 +9776,7 @@
       <c r="Y178" s="9"/>
       <c r="Z178" s="9"/>
     </row>
-    <row r="179" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -9775,7 +9802,7 @@
       <c r="Y179" s="9"/>
       <c r="Z179" s="9"/>
     </row>
-    <row r="180" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -9801,7 +9828,7 @@
       <c r="Y180" s="9"/>
       <c r="Z180" s="9"/>
     </row>
-    <row r="181" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -9827,7 +9854,7 @@
       <c r="Y181" s="9"/>
       <c r="Z181" s="9"/>
     </row>
-    <row r="182" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -9853,7 +9880,7 @@
       <c r="Y182" s="9"/>
       <c r="Z182" s="9"/>
     </row>
-    <row r="183" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -9879,7 +9906,7 @@
       <c r="Y183" s="9"/>
       <c r="Z183" s="9"/>
     </row>
-    <row r="184" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -9905,7 +9932,7 @@
       <c r="Y184" s="9"/>
       <c r="Z184" s="9"/>
     </row>
-    <row r="185" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -9931,7 +9958,7 @@
       <c r="Y185" s="9"/>
       <c r="Z185" s="9"/>
     </row>
-    <row r="186" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -9957,7 +9984,7 @@
       <c r="Y186" s="9"/>
       <c r="Z186" s="9"/>
     </row>
-    <row r="187" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -9983,7 +10010,7 @@
       <c r="Y187" s="9"/>
       <c r="Z187" s="9"/>
     </row>
-    <row r="188" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -10009,7 +10036,7 @@
       <c r="Y188" s="9"/>
       <c r="Z188" s="9"/>
     </row>
-    <row r="189" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -10035,7 +10062,7 @@
       <c r="Y189" s="9"/>
       <c r="Z189" s="9"/>
     </row>
-    <row r="190" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -10061,7 +10088,7 @@
       <c r="Y190" s="9"/>
       <c r="Z190" s="9"/>
     </row>
-    <row r="191" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -10087,7 +10114,7 @@
       <c r="Y191" s="9"/>
       <c r="Z191" s="9"/>
     </row>
-    <row r="192" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -10113,7 +10140,7 @@
       <c r="Y192" s="9"/>
       <c r="Z192" s="9"/>
     </row>
-    <row r="193" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -10139,7 +10166,7 @@
       <c r="Y193" s="9"/>
       <c r="Z193" s="9"/>
     </row>
-    <row r="194" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -10165,7 +10192,7 @@
       <c r="Y194" s="9"/>
       <c r="Z194" s="9"/>
     </row>
-    <row r="195" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -10191,7 +10218,7 @@
       <c r="Y195" s="9"/>
       <c r="Z195" s="9"/>
     </row>
-    <row r="196" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -10217,7 +10244,7 @@
       <c r="Y196" s="9"/>
       <c r="Z196" s="9"/>
     </row>
-    <row r="197" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -10243,7 +10270,7 @@
       <c r="Y197" s="9"/>
       <c r="Z197" s="9"/>
     </row>
-    <row r="198" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -10269,7 +10296,7 @@
       <c r="Y198" s="9"/>
       <c r="Z198" s="9"/>
     </row>
-    <row r="199" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -10295,7 +10322,7 @@
       <c r="Y199" s="9"/>
       <c r="Z199" s="9"/>
     </row>
-    <row r="200" spans="3:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -10322,26 +10349,23 @@
       <c r="Z200" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Atlantic Safety Builders, LLC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="P1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:AZ200">
-    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cert_tracker/Contractor Certifications Tracker Demo.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528B7203-3DA0-4E1E-8547-6A892205B245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8882C1C4-7586-47DE-9B4C-C72CFBF891C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,11 @@
     <sheet name="Tracker" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Tracker!$A$2:$Z$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Tracker!$A$2:$AD$200</definedName>
     <definedName name="ContractorOption" comment="=Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;&quot;&quot;),ROW(Workers!$B:$B)))">Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;""),ROW(Workers!$B:$B)))</definedName>
     <definedName name="JobTitleOptions">Workers!$C$2:INDEX(Workers!$C:$C,LOOKUP(2,1/(Workers!$C:$C&lt;&gt;""),ROW(Workers!$C:$C)))</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +43,328 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="211">
+  <si>
+    <t>HSE Required Certifications</t>
+  </si>
+  <si>
+    <t>Additional Training</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>Stonewall Drilling Services, LLC</t>
+  </si>
+  <si>
+    <t>Pedro A. Maldonado</t>
+  </si>
+  <si>
+    <t>Samuel Ortiz Burgos</t>
+  </si>
+  <si>
+    <t>Luis R. Negrón Ruiz</t>
+  </si>
+  <si>
+    <t>Marta I. Colón</t>
+  </si>
+  <si>
+    <t>Atlas Concrete Works, Inc.</t>
+  </si>
+  <si>
+    <t>Raúl García Molina</t>
+  </si>
+  <si>
+    <t>Ismael Villa</t>
+  </si>
+  <si>
+    <t>Diego Acosta</t>
+  </si>
+  <si>
+    <t>PowerLine Electric Corp.</t>
+  </si>
+  <si>
+    <t>Javier Méndez Torres</t>
+  </si>
+  <si>
+    <t>Óscar R. Figueroa</t>
+  </si>
+  <si>
+    <t>Edwin Ruiz Pagán</t>
+  </si>
+  <si>
+    <t>SafePath Excavation, Co.</t>
+  </si>
+  <si>
+    <t>Antonio Benítez</t>
+  </si>
+  <si>
+    <t>Fernando Soto</t>
+  </si>
+  <si>
+    <t>Rafael Martínez</t>
+  </si>
+  <si>
+    <t>SkyHigh Scaffolding Solutions</t>
+  </si>
+  <si>
+    <t>Gabriel Estévez</t>
+  </si>
+  <si>
+    <t>Mateo Villanueva</t>
+  </si>
+  <si>
+    <t>Leonardo Benítez</t>
+  </si>
+  <si>
+    <t>Atlantic Safety Builders, LLC</t>
+  </si>
+  <si>
+    <t>John Martinez</t>
+  </si>
+  <si>
+    <t>Luis Gonzalez</t>
+  </si>
+  <si>
+    <t>Maria Torres</t>
+  </si>
+  <si>
+    <t>North Shore Mechanical, Inc.</t>
+  </si>
+  <si>
+    <t>Carlos Rivera</t>
+  </si>
+  <si>
+    <t>Javier Morales</t>
+  </si>
+  <si>
+    <t>Elena Ruiz</t>
+  </si>
+  <si>
+    <t>Caribbean Concrete Works</t>
+  </si>
+  <si>
+    <t>Andrea Cruz</t>
+  </si>
+  <si>
+    <t>Pedro Santiago</t>
+  </si>
+  <si>
+    <t>Ricardo Vega</t>
+  </si>
+  <si>
+    <t>IronCore Contractors</t>
+  </si>
+  <si>
+    <t>Daniel Perez</t>
+  </si>
+  <si>
+    <t>Sofia Martinez</t>
+  </si>
+  <si>
+    <t>Coastal Infrastructure LLC</t>
+  </si>
+  <si>
+    <t>Miguel Lopez</t>
+  </si>
+  <si>
+    <t>Valeria Ortiz</t>
+  </si>
+  <si>
+    <t>Pioneer Site Solutions</t>
+  </si>
+  <si>
+    <t>Anthony Ramos</t>
+  </si>
+  <si>
+    <t>Camila Reyes</t>
+  </si>
+  <si>
+    <t>Cornerstone Industrial Group, Corp</t>
+  </si>
+  <si>
+    <t>Francisco González Carmona</t>
+  </si>
+  <si>
+    <t>Steven Cruz Martínez</t>
+  </si>
+  <si>
+    <t>Contractor Certifications Tracker</t>
+  </si>
+  <si>
+    <t>How to use this workbook</t>
+  </si>
+  <si>
+    <t>1. Add new contractors on the Contractors tab.</t>
+  </si>
+  <si>
+    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
+  </si>
+  <si>
+    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
+  </si>
+  <si>
+    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
+  </si>
+  <si>
+    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
+  </si>
+  <si>
+    <t>Color coding on the Tracker</t>
+  </si>
+  <si>
+    <t>• Red cell     = certification missing (empty)</t>
+  </si>
+  <si>
+    <t>• Yellow cell  = completed, expiring within 60 days</t>
+  </si>
+  <si>
+    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
+  </si>
+  <si>
+    <t>• Green cell   = current</t>
+  </si>
+  <si>
+    <t>Sharing with peers</t>
+  </si>
+  <si>
+    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
+  </si>
+  <si>
+    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
+  </si>
+  <si>
+    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
+  </si>
+  <si>
+    <t>Contractor Certifications Dashboard</t>
+  </si>
+  <si>
+    <t>Total Contractors</t>
+  </si>
+  <si>
+    <t>Total Workers</t>
+  </si>
+  <si>
+    <t>Active Workers</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Compliance by Certification</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>% Complete</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>Validity (years, 0=none)</t>
+  </si>
+  <si>
+    <t>Protección Contra Caídas</t>
+  </si>
+  <si>
+    <t>HSE Required</t>
+  </si>
+  <si>
+    <t>Flama Expuesta</t>
+  </si>
+  <si>
+    <t>Espacios Confinados</t>
+  </si>
+  <si>
+    <t>Manejo de Equipo Motorizado</t>
+  </si>
+  <si>
+    <t>Excavación o Zanja</t>
+  </si>
+  <si>
+    <t>Manejo de Tijeras (Scissor Lift)</t>
+  </si>
+  <si>
+    <t>Seguridad Eléctrica</t>
+  </si>
+  <si>
+    <t>Lockout</t>
+  </si>
+  <si>
+    <t>Manejo de Grúas</t>
+  </si>
+  <si>
+    <t>Escaleras</t>
+  </si>
+  <si>
+    <t>Andamios</t>
+  </si>
+  <si>
+    <t>Trabajos con Plomo o Asbesto</t>
+  </si>
+  <si>
+    <t>Comunicación de Riesgos</t>
+  </si>
+  <si>
+    <t>Inducción Jacobs/Lilly</t>
+  </si>
+  <si>
+    <t>OSHA 40Hr HAZWOPER</t>
+  </si>
+  <si>
+    <t>OSHA 8Hr Refresher</t>
+  </si>
+  <si>
+    <t>Drilling Safety</t>
+  </si>
+  <si>
+    <t>Utility Locating</t>
+  </si>
+  <si>
+    <t>OSHA 10</t>
+  </si>
+  <si>
+    <t>OSHA 30</t>
+  </si>
+  <si>
+    <t>Rebar Safety</t>
+  </si>
+  <si>
+    <t>Formwork &amp; Shoring</t>
+  </si>
+  <si>
+    <t>Silica Exposure</t>
+  </si>
+  <si>
+    <t>Concrete &amp; Masonry</t>
+  </si>
+  <si>
+    <t>Equipment Training</t>
+  </si>
+  <si>
+    <t>OSHA 30 501</t>
+  </si>
+  <si>
+    <t>OSHA 30 511</t>
+  </si>
+  <si>
+    <t>Estamos mas que bien</t>
+  </si>
   <si>
     <t>Contractor Name</t>
   </si>
@@ -57,57 +378,36 @@
     <t>Workers (count)</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Stonewall Drilling Services, LLC</t>
-  </si>
-  <si>
     <t>Juan Pérez Vázquez</t>
   </si>
   <si>
     <t>Drilling / Geotechnical</t>
   </si>
   <si>
-    <t>Atlas Concrete Works, Inc.</t>
-  </si>
-  <si>
     <t>Carla M. Santos Vega</t>
   </si>
   <si>
     <t>Concrete &amp; Foundation</t>
   </si>
   <si>
-    <t>PowerLine Electric Corp.</t>
-  </si>
-  <si>
     <t>Miguel Torres Ramos</t>
   </si>
   <si>
     <t>Electrical &amp; Instrumentation</t>
   </si>
   <si>
-    <t>SafePath Excavation, Co.</t>
-  </si>
-  <si>
     <t>Ana L. Reyes Díaz</t>
   </si>
   <si>
     <t>Excavation &amp; Earthworks</t>
   </si>
   <si>
-    <t>SkyHigh Scaffolding Solutions</t>
-  </si>
-  <si>
     <t>Roberto Díaz Cruz</t>
   </si>
   <si>
     <t>Scaffolding / Access Systems</t>
   </si>
   <si>
-    <t>Atlantic Safety Builders, LLC</t>
-  </si>
-  <si>
     <t>Maria Santos</t>
   </si>
   <si>
@@ -117,222 +417,24 @@
     <t>Demo contractor</t>
   </si>
   <si>
-    <t>North Shore Mechanical, Inc.</t>
-  </si>
-  <si>
-    <t>Carlos Rivera</t>
-  </si>
-  <si>
     <t>Mechanical / Utilities</t>
   </si>
   <si>
-    <t>Caribbean Concrete Works</t>
-  </si>
-  <si>
-    <t>Andrea Cruz</t>
-  </si>
-  <si>
     <t>Concrete and Masonry</t>
   </si>
   <si>
-    <t>IronCore Contractors</t>
-  </si>
-  <si>
-    <t>Daniel Perez</t>
-  </si>
-  <si>
     <t>Structural Steel</t>
   </si>
   <si>
-    <t>Coastal Infrastructure LLC</t>
-  </si>
-  <si>
-    <t>Miguel Lopez</t>
-  </si>
-  <si>
     <t>Civil / Infrastructure</t>
   </si>
   <si>
-    <t>Pioneer Site Solutions</t>
-  </si>
-  <si>
-    <t>Anthony Ramos</t>
-  </si>
-  <si>
     <t>Site Development</t>
   </si>
   <si>
-    <t>Cornerstone Industrial Group, Corp</t>
-  </si>
-  <si>
-    <t>Contractor Certifications Tracker</t>
-  </si>
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t>1. Add new contractors on the Contractors tab.</t>
-  </si>
-  <si>
-    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
-  </si>
-  <si>
-    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
-  </si>
-  <si>
-    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
-  </si>
-  <si>
-    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
-  </si>
-  <si>
-    <t>Color coding on the Tracker</t>
-  </si>
-  <si>
-    <t>• Red cell     = certification missing (empty)</t>
-  </si>
-  <si>
-    <t>• Yellow cell  = completed, expiring within 60 days</t>
-  </si>
-  <si>
-    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
-  </si>
-  <si>
-    <t>• Green cell   = current</t>
-  </si>
-  <si>
-    <t>Sharing with peers</t>
-  </si>
-  <si>
-    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
-  </si>
-  <si>
-    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
-  </si>
-  <si>
-    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
-  </si>
-  <si>
-    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
-  </si>
-  <si>
-    <t>Contractor Certifications Dashboard</t>
-  </si>
-  <si>
-    <t>Total Contractors</t>
-  </si>
-  <si>
-    <t>Total Workers</t>
-  </si>
-  <si>
-    <t>Active Workers</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>Compliance by Certification</t>
-  </si>
-  <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>% Complete</t>
-  </si>
-  <si>
-    <t>Bar</t>
-  </si>
-  <si>
-    <t>Validity (years, 0=none)</t>
-  </si>
-  <si>
-    <t>Protección Contra Caídas</t>
-  </si>
-  <si>
-    <t>HSE Required</t>
-  </si>
-  <si>
-    <t>Flama Expuesta</t>
-  </si>
-  <si>
-    <t>Espacios Confinados</t>
-  </si>
-  <si>
-    <t>Manejo de Equipo Motorizado</t>
-  </si>
-  <si>
-    <t>Excavación o Zanja</t>
-  </si>
-  <si>
-    <t>Manejo de Tijeras (Scissor Lift)</t>
-  </si>
-  <si>
-    <t>Seguridad Eléctrica</t>
-  </si>
-  <si>
-    <t>Lockout</t>
-  </si>
-  <si>
-    <t>Manejo de Grúas</t>
-  </si>
-  <si>
-    <t>Escaleras</t>
-  </si>
-  <si>
-    <t>Andamios</t>
-  </si>
-  <si>
-    <t>Trabajos con Plomo o Asbesto</t>
-  </si>
-  <si>
-    <t>Comunicación de Riesgos</t>
-  </si>
-  <si>
-    <t>Inducción Jacobs/Lilly</t>
-  </si>
-  <si>
-    <t>Additional Training</t>
-  </si>
-  <si>
-    <t>OSHA 40Hr HAZWOPER</t>
-  </si>
-  <si>
-    <t>OSHA 8Hr Refresher</t>
-  </si>
-  <si>
-    <t>Drilling Safety</t>
-  </si>
-  <si>
-    <t>Utility Locating</t>
-  </si>
-  <si>
-    <t>OSHA 10</t>
-  </si>
-  <si>
-    <t>OSHA 30</t>
-  </si>
-  <si>
-    <t>Rebar Safety</t>
-  </si>
-  <si>
-    <t>Formwork &amp; Shoring</t>
-  </si>
-  <si>
-    <t>Silica Exposure</t>
-  </si>
-  <si>
-    <t>Concrete &amp; Masonry</t>
-  </si>
-  <si>
     <t>Worker Name</t>
   </si>
   <si>
-    <t>Contractor</t>
-  </si>
-  <si>
     <t>Job Title</t>
   </si>
   <si>
@@ -351,108 +453,57 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Pedro A. Maldonado</t>
-  </si>
-  <si>
     <t>Lead Driller</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
-    <t>Samuel Ortiz Burgos</t>
-  </si>
-  <si>
     <t>Driller Helper</t>
   </si>
   <si>
-    <t>Luis R. Negrón Ruiz</t>
-  </si>
-  <si>
     <t>Driller</t>
   </si>
   <si>
-    <t>Marta I. Colón</t>
-  </si>
-  <si>
     <t>Apprentice</t>
   </si>
   <si>
     <t>onboarding</t>
   </si>
   <si>
-    <t>Raúl García Molina</t>
-  </si>
-  <si>
     <t>Foreman</t>
   </si>
   <si>
-    <t>Ismael Villa</t>
-  </si>
-  <si>
     <t>Concrete Finisher</t>
   </si>
   <si>
-    <t>Diego Acosta</t>
-  </si>
-  <si>
     <t>Laborer</t>
   </si>
   <si>
-    <t>Javier Méndez Torres</t>
-  </si>
-  <si>
     <t>Master Electrician</t>
   </si>
   <si>
-    <t>Óscar R. Figueroa</t>
-  </si>
-  <si>
     <t>Electrician</t>
   </si>
   <si>
-    <t>Edwin Ruiz Pagán</t>
-  </si>
-  <si>
     <t>Apprentice Electrician</t>
   </si>
   <si>
-    <t>Antonio Benítez</t>
-  </si>
-  <si>
     <t>Equipment Operator</t>
   </si>
   <si>
-    <t>Fernando Soto</t>
-  </si>
-  <si>
     <t>Operator</t>
   </si>
   <si>
-    <t>Rafael Martínez</t>
-  </si>
-  <si>
     <t>Spotter</t>
   </si>
   <si>
-    <t>Gabriel Estévez</t>
-  </si>
-  <si>
     <t>Scaffold Erector</t>
   </si>
   <si>
-    <t>Mateo Villanueva</t>
-  </si>
-  <si>
     <t>Scaffold Helper</t>
   </si>
   <si>
-    <t>Leonardo Benítez</t>
-  </si>
-  <si>
-    <t>John Martinez</t>
-  </si>
-  <si>
     <t>ASB-001</t>
   </si>
   <si>
@@ -462,9 +513,6 @@
     <t>787-555-0101</t>
   </si>
   <si>
-    <t>Luis Gonzalez</t>
-  </si>
-  <si>
     <t>ASB-002</t>
   </si>
   <si>
@@ -474,9 +522,6 @@
     <t>787-555-0102</t>
   </si>
   <si>
-    <t>Maria Torres</t>
-  </si>
-  <si>
     <t>Safety Officer</t>
   </si>
   <si>
@@ -504,9 +549,6 @@
     <t>787-555-0201</t>
   </si>
   <si>
-    <t>Javier Morales</t>
-  </si>
-  <si>
     <t>Technician</t>
   </si>
   <si>
@@ -519,9 +561,6 @@
     <t>787-555-0202</t>
   </si>
   <si>
-    <t>Elena Ruiz</t>
-  </si>
-  <si>
     <t>Engineer</t>
   </si>
   <si>
@@ -546,9 +585,6 @@
     <t>787-555-0301</t>
   </si>
   <si>
-    <t>Pedro Santiago</t>
-  </si>
-  <si>
     <t>Mason</t>
   </si>
   <si>
@@ -561,9 +597,6 @@
     <t>787-555-0302</t>
   </si>
   <si>
-    <t>Ricardo Vega</t>
-  </si>
-  <si>
     <t>CCW-003</t>
   </si>
   <si>
@@ -585,9 +618,6 @@
     <t>787-555-0401</t>
   </si>
   <si>
-    <t>Sofia Martinez</t>
-  </si>
-  <si>
     <t>Inspector</t>
   </si>
   <si>
@@ -612,9 +642,6 @@
     <t>787-555-0501</t>
   </si>
   <si>
-    <t>Valeria Ortiz</t>
-  </si>
-  <si>
     <t>Surveyor</t>
   </si>
   <si>
@@ -639,9 +666,6 @@
     <t>787-555-0601</t>
   </si>
   <si>
-    <t>Camila Reyes</t>
-  </si>
-  <si>
     <t>Coordinator</t>
   </si>
   <si>
@@ -652,18 +676,6 @@
   </si>
   <si>
     <t>787-555-0602</t>
-  </si>
-  <si>
-    <t>Francisco González Carmona</t>
-  </si>
-  <si>
-    <t>Steven Cruz Martínez</t>
-  </si>
-  <si>
-    <t>HSE Required Certifications</t>
-  </si>
-  <si>
-    <t>Worker</t>
   </si>
 </sst>
 </file>
@@ -674,7 +686,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +747,16 @@
       <color rgb="FF2E7D32"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -750,16 +772,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E5984"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -797,11 +820,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -824,23 +877,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -858,35 +919,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFE699"/>
+          <bgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -947,7 +980,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Contractor Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Primary Contact"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Specialty"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Workers (count)" dataDxfId="6">
       <calculatedColumnFormula>IF(A2="","",COUNTIF(Workers!B:B,A2))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Notes"/>
@@ -1266,46 +1299,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1313,27 +1346,27 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,17 +1374,17 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -1359,17 +1392,17 @@
     </row>
     <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1382,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
@@ -1395,89 +1428,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="A3" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="20"/>
+      <c r="G3" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="20"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+      <c r="A4" s="22">
         <f>COUNTA(Contractors!A2:A50)</f>
-        <v>12</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="18">
+        <v>11</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="22">
         <f>COUNTA(Workers!A2:A200)</f>
-        <v>33</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="18">
+        <v>31</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="22">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
-        <v>27</v>
-      </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="18" t="str">
+        <v>25</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="22" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
         <v>04/28/2026</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="A7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1495,15 +1528,15 @@
       </c>
       <c r="D9" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C9</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" ref="E9:E32" si="0">IFERROR(C9/(C9+D9),0)</f>
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="F9" s="4" t="str">
-        <f t="shared" ref="F9:F32" si="1">REPT("■",ROUND(E9*20,0))</f>
-        <v>■■■■■■■■■■■■■■■</v>
+        <f t="shared" ref="E9:E36" si="0">IFERROR(C9/(C9+D9),0)</f>
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="F9" s="4" t="e">
+        <f t="shared" ref="F9:F36" si="1">REPT(CHAR(9632),ROUND(E9*20,0))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1521,15 +1554,15 @@
       </c>
       <c r="D10" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C10</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>0.48484848484848486</v>
-      </c>
-      <c r="F10" s="4" t="str">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="F10" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1547,15 +1580,15 @@
       </c>
       <c r="D11" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C11</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="F11" s="4" t="str">
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="F11" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1573,15 +1606,15 @@
       </c>
       <c r="D12" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C12</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>0.48484848484848486</v>
-      </c>
-      <c r="F12" s="4" t="str">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="F12" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1599,15 +1632,15 @@
       </c>
       <c r="D13" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C13</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>0.42424242424242425</v>
-      </c>
-      <c r="F13" s="4" t="str">
+        <v>0.45161290322580644</v>
+      </c>
+      <c r="F13" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1625,15 +1658,15 @@
       </c>
       <c r="D14" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C14</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="F14" s="4" t="str">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="F14" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1651,15 +1684,15 @@
       </c>
       <c r="D15" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C15</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F15" s="4" t="str">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="F15" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,15 +1710,15 @@
       </c>
       <c r="D16" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C16</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="F16" s="4" t="str">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="F16" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,15 +1736,15 @@
       </c>
       <c r="D17" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C17</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="F17" s="4" t="str">
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="F17" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1729,15 +1762,15 @@
       </c>
       <c r="D18" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C18</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="F18" s="4" t="str">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="F18" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1755,15 +1788,15 @@
       </c>
       <c r="D19" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C19</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="F19" s="4" t="str">
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="F19" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1781,15 +1814,15 @@
       </c>
       <c r="D20" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C20</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>0.42424242424242425</v>
-      </c>
-      <c r="F20" s="4" t="str">
+        <v>0.45161290322580644</v>
+      </c>
+      <c r="F20" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1807,15 +1840,15 @@
       </c>
       <c r="D21" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C21</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F21" s="4" t="str">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="F21" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1833,15 +1866,15 @@
       </c>
       <c r="D22" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C22</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="F22" s="4" t="str">
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="F22" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,15 +1892,15 @@
       </c>
       <c r="D23" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C23</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F23" s="4" t="str">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="F23" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1885,15 +1918,15 @@
       </c>
       <c r="D24" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C24</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="F24" s="4" t="str">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="F24" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,19 +1940,19 @@
       </c>
       <c r="C25" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A25,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C25</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>0.30303030303030304</v>
-      </c>
-      <c r="F25" s="4" t="str">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="F25" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,15 +1970,15 @@
       </c>
       <c r="D26" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C26</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>0.30303030303030304</v>
-      </c>
-      <c r="F26" s="4" t="str">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="F26" s="4" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1963,15 +1996,15 @@
       </c>
       <c r="D27" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C27</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" s="12">
         <f t="shared" si="0"/>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="F27" s="13" t="str">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="F27" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,15 +2022,15 @@
       </c>
       <c r="D28" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C28</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" s="12">
         <f t="shared" si="0"/>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="F28" s="13" t="str">
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="F28" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2015,15 +2048,15 @@
       </c>
       <c r="D29" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C29</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" s="12">
         <f t="shared" si="0"/>
-        <v>0.30303030303030304</v>
-      </c>
-      <c r="F29" s="13" t="str">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="F29" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,15 +2074,15 @@
       </c>
       <c r="D30" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C30</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E30" s="12">
         <f t="shared" si="0"/>
-        <v>0.24242424242424243</v>
-      </c>
-      <c r="F30" s="13" t="str">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="F30" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,15 +2100,15 @@
       </c>
       <c r="D31" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C31</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F31" s="13" t="str">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="F31" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2093,39 +2126,143 @@
       </c>
       <c r="D32" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C32</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E32" s="12">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F32" s="13" t="str">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="F32" s="13" t="e">
         <f t="shared" si="1"/>
-        <v>■■■■■■■</v>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="str">
+        <f>Certifications!A26</f>
+        <v>Equipment Training</v>
+      </c>
+      <c r="B33" s="14" t="str">
+        <f>Certifications!B26</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C33" s="14">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A33,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <f>COUNTA(Workers!A$2:A$200)-C33</f>
+        <v>31</v>
+      </c>
+      <c r="E33" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="16" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="str">
+        <f>Certifications!A27</f>
+        <v>OSHA 30 501</v>
+      </c>
+      <c r="B34" s="14" t="str">
+        <f>Certifications!B27</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C34" s="14">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A34,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <f>COUNTA(Workers!A$2:A$200)-C34</f>
+        <v>31</v>
+      </c>
+      <c r="E34" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="str">
+        <f>Certifications!A28</f>
+        <v>OSHA 30 511</v>
+      </c>
+      <c r="B35" s="14" t="str">
+        <f>Certifications!B28</f>
+        <v>Additional Training</v>
+      </c>
+      <c r="C35" s="14">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A35,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="14">
+        <f>COUNTA(Workers!A$2:A$200)-C35</f>
+        <v>30</v>
+      </c>
+      <c r="E35" s="15">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F35" s="16" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="str">
+        <f>Certifications!A29</f>
+        <v>Estamos mas que bien</v>
+      </c>
+      <c r="B36" s="17">
+        <f>Certifications!B29</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="17">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A36,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>27</v>
+      </c>
+      <c r="D36" s="17">
+        <f>COUNTA(Workers!A$2:A$200)-C36</f>
+        <v>4</v>
+      </c>
+      <c r="E36" s="18">
+        <f t="shared" si="0"/>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="19" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="C4:D5"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="G4:H5"/>
     <mergeCell ref="E4:F5"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
       <formula>0.7</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2135,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2146,24 +2283,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2171,10 +2308,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2182,10 +2319,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2193,10 +2330,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2204,10 +2341,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2215,10 +2352,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2226,10 +2363,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2237,10 +2374,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2248,43 +2385,43 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2292,10 +2429,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2303,10 +2440,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2314,21 +2451,21 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2336,21 +2473,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2358,73 +2495,111 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B60" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B58" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"HSE Required,Additional Training"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2449,30 +2624,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="D2">
         <f>IF(A2="","",COUNTIF(Workers!B:B,A2))</f>
@@ -2481,13 +2656,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <f>IF(A3="","",COUNTIF(Workers!B:B,A3))</f>
@@ -2496,13 +2671,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D4">
         <f>IF(A4="","",COUNTIF(Workers!B:B,A4))</f>
@@ -2511,13 +2686,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <f>IF(A5="","",COUNTIF(Workers!B:B,A5))</f>
@@ -2526,13 +2701,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D6">
         <f>IF(A6="","",COUNTIF(Workers!B:B,A6))</f>
@@ -2541,119 +2716,110 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="D7">
         <f>IF(A7="","",COUNTIF(Workers!B:B,A7))</f>
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="D8">
         <f>IF(A8="","",COUNTIF(Workers!B:B,A8))</f>
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="D9">
         <f>IF(A9="","",COUNTIF(Workers!B:B,A9))</f>
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="D10">
         <f>IF(A10="","",COUNTIF(Workers!B:B,A10))</f>
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="D11">
         <f>IF(A11="","",COUNTIF(Workers!B:B,A11))</f>
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="D12">
         <f>IF(A12="","",COUNTIF(Workers!B:B,A12))</f>
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <f>IF(A13="","",COUNTIF(Workers!B:B,A13))</f>
-        <v>2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2904,45 +3070,45 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F2" s="7">
         <v>44270</v>
@@ -2950,16 +3116,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F3" s="7">
         <v>45117</v>
@@ -2967,16 +3133,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F4" s="7">
         <v>44586</v>
@@ -2984,16 +3150,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F5" s="7">
         <v>46054</v>
@@ -3001,16 +3167,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F6" s="7">
         <v>43605</v>
@@ -3018,16 +3184,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F7" s="7">
         <v>44058</v>
@@ -3035,16 +3201,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F8" s="7">
         <v>45597</v>
@@ -3052,16 +3218,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F9" s="7">
         <v>42098</v>
@@ -3069,16 +3235,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F10" s="7">
         <v>44447</v>
@@ -3086,16 +3252,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F11" s="7">
         <v>45940</v>
@@ -3103,16 +3269,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F12" s="7">
         <v>43271</v>
@@ -3120,16 +3286,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F13" s="7">
         <v>44666</v>
@@ -3137,16 +3303,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F14" s="7">
         <v>44985</v>
@@ -3154,16 +3320,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F15" s="7">
         <v>43019</v>
@@ -3171,16 +3337,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="F16" s="7">
         <v>44943</v>
@@ -3188,16 +3354,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F17" s="7">
         <v>46086</v>
@@ -3205,458 +3371,440 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="F18" s="7">
         <v>44635</v>
       </c>
       <c r="G18" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="H18" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F19" s="7">
         <v>45129</v>
       </c>
       <c r="G19" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H19" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F20" s="7">
         <v>44505</v>
       </c>
       <c r="G20" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F21" s="7">
         <v>43992</v>
       </c>
       <c r="G21" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="H21" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="F22" s="7">
         <v>44822</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F23" s="7">
         <v>45303</v>
       </c>
       <c r="G23" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F24" s="7">
         <v>44311</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H24" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F25" s="7">
         <v>44971</v>
       </c>
       <c r="G25" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="H25" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F26" s="7">
         <v>44073</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F27" s="7">
         <v>44700</v>
       </c>
       <c r="G27" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H27" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F28" s="7">
         <v>45202</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H28" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F29" s="7">
         <v>44207</v>
       </c>
       <c r="G29" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H29" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F30" s="7">
         <v>45342</v>
       </c>
       <c r="G30" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H30" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F31" s="7">
         <v>44903</v>
       </c>
       <c r="G31" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H31" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F32" s="7">
         <v>44374</v>
       </c>
       <c r="G32" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H32" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>203</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>204</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F48" s="7"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
@@ -4137,53 +4285,57 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Z200"/>
+  <dimension ref="A1:AD200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="19" width="14" customWidth="1"/>
-    <col min="20" max="26" width="13" customWidth="1"/>
+    <col min="20" max="30" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-    </row>
-    <row r="2" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="27"/>
+    </row>
+    <row r="2" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="str">
         <f>Certifications!A2</f>
@@ -4281,13 +4433,29 @@
         <f>Certifications!A25</f>
         <v>Concrete &amp; Masonry</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA2" s="1" t="str">
+        <f>Certifications!A26</f>
+        <v>Equipment Training</v>
+      </c>
+      <c r="AB2" s="1" t="str">
+        <f>Certifications!A27</f>
+        <v>OSHA 30 501</v>
+      </c>
+      <c r="AC2" s="1" t="str">
+        <f>Certifications!A28</f>
+        <v>OSHA 30 511</v>
+      </c>
+      <c r="AD2" s="1" t="str">
+        <f>Certifications!A29</f>
+        <v>Estamos mas que bien</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>102</v>
       </c>
       <c r="C3" s="9">
         <v>45976</v>
@@ -4349,13 +4517,19 @@
       <c r="X3" s="9"/>
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="C4" s="9">
         <v>45797</v>
@@ -4415,13 +4589,19 @@
       <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="C5" s="9">
         <v>45976</v>
@@ -4475,13 +4655,21 @@
       <c r="X5" s="9"/>
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9">
+        <v>45858</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="C6" s="9">
         <v>45976</v>
@@ -4515,13 +4703,19 @@
       <c r="X6" s="9"/>
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9">
         <v>45976</v>
@@ -4585,13 +4779,19 @@
       <c r="Z7" s="9">
         <v>45248</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="C8" s="9">
         <v>45976</v>
@@ -4649,13 +4849,19 @@
       <c r="Z8" s="9">
         <v>45455</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9">
         <v>45976</v>
@@ -4679,7 +4885,9 @@
       </c>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
+      <c r="S9" s="9">
+        <v>46003</v>
+      </c>
       <c r="T9" s="9"/>
       <c r="U9" s="9">
         <v>45601</v>
@@ -4689,13 +4897,19 @@
       <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="C10" s="9">
         <v>45976</v>
@@ -4745,13 +4959,19 @@
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9">
         <v>45458</v>
@@ -4797,13 +5017,19 @@
       <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9">
         <v>45976</v>
@@ -4839,13 +5065,19 @@
       <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C13" s="9">
         <v>45976</v>
@@ -4901,13 +5133,19 @@
       <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9">
         <v>45797</v>
@@ -4928,7 +5166,7 @@
         <v>45066</v>
       </c>
       <c r="I14" s="9">
-        <v>45797</v>
+        <v>45828</v>
       </c>
       <c r="J14" s="9">
         <v>45797</v>
@@ -4959,13 +5197,19 @@
       <c r="X14" s="9"/>
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9">
         <v>45458</v>
@@ -5007,13 +5251,19 @@
       <c r="X15" s="9"/>
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9">
         <v>45976</v>
@@ -5063,13 +5313,19 @@
       <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C17" s="9">
         <v>45797</v>
@@ -5086,7 +5342,7 @@
         <v>45514</v>
       </c>
       <c r="I17" s="9">
-        <v>45976</v>
+        <v>45945</v>
       </c>
       <c r="J17" s="9">
         <v>45976</v>
@@ -5117,13 +5373,19 @@
       <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9">
         <v>45976</v>
@@ -5155,13 +5417,19 @@
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="C19" s="9">
         <v>45708</v>
@@ -5219,13 +5487,19 @@
       <c r="Z19" s="9">
         <v>44885</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="C20" s="9">
         <v>45976</v>
@@ -5273,13 +5547,19 @@
       <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="C21" s="9">
         <v>45976</v>
@@ -5317,13 +5597,19 @@
       <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9">
@@ -5375,13 +5661,19 @@
       <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -5425,13 +5717,19 @@
         <v>44338</v>
       </c>
       <c r="Z23" s="9"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="C24" s="9">
         <v>45976</v>
@@ -5489,13 +5787,19 @@
       <c r="Z24" s="9">
         <v>43172</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C25" s="9">
         <v>45976</v>
@@ -5549,13 +5853,19 @@
       <c r="Z25" s="9">
         <v>45687</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>35</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -5601,13 +5911,19 @@
       <c r="Z26" s="9">
         <v>43152</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5643,13 +5959,19 @@
         <v>45627</v>
       </c>
       <c r="Z27" s="9"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C28" s="9">
         <v>45976</v>
@@ -5699,13 +6021,19 @@
       <c r="Z28" s="9">
         <v>44639</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="C29" s="9">
         <v>45976</v>
@@ -5763,13 +6091,19 @@
         <v>44984</v>
       </c>
       <c r="Z29" s="9"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9">
@@ -5827,13 +6161,17 @@
       <c r="Z30" s="9">
         <v>44660</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>42</v>
       </c>
       <c r="C31" s="9">
         <v>45458</v>
@@ -5883,13 +6221,17 @@
       <c r="Z31" s="9">
         <v>45632</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -5939,13 +6281,17 @@
       <c r="Z32" s="9">
         <v>43239</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -5979,13 +6325,17 @@
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -6013,13 +6363,17 @@
       <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -6057,8 +6411,12 @@
       <c r="Z35" s="9">
         <v>46059</v>
       </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -6083,8 +6441,12 @@
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -6109,8 +6471,12 @@
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -6135,8 +6501,12 @@
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -6161,8 +6531,12 @@
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -6187,8 +6561,12 @@
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -6213,8 +6591,12 @@
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="9"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -6239,8 +6621,12 @@
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA42" s="9"/>
+      <c r="AB42" s="9"/>
+      <c r="AC42" s="9"/>
+      <c r="AD42" s="9"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -6265,8 +6651,12 @@
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
+      <c r="AD43" s="9"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -6291,8 +6681,12 @@
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="9"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -6317,8 +6711,12 @@
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+      <c r="AD45" s="9"/>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -6343,8 +6741,12 @@
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="9"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -6369,8 +6771,12 @@
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -6395,8 +6801,12 @@
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+      <c r="AD48" s="9"/>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -6421,8 +6831,12 @@
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+      <c r="AD49" s="9"/>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -6447,8 +6861,12 @@
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA50" s="9"/>
+      <c r="AB50" s="9"/>
+      <c r="AC50" s="9"/>
+      <c r="AD50" s="9"/>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -6473,8 +6891,12 @@
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA51" s="9"/>
+      <c r="AB51" s="9"/>
+      <c r="AC51" s="9"/>
+      <c r="AD51" s="9"/>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -6499,8 +6921,12 @@
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA52" s="9"/>
+      <c r="AB52" s="9"/>
+      <c r="AC52" s="9"/>
+      <c r="AD52" s="9"/>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -6525,8 +6951,12 @@
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9"/>
+      <c r="AD53" s="9"/>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -6551,8 +6981,12 @@
       <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA54" s="9"/>
+      <c r="AB54" s="9"/>
+      <c r="AC54" s="9"/>
+      <c r="AD54" s="9"/>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -6577,8 +7011,12 @@
       <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA55" s="9"/>
+      <c r="AB55" s="9"/>
+      <c r="AC55" s="9"/>
+      <c r="AD55" s="9"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -6603,8 +7041,12 @@
       <c r="X56" s="9"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA56" s="9"/>
+      <c r="AB56" s="9"/>
+      <c r="AC56" s="9"/>
+      <c r="AD56" s="9"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -6629,8 +7071,12 @@
       <c r="X57" s="9"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA57" s="9"/>
+      <c r="AB57" s="9"/>
+      <c r="AC57" s="9"/>
+      <c r="AD57" s="9"/>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -6655,8 +7101,12 @@
       <c r="X58" s="9"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA58" s="9"/>
+      <c r="AB58" s="9"/>
+      <c r="AC58" s="9"/>
+      <c r="AD58" s="9"/>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -6681,8 +7131,12 @@
       <c r="X59" s="9"/>
       <c r="Y59" s="9"/>
       <c r="Z59" s="9"/>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA59" s="9"/>
+      <c r="AB59" s="9"/>
+      <c r="AC59" s="9"/>
+      <c r="AD59" s="9"/>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -6707,8 +7161,12 @@
       <c r="X60" s="9"/>
       <c r="Y60" s="9"/>
       <c r="Z60" s="9"/>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA60" s="9"/>
+      <c r="AB60" s="9"/>
+      <c r="AC60" s="9"/>
+      <c r="AD60" s="9"/>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -6733,8 +7191,12 @@
       <c r="X61" s="9"/>
       <c r="Y61" s="9"/>
       <c r="Z61" s="9"/>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA61" s="9"/>
+      <c r="AB61" s="9"/>
+      <c r="AC61" s="9"/>
+      <c r="AD61" s="9"/>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -6759,8 +7221,12 @@
       <c r="X62" s="9"/>
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA62" s="9"/>
+      <c r="AB62" s="9"/>
+      <c r="AC62" s="9"/>
+      <c r="AD62" s="9"/>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -6785,8 +7251,12 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA63" s="9"/>
+      <c r="AB63" s="9"/>
+      <c r="AC63" s="9"/>
+      <c r="AD63" s="9"/>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -6811,8 +7281,12 @@
       <c r="X64" s="9"/>
       <c r="Y64" s="9"/>
       <c r="Z64" s="9"/>
-    </row>
-    <row r="65" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA64" s="9"/>
+      <c r="AB64" s="9"/>
+      <c r="AC64" s="9"/>
+      <c r="AD64" s="9"/>
+    </row>
+    <row r="65" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -6837,8 +7311,12 @@
       <c r="X65" s="9"/>
       <c r="Y65" s="9"/>
       <c r="Z65" s="9"/>
-    </row>
-    <row r="66" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA65" s="9"/>
+      <c r="AB65" s="9"/>
+      <c r="AC65" s="9"/>
+      <c r="AD65" s="9"/>
+    </row>
+    <row r="66" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -6863,8 +7341,12 @@
       <c r="X66" s="9"/>
       <c r="Y66" s="9"/>
       <c r="Z66" s="9"/>
-    </row>
-    <row r="67" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA66" s="9"/>
+      <c r="AB66" s="9"/>
+      <c r="AC66" s="9"/>
+      <c r="AD66" s="9"/>
+    </row>
+    <row r="67" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -6889,8 +7371,12 @@
       <c r="X67" s="9"/>
       <c r="Y67" s="9"/>
       <c r="Z67" s="9"/>
-    </row>
-    <row r="68" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA67" s="9"/>
+      <c r="AB67" s="9"/>
+      <c r="AC67" s="9"/>
+      <c r="AD67" s="9"/>
+    </row>
+    <row r="68" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -6915,8 +7401,12 @@
       <c r="X68" s="9"/>
       <c r="Y68" s="9"/>
       <c r="Z68" s="9"/>
-    </row>
-    <row r="69" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA68" s="9"/>
+      <c r="AB68" s="9"/>
+      <c r="AC68" s="9"/>
+      <c r="AD68" s="9"/>
+    </row>
+    <row r="69" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -6941,8 +7431,12 @@
       <c r="X69" s="9"/>
       <c r="Y69" s="9"/>
       <c r="Z69" s="9"/>
-    </row>
-    <row r="70" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA69" s="9"/>
+      <c r="AB69" s="9"/>
+      <c r="AC69" s="9"/>
+      <c r="AD69" s="9"/>
+    </row>
+    <row r="70" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
@@ -6967,8 +7461,12 @@
       <c r="X70" s="9"/>
       <c r="Y70" s="9"/>
       <c r="Z70" s="9"/>
-    </row>
-    <row r="71" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA70" s="9"/>
+      <c r="AB70" s="9"/>
+      <c r="AC70" s="9"/>
+      <c r="AD70" s="9"/>
+    </row>
+    <row r="71" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -6993,8 +7491,12 @@
       <c r="X71" s="9"/>
       <c r="Y71" s="9"/>
       <c r="Z71" s="9"/>
-    </row>
-    <row r="72" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA71" s="9"/>
+      <c r="AB71" s="9"/>
+      <c r="AC71" s="9"/>
+      <c r="AD71" s="9"/>
+    </row>
+    <row r="72" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -7019,8 +7521,12 @@
       <c r="X72" s="9"/>
       <c r="Y72" s="9"/>
       <c r="Z72" s="9"/>
-    </row>
-    <row r="73" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA72" s="9"/>
+      <c r="AB72" s="9"/>
+      <c r="AC72" s="9"/>
+      <c r="AD72" s="9"/>
+    </row>
+    <row r="73" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -7045,8 +7551,12 @@
       <c r="X73" s="9"/>
       <c r="Y73" s="9"/>
       <c r="Z73" s="9"/>
-    </row>
-    <row r="74" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA73" s="9"/>
+      <c r="AB73" s="9"/>
+      <c r="AC73" s="9"/>
+      <c r="AD73" s="9"/>
+    </row>
+    <row r="74" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -7071,8 +7581,12 @@
       <c r="X74" s="9"/>
       <c r="Y74" s="9"/>
       <c r="Z74" s="9"/>
-    </row>
-    <row r="75" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA74" s="9"/>
+      <c r="AB74" s="9"/>
+      <c r="AC74" s="9"/>
+      <c r="AD74" s="9"/>
+    </row>
+    <row r="75" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -7097,8 +7611,12 @@
       <c r="X75" s="9"/>
       <c r="Y75" s="9"/>
       <c r="Z75" s="9"/>
-    </row>
-    <row r="76" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA75" s="9"/>
+      <c r="AB75" s="9"/>
+      <c r="AC75" s="9"/>
+      <c r="AD75" s="9"/>
+    </row>
+    <row r="76" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -7123,8 +7641,12 @@
       <c r="X76" s="9"/>
       <c r="Y76" s="9"/>
       <c r="Z76" s="9"/>
-    </row>
-    <row r="77" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA76" s="9"/>
+      <c r="AB76" s="9"/>
+      <c r="AC76" s="9"/>
+      <c r="AD76" s="9"/>
+    </row>
+    <row r="77" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -7149,8 +7671,12 @@
       <c r="X77" s="9"/>
       <c r="Y77" s="9"/>
       <c r="Z77" s="9"/>
-    </row>
-    <row r="78" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA77" s="9"/>
+      <c r="AB77" s="9"/>
+      <c r="AC77" s="9"/>
+      <c r="AD77" s="9"/>
+    </row>
+    <row r="78" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -7175,8 +7701,12 @@
       <c r="X78" s="9"/>
       <c r="Y78" s="9"/>
       <c r="Z78" s="9"/>
-    </row>
-    <row r="79" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA78" s="9"/>
+      <c r="AB78" s="9"/>
+      <c r="AC78" s="9"/>
+      <c r="AD78" s="9"/>
+    </row>
+    <row r="79" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -7201,8 +7731,12 @@
       <c r="X79" s="9"/>
       <c r="Y79" s="9"/>
       <c r="Z79" s="9"/>
-    </row>
-    <row r="80" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA79" s="9"/>
+      <c r="AB79" s="9"/>
+      <c r="AC79" s="9"/>
+      <c r="AD79" s="9"/>
+    </row>
+    <row r="80" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -7227,8 +7761,12 @@
       <c r="X80" s="9"/>
       <c r="Y80" s="9"/>
       <c r="Z80" s="9"/>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA80" s="9"/>
+      <c r="AB80" s="9"/>
+      <c r="AC80" s="9"/>
+      <c r="AD80" s="9"/>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -7253,8 +7791,12 @@
       <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
       <c r="Z81" s="9"/>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA81" s="9"/>
+      <c r="AB81" s="9"/>
+      <c r="AC81" s="9"/>
+      <c r="AD81" s="9"/>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -7279,8 +7821,12 @@
       <c r="X82" s="9"/>
       <c r="Y82" s="9"/>
       <c r="Z82" s="9"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA82" s="9"/>
+      <c r="AB82" s="9"/>
+      <c r="AC82" s="9"/>
+      <c r="AD82" s="9"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -7305,8 +7851,12 @@
       <c r="X83" s="9"/>
       <c r="Y83" s="9"/>
       <c r="Z83" s="9"/>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA83" s="9"/>
+      <c r="AB83" s="9"/>
+      <c r="AC83" s="9"/>
+      <c r="AD83" s="9"/>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -7331,8 +7881,12 @@
       <c r="X84" s="9"/>
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA84" s="9"/>
+      <c r="AB84" s="9"/>
+      <c r="AC84" s="9"/>
+      <c r="AD84" s="9"/>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -7357,8 +7911,12 @@
       <c r="X85" s="9"/>
       <c r="Y85" s="9"/>
       <c r="Z85" s="9"/>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA85" s="9"/>
+      <c r="AB85" s="9"/>
+      <c r="AC85" s="9"/>
+      <c r="AD85" s="9"/>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -7383,8 +7941,12 @@
       <c r="X86" s="9"/>
       <c r="Y86" s="9"/>
       <c r="Z86" s="9"/>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA86" s="9"/>
+      <c r="AB86" s="9"/>
+      <c r="AC86" s="9"/>
+      <c r="AD86" s="9"/>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -7409,8 +7971,12 @@
       <c r="X87" s="9"/>
       <c r="Y87" s="9"/>
       <c r="Z87" s="9"/>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA87" s="9"/>
+      <c r="AB87" s="9"/>
+      <c r="AC87" s="9"/>
+      <c r="AD87" s="9"/>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -7435,8 +8001,12 @@
       <c r="X88" s="9"/>
       <c r="Y88" s="9"/>
       <c r="Z88" s="9"/>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA88" s="9"/>
+      <c r="AB88" s="9"/>
+      <c r="AC88" s="9"/>
+      <c r="AD88" s="9"/>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -7461,8 +8031,12 @@
       <c r="X89" s="9"/>
       <c r="Y89" s="9"/>
       <c r="Z89" s="9"/>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA89" s="9"/>
+      <c r="AB89" s="9"/>
+      <c r="AC89" s="9"/>
+      <c r="AD89" s="9"/>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -7487,8 +8061,12 @@
       <c r="X90" s="9"/>
       <c r="Y90" s="9"/>
       <c r="Z90" s="9"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA90" s="9"/>
+      <c r="AB90" s="9"/>
+      <c r="AC90" s="9"/>
+      <c r="AD90" s="9"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -7513,8 +8091,12 @@
       <c r="X91" s="9"/>
       <c r="Y91" s="9"/>
       <c r="Z91" s="9"/>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA91" s="9"/>
+      <c r="AB91" s="9"/>
+      <c r="AC91" s="9"/>
+      <c r="AD91" s="9"/>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -7539,8 +8121,12 @@
       <c r="X92" s="9"/>
       <c r="Y92" s="9"/>
       <c r="Z92" s="9"/>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA92" s="9"/>
+      <c r="AB92" s="9"/>
+      <c r="AC92" s="9"/>
+      <c r="AD92" s="9"/>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -7565,8 +8151,12 @@
       <c r="X93" s="9"/>
       <c r="Y93" s="9"/>
       <c r="Z93" s="9"/>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA93" s="9"/>
+      <c r="AB93" s="9"/>
+      <c r="AC93" s="9"/>
+      <c r="AD93" s="9"/>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -7591,8 +8181,12 @@
       <c r="X94" s="9"/>
       <c r="Y94" s="9"/>
       <c r="Z94" s="9"/>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA94" s="9"/>
+      <c r="AB94" s="9"/>
+      <c r="AC94" s="9"/>
+      <c r="AD94" s="9"/>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -7617,8 +8211,12 @@
       <c r="X95" s="9"/>
       <c r="Y95" s="9"/>
       <c r="Z95" s="9"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA95" s="9"/>
+      <c r="AB95" s="9"/>
+      <c r="AC95" s="9"/>
+      <c r="AD95" s="9"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -7643,8 +8241,12 @@
       <c r="X96" s="9"/>
       <c r="Y96" s="9"/>
       <c r="Z96" s="9"/>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA96" s="9"/>
+      <c r="AB96" s="9"/>
+      <c r="AC96" s="9"/>
+      <c r="AD96" s="9"/>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -7669,8 +8271,12 @@
       <c r="X97" s="9"/>
       <c r="Y97" s="9"/>
       <c r="Z97" s="9"/>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA97" s="9"/>
+      <c r="AB97" s="9"/>
+      <c r="AC97" s="9"/>
+      <c r="AD97" s="9"/>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -7695,8 +8301,12 @@
       <c r="X98" s="9"/>
       <c r="Y98" s="9"/>
       <c r="Z98" s="9"/>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA98" s="9"/>
+      <c r="AB98" s="9"/>
+      <c r="AC98" s="9"/>
+      <c r="AD98" s="9"/>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -7721,8 +8331,12 @@
       <c r="X99" s="9"/>
       <c r="Y99" s="9"/>
       <c r="Z99" s="9"/>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA99" s="9"/>
+      <c r="AB99" s="9"/>
+      <c r="AC99" s="9"/>
+      <c r="AD99" s="9"/>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -7747,8 +8361,12 @@
       <c r="X100" s="9"/>
       <c r="Y100" s="9"/>
       <c r="Z100" s="9"/>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA100" s="9"/>
+      <c r="AB100" s="9"/>
+      <c r="AC100" s="9"/>
+      <c r="AD100" s="9"/>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -7773,8 +8391,12 @@
       <c r="X101" s="9"/>
       <c r="Y101" s="9"/>
       <c r="Z101" s="9"/>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA101" s="9"/>
+      <c r="AB101" s="9"/>
+      <c r="AC101" s="9"/>
+      <c r="AD101" s="9"/>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -7799,8 +8421,12 @@
       <c r="X102" s="9"/>
       <c r="Y102" s="9"/>
       <c r="Z102" s="9"/>
-    </row>
-    <row r="103" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA102" s="9"/>
+      <c r="AB102" s="9"/>
+      <c r="AC102" s="9"/>
+      <c r="AD102" s="9"/>
+    </row>
+    <row r="103" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -7825,8 +8451,12 @@
       <c r="X103" s="9"/>
       <c r="Y103" s="9"/>
       <c r="Z103" s="9"/>
-    </row>
-    <row r="104" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA103" s="9"/>
+      <c r="AB103" s="9"/>
+      <c r="AC103" s="9"/>
+      <c r="AD103" s="9"/>
+    </row>
+    <row r="104" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -7851,8 +8481,12 @@
       <c r="X104" s="9"/>
       <c r="Y104" s="9"/>
       <c r="Z104" s="9"/>
-    </row>
-    <row r="105" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA104" s="9"/>
+      <c r="AB104" s="9"/>
+      <c r="AC104" s="9"/>
+      <c r="AD104" s="9"/>
+    </row>
+    <row r="105" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -7877,8 +8511,12 @@
       <c r="X105" s="9"/>
       <c r="Y105" s="9"/>
       <c r="Z105" s="9"/>
-    </row>
-    <row r="106" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA105" s="9"/>
+      <c r="AB105" s="9"/>
+      <c r="AC105" s="9"/>
+      <c r="AD105" s="9"/>
+    </row>
+    <row r="106" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -7903,8 +8541,12 @@
       <c r="X106" s="9"/>
       <c r="Y106" s="9"/>
       <c r="Z106" s="9"/>
-    </row>
-    <row r="107" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA106" s="9"/>
+      <c r="AB106" s="9"/>
+      <c r="AC106" s="9"/>
+      <c r="AD106" s="9"/>
+    </row>
+    <row r="107" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -7929,8 +8571,12 @@
       <c r="X107" s="9"/>
       <c r="Y107" s="9"/>
       <c r="Z107" s="9"/>
-    </row>
-    <row r="108" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA107" s="9"/>
+      <c r="AB107" s="9"/>
+      <c r="AC107" s="9"/>
+      <c r="AD107" s="9"/>
+    </row>
+    <row r="108" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -7955,8 +8601,12 @@
       <c r="X108" s="9"/>
       <c r="Y108" s="9"/>
       <c r="Z108" s="9"/>
-    </row>
-    <row r="109" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA108" s="9"/>
+      <c r="AB108" s="9"/>
+      <c r="AC108" s="9"/>
+      <c r="AD108" s="9"/>
+    </row>
+    <row r="109" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -7981,8 +8631,12 @@
       <c r="X109" s="9"/>
       <c r="Y109" s="9"/>
       <c r="Z109" s="9"/>
-    </row>
-    <row r="110" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA109" s="9"/>
+      <c r="AB109" s="9"/>
+      <c r="AC109" s="9"/>
+      <c r="AD109" s="9"/>
+    </row>
+    <row r="110" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -8007,8 +8661,12 @@
       <c r="X110" s="9"/>
       <c r="Y110" s="9"/>
       <c r="Z110" s="9"/>
-    </row>
-    <row r="111" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA110" s="9"/>
+      <c r="AB110" s="9"/>
+      <c r="AC110" s="9"/>
+      <c r="AD110" s="9"/>
+    </row>
+    <row r="111" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -8033,8 +8691,12 @@
       <c r="X111" s="9"/>
       <c r="Y111" s="9"/>
       <c r="Z111" s="9"/>
-    </row>
-    <row r="112" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA111" s="9"/>
+      <c r="AB111" s="9"/>
+      <c r="AC111" s="9"/>
+      <c r="AD111" s="9"/>
+    </row>
+    <row r="112" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -8059,8 +8721,12 @@
       <c r="X112" s="9"/>
       <c r="Y112" s="9"/>
       <c r="Z112" s="9"/>
-    </row>
-    <row r="113" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="9"/>
+      <c r="AC112" s="9"/>
+      <c r="AD112" s="9"/>
+    </row>
+    <row r="113" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -8085,8 +8751,12 @@
       <c r="X113" s="9"/>
       <c r="Y113" s="9"/>
       <c r="Z113" s="9"/>
-    </row>
-    <row r="114" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA113" s="9"/>
+      <c r="AB113" s="9"/>
+      <c r="AC113" s="9"/>
+      <c r="AD113" s="9"/>
+    </row>
+    <row r="114" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -8111,8 +8781,12 @@
       <c r="X114" s="9"/>
       <c r="Y114" s="9"/>
       <c r="Z114" s="9"/>
-    </row>
-    <row r="115" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA114" s="9"/>
+      <c r="AB114" s="9"/>
+      <c r="AC114" s="9"/>
+      <c r="AD114" s="9"/>
+    </row>
+    <row r="115" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -8137,8 +8811,12 @@
       <c r="X115" s="9"/>
       <c r="Y115" s="9"/>
       <c r="Z115" s="9"/>
-    </row>
-    <row r="116" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA115" s="9"/>
+      <c r="AB115" s="9"/>
+      <c r="AC115" s="9"/>
+      <c r="AD115" s="9"/>
+    </row>
+    <row r="116" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -8163,8 +8841,12 @@
       <c r="X116" s="9"/>
       <c r="Y116" s="9"/>
       <c r="Z116" s="9"/>
-    </row>
-    <row r="117" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA116" s="9"/>
+      <c r="AB116" s="9"/>
+      <c r="AC116" s="9"/>
+      <c r="AD116" s="9"/>
+    </row>
+    <row r="117" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -8189,8 +8871,12 @@
       <c r="X117" s="9"/>
       <c r="Y117" s="9"/>
       <c r="Z117" s="9"/>
-    </row>
-    <row r="118" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA117" s="9"/>
+      <c r="AB117" s="9"/>
+      <c r="AC117" s="9"/>
+      <c r="AD117" s="9"/>
+    </row>
+    <row r="118" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -8215,8 +8901,12 @@
       <c r="X118" s="9"/>
       <c r="Y118" s="9"/>
       <c r="Z118" s="9"/>
-    </row>
-    <row r="119" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA118" s="9"/>
+      <c r="AB118" s="9"/>
+      <c r="AC118" s="9"/>
+      <c r="AD118" s="9"/>
+    </row>
+    <row r="119" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -8241,8 +8931,12 @@
       <c r="X119" s="9"/>
       <c r="Y119" s="9"/>
       <c r="Z119" s="9"/>
-    </row>
-    <row r="120" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA119" s="9"/>
+      <c r="AB119" s="9"/>
+      <c r="AC119" s="9"/>
+      <c r="AD119" s="9"/>
+    </row>
+    <row r="120" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -8267,8 +8961,12 @@
       <c r="X120" s="9"/>
       <c r="Y120" s="9"/>
       <c r="Z120" s="9"/>
-    </row>
-    <row r="121" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA120" s="9"/>
+      <c r="AB120" s="9"/>
+      <c r="AC120" s="9"/>
+      <c r="AD120" s="9"/>
+    </row>
+    <row r="121" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -8293,8 +8991,12 @@
       <c r="X121" s="9"/>
       <c r="Y121" s="9"/>
       <c r="Z121" s="9"/>
-    </row>
-    <row r="122" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+      <c r="AD121" s="9"/>
+    </row>
+    <row r="122" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -8319,8 +9021,12 @@
       <c r="X122" s="9"/>
       <c r="Y122" s="9"/>
       <c r="Z122" s="9"/>
-    </row>
-    <row r="123" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA122" s="9"/>
+      <c r="AB122" s="9"/>
+      <c r="AC122" s="9"/>
+      <c r="AD122" s="9"/>
+    </row>
+    <row r="123" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -8345,8 +9051,12 @@
       <c r="X123" s="9"/>
       <c r="Y123" s="9"/>
       <c r="Z123" s="9"/>
-    </row>
-    <row r="124" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="9"/>
+      <c r="AD123" s="9"/>
+    </row>
+    <row r="124" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -8371,8 +9081,12 @@
       <c r="X124" s="9"/>
       <c r="Y124" s="9"/>
       <c r="Z124" s="9"/>
-    </row>
-    <row r="125" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA124" s="9"/>
+      <c r="AB124" s="9"/>
+      <c r="AC124" s="9"/>
+      <c r="AD124" s="9"/>
+    </row>
+    <row r="125" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -8397,8 +9111,12 @@
       <c r="X125" s="9"/>
       <c r="Y125" s="9"/>
       <c r="Z125" s="9"/>
-    </row>
-    <row r="126" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA125" s="9"/>
+      <c r="AB125" s="9"/>
+      <c r="AC125" s="9"/>
+      <c r="AD125" s="9"/>
+    </row>
+    <row r="126" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -8423,8 +9141,12 @@
       <c r="X126" s="9"/>
       <c r="Y126" s="9"/>
       <c r="Z126" s="9"/>
-    </row>
-    <row r="127" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA126" s="9"/>
+      <c r="AB126" s="9"/>
+      <c r="AC126" s="9"/>
+      <c r="AD126" s="9"/>
+    </row>
+    <row r="127" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -8449,8 +9171,12 @@
       <c r="X127" s="9"/>
       <c r="Y127" s="9"/>
       <c r="Z127" s="9"/>
-    </row>
-    <row r="128" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA127" s="9"/>
+      <c r="AB127" s="9"/>
+      <c r="AC127" s="9"/>
+      <c r="AD127" s="9"/>
+    </row>
+    <row r="128" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -8475,8 +9201,12 @@
       <c r="X128" s="9"/>
       <c r="Y128" s="9"/>
       <c r="Z128" s="9"/>
-    </row>
-    <row r="129" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA128" s="9"/>
+      <c r="AB128" s="9"/>
+      <c r="AC128" s="9"/>
+      <c r="AD128" s="9"/>
+    </row>
+    <row r="129" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -8501,8 +9231,12 @@
       <c r="X129" s="9"/>
       <c r="Y129" s="9"/>
       <c r="Z129" s="9"/>
-    </row>
-    <row r="130" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA129" s="9"/>
+      <c r="AB129" s="9"/>
+      <c r="AC129" s="9"/>
+      <c r="AD129" s="9"/>
+    </row>
+    <row r="130" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -8527,8 +9261,12 @@
       <c r="X130" s="9"/>
       <c r="Y130" s="9"/>
       <c r="Z130" s="9"/>
-    </row>
-    <row r="131" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA130" s="9"/>
+      <c r="AB130" s="9"/>
+      <c r="AC130" s="9"/>
+      <c r="AD130" s="9"/>
+    </row>
+    <row r="131" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -8553,8 +9291,12 @@
       <c r="X131" s="9"/>
       <c r="Y131" s="9"/>
       <c r="Z131" s="9"/>
-    </row>
-    <row r="132" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA131" s="9"/>
+      <c r="AB131" s="9"/>
+      <c r="AC131" s="9"/>
+      <c r="AD131" s="9"/>
+    </row>
+    <row r="132" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -8579,8 +9321,12 @@
       <c r="X132" s="9"/>
       <c r="Y132" s="9"/>
       <c r="Z132" s="9"/>
-    </row>
-    <row r="133" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA132" s="9"/>
+      <c r="AB132" s="9"/>
+      <c r="AC132" s="9"/>
+      <c r="AD132" s="9"/>
+    </row>
+    <row r="133" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -8605,8 +9351,12 @@
       <c r="X133" s="9"/>
       <c r="Y133" s="9"/>
       <c r="Z133" s="9"/>
-    </row>
-    <row r="134" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA133" s="9"/>
+      <c r="AB133" s="9"/>
+      <c r="AC133" s="9"/>
+      <c r="AD133" s="9"/>
+    </row>
+    <row r="134" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -8631,8 +9381,12 @@
       <c r="X134" s="9"/>
       <c r="Y134" s="9"/>
       <c r="Z134" s="9"/>
-    </row>
-    <row r="135" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA134" s="9"/>
+      <c r="AB134" s="9"/>
+      <c r="AC134" s="9"/>
+      <c r="AD134" s="9"/>
+    </row>
+    <row r="135" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -8657,8 +9411,12 @@
       <c r="X135" s="9"/>
       <c r="Y135" s="9"/>
       <c r="Z135" s="9"/>
-    </row>
-    <row r="136" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA135" s="9"/>
+      <c r="AB135" s="9"/>
+      <c r="AC135" s="9"/>
+      <c r="AD135" s="9"/>
+    </row>
+    <row r="136" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -8683,8 +9441,12 @@
       <c r="X136" s="9"/>
       <c r="Y136" s="9"/>
       <c r="Z136" s="9"/>
-    </row>
-    <row r="137" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA136" s="9"/>
+      <c r="AB136" s="9"/>
+      <c r="AC136" s="9"/>
+      <c r="AD136" s="9"/>
+    </row>
+    <row r="137" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -8709,8 +9471,12 @@
       <c r="X137" s="9"/>
       <c r="Y137" s="9"/>
       <c r="Z137" s="9"/>
-    </row>
-    <row r="138" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA137" s="9"/>
+      <c r="AB137" s="9"/>
+      <c r="AC137" s="9"/>
+      <c r="AD137" s="9"/>
+    </row>
+    <row r="138" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -8735,8 +9501,12 @@
       <c r="X138" s="9"/>
       <c r="Y138" s="9"/>
       <c r="Z138" s="9"/>
-    </row>
-    <row r="139" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA138" s="9"/>
+      <c r="AB138" s="9"/>
+      <c r="AC138" s="9"/>
+      <c r="AD138" s="9"/>
+    </row>
+    <row r="139" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -8761,8 +9531,12 @@
       <c r="X139" s="9"/>
       <c r="Y139" s="9"/>
       <c r="Z139" s="9"/>
-    </row>
-    <row r="140" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA139" s="9"/>
+      <c r="AB139" s="9"/>
+      <c r="AC139" s="9"/>
+      <c r="AD139" s="9"/>
+    </row>
+    <row r="140" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -8787,8 +9561,12 @@
       <c r="X140" s="9"/>
       <c r="Y140" s="9"/>
       <c r="Z140" s="9"/>
-    </row>
-    <row r="141" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA140" s="9"/>
+      <c r="AB140" s="9"/>
+      <c r="AC140" s="9"/>
+      <c r="AD140" s="9"/>
+    </row>
+    <row r="141" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -8813,8 +9591,12 @@
       <c r="X141" s="9"/>
       <c r="Y141" s="9"/>
       <c r="Z141" s="9"/>
-    </row>
-    <row r="142" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA141" s="9"/>
+      <c r="AB141" s="9"/>
+      <c r="AC141" s="9"/>
+      <c r="AD141" s="9"/>
+    </row>
+    <row r="142" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -8839,8 +9621,12 @@
       <c r="X142" s="9"/>
       <c r="Y142" s="9"/>
       <c r="Z142" s="9"/>
-    </row>
-    <row r="143" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA142" s="9"/>
+      <c r="AB142" s="9"/>
+      <c r="AC142" s="9"/>
+      <c r="AD142" s="9"/>
+    </row>
+    <row r="143" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -8865,8 +9651,12 @@
       <c r="X143" s="9"/>
       <c r="Y143" s="9"/>
       <c r="Z143" s="9"/>
-    </row>
-    <row r="144" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA143" s="9"/>
+      <c r="AB143" s="9"/>
+      <c r="AC143" s="9"/>
+      <c r="AD143" s="9"/>
+    </row>
+    <row r="144" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -8891,8 +9681,12 @@
       <c r="X144" s="9"/>
       <c r="Y144" s="9"/>
       <c r="Z144" s="9"/>
-    </row>
-    <row r="145" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA144" s="9"/>
+      <c r="AB144" s="9"/>
+      <c r="AC144" s="9"/>
+      <c r="AD144" s="9"/>
+    </row>
+    <row r="145" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -8917,8 +9711,12 @@
       <c r="X145" s="9"/>
       <c r="Y145" s="9"/>
       <c r="Z145" s="9"/>
-    </row>
-    <row r="146" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA145" s="9"/>
+      <c r="AB145" s="9"/>
+      <c r="AC145" s="9"/>
+      <c r="AD145" s="9"/>
+    </row>
+    <row r="146" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -8943,8 +9741,12 @@
       <c r="X146" s="9"/>
       <c r="Y146" s="9"/>
       <c r="Z146" s="9"/>
-    </row>
-    <row r="147" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA146" s="9"/>
+      <c r="AB146" s="9"/>
+      <c r="AC146" s="9"/>
+      <c r="AD146" s="9"/>
+    </row>
+    <row r="147" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -8969,8 +9771,12 @@
       <c r="X147" s="9"/>
       <c r="Y147" s="9"/>
       <c r="Z147" s="9"/>
-    </row>
-    <row r="148" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA147" s="9"/>
+      <c r="AB147" s="9"/>
+      <c r="AC147" s="9"/>
+      <c r="AD147" s="9"/>
+    </row>
+    <row r="148" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -8995,8 +9801,12 @@
       <c r="X148" s="9"/>
       <c r="Y148" s="9"/>
       <c r="Z148" s="9"/>
-    </row>
-    <row r="149" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA148" s="9"/>
+      <c r="AB148" s="9"/>
+      <c r="AC148" s="9"/>
+      <c r="AD148" s="9"/>
+    </row>
+    <row r="149" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -9021,8 +9831,12 @@
       <c r="X149" s="9"/>
       <c r="Y149" s="9"/>
       <c r="Z149" s="9"/>
-    </row>
-    <row r="150" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA149" s="9"/>
+      <c r="AB149" s="9"/>
+      <c r="AC149" s="9"/>
+      <c r="AD149" s="9"/>
+    </row>
+    <row r="150" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -9047,8 +9861,12 @@
       <c r="X150" s="9"/>
       <c r="Y150" s="9"/>
       <c r="Z150" s="9"/>
-    </row>
-    <row r="151" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA150" s="9"/>
+      <c r="AB150" s="9"/>
+      <c r="AC150" s="9"/>
+      <c r="AD150" s="9"/>
+    </row>
+    <row r="151" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -9073,8 +9891,12 @@
       <c r="X151" s="9"/>
       <c r="Y151" s="9"/>
       <c r="Z151" s="9"/>
-    </row>
-    <row r="152" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA151" s="9"/>
+      <c r="AB151" s="9"/>
+      <c r="AC151" s="9"/>
+      <c r="AD151" s="9"/>
+    </row>
+    <row r="152" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -9099,8 +9921,12 @@
       <c r="X152" s="9"/>
       <c r="Y152" s="9"/>
       <c r="Z152" s="9"/>
-    </row>
-    <row r="153" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA152" s="9"/>
+      <c r="AB152" s="9"/>
+      <c r="AC152" s="9"/>
+      <c r="AD152" s="9"/>
+    </row>
+    <row r="153" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -9125,8 +9951,12 @@
       <c r="X153" s="9"/>
       <c r="Y153" s="9"/>
       <c r="Z153" s="9"/>
-    </row>
-    <row r="154" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA153" s="9"/>
+      <c r="AB153" s="9"/>
+      <c r="AC153" s="9"/>
+      <c r="AD153" s="9"/>
+    </row>
+    <row r="154" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -9151,8 +9981,12 @@
       <c r="X154" s="9"/>
       <c r="Y154" s="9"/>
       <c r="Z154" s="9"/>
-    </row>
-    <row r="155" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA154" s="9"/>
+      <c r="AB154" s="9"/>
+      <c r="AC154" s="9"/>
+      <c r="AD154" s="9"/>
+    </row>
+    <row r="155" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -9177,8 +10011,12 @@
       <c r="X155" s="9"/>
       <c r="Y155" s="9"/>
       <c r="Z155" s="9"/>
-    </row>
-    <row r="156" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA155" s="9"/>
+      <c r="AB155" s="9"/>
+      <c r="AC155" s="9"/>
+      <c r="AD155" s="9"/>
+    </row>
+    <row r="156" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -9203,8 +10041,12 @@
       <c r="X156" s="9"/>
       <c r="Y156" s="9"/>
       <c r="Z156" s="9"/>
-    </row>
-    <row r="157" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA156" s="9"/>
+      <c r="AB156" s="9"/>
+      <c r="AC156" s="9"/>
+      <c r="AD156" s="9"/>
+    </row>
+    <row r="157" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -9229,8 +10071,12 @@
       <c r="X157" s="9"/>
       <c r="Y157" s="9"/>
       <c r="Z157" s="9"/>
-    </row>
-    <row r="158" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA157" s="9"/>
+      <c r="AB157" s="9"/>
+      <c r="AC157" s="9"/>
+      <c r="AD157" s="9"/>
+    </row>
+    <row r="158" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -9255,8 +10101,12 @@
       <c r="X158" s="9"/>
       <c r="Y158" s="9"/>
       <c r="Z158" s="9"/>
-    </row>
-    <row r="159" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA158" s="9"/>
+      <c r="AB158" s="9"/>
+      <c r="AC158" s="9"/>
+      <c r="AD158" s="9"/>
+    </row>
+    <row r="159" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -9281,8 +10131,12 @@
       <c r="X159" s="9"/>
       <c r="Y159" s="9"/>
       <c r="Z159" s="9"/>
-    </row>
-    <row r="160" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA159" s="9"/>
+      <c r="AB159" s="9"/>
+      <c r="AC159" s="9"/>
+      <c r="AD159" s="9"/>
+    </row>
+    <row r="160" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -9307,8 +10161,12 @@
       <c r="X160" s="9"/>
       <c r="Y160" s="9"/>
       <c r="Z160" s="9"/>
-    </row>
-    <row r="161" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA160" s="9"/>
+      <c r="AB160" s="9"/>
+      <c r="AC160" s="9"/>
+      <c r="AD160" s="9"/>
+    </row>
+    <row r="161" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -9333,8 +10191,12 @@
       <c r="X161" s="9"/>
       <c r="Y161" s="9"/>
       <c r="Z161" s="9"/>
-    </row>
-    <row r="162" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA161" s="9"/>
+      <c r="AB161" s="9"/>
+      <c r="AC161" s="9"/>
+      <c r="AD161" s="9"/>
+    </row>
+    <row r="162" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -9359,8 +10221,12 @@
       <c r="X162" s="9"/>
       <c r="Y162" s="9"/>
       <c r="Z162" s="9"/>
-    </row>
-    <row r="163" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA162" s="9"/>
+      <c r="AB162" s="9"/>
+      <c r="AC162" s="9"/>
+      <c r="AD162" s="9"/>
+    </row>
+    <row r="163" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -9385,8 +10251,12 @@
       <c r="X163" s="9"/>
       <c r="Y163" s="9"/>
       <c r="Z163" s="9"/>
-    </row>
-    <row r="164" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA163" s="9"/>
+      <c r="AB163" s="9"/>
+      <c r="AC163" s="9"/>
+      <c r="AD163" s="9"/>
+    </row>
+    <row r="164" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -9411,8 +10281,12 @@
       <c r="X164" s="9"/>
       <c r="Y164" s="9"/>
       <c r="Z164" s="9"/>
-    </row>
-    <row r="165" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA164" s="9"/>
+      <c r="AB164" s="9"/>
+      <c r="AC164" s="9"/>
+      <c r="AD164" s="9"/>
+    </row>
+    <row r="165" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -9437,8 +10311,12 @@
       <c r="X165" s="9"/>
       <c r="Y165" s="9"/>
       <c r="Z165" s="9"/>
-    </row>
-    <row r="166" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA165" s="9"/>
+      <c r="AB165" s="9"/>
+      <c r="AC165" s="9"/>
+      <c r="AD165" s="9"/>
+    </row>
+    <row r="166" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -9463,8 +10341,12 @@
       <c r="X166" s="9"/>
       <c r="Y166" s="9"/>
       <c r="Z166" s="9"/>
-    </row>
-    <row r="167" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA166" s="9"/>
+      <c r="AB166" s="9"/>
+      <c r="AC166" s="9"/>
+      <c r="AD166" s="9"/>
+    </row>
+    <row r="167" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -9489,8 +10371,12 @@
       <c r="X167" s="9"/>
       <c r="Y167" s="9"/>
       <c r="Z167" s="9"/>
-    </row>
-    <row r="168" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA167" s="9"/>
+      <c r="AB167" s="9"/>
+      <c r="AC167" s="9"/>
+      <c r="AD167" s="9"/>
+    </row>
+    <row r="168" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -9515,8 +10401,12 @@
       <c r="X168" s="9"/>
       <c r="Y168" s="9"/>
       <c r="Z168" s="9"/>
-    </row>
-    <row r="169" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA168" s="9"/>
+      <c r="AB168" s="9"/>
+      <c r="AC168" s="9"/>
+      <c r="AD168" s="9"/>
+    </row>
+    <row r="169" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -9541,8 +10431,12 @@
       <c r="X169" s="9"/>
       <c r="Y169" s="9"/>
       <c r="Z169" s="9"/>
-    </row>
-    <row r="170" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA169" s="9"/>
+      <c r="AB169" s="9"/>
+      <c r="AC169" s="9"/>
+      <c r="AD169" s="9"/>
+    </row>
+    <row r="170" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -9567,8 +10461,12 @@
       <c r="X170" s="9"/>
       <c r="Y170" s="9"/>
       <c r="Z170" s="9"/>
-    </row>
-    <row r="171" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA170" s="9"/>
+      <c r="AB170" s="9"/>
+      <c r="AC170" s="9"/>
+      <c r="AD170" s="9"/>
+    </row>
+    <row r="171" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -9593,8 +10491,12 @@
       <c r="X171" s="9"/>
       <c r="Y171" s="9"/>
       <c r="Z171" s="9"/>
-    </row>
-    <row r="172" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA171" s="9"/>
+      <c r="AB171" s="9"/>
+      <c r="AC171" s="9"/>
+      <c r="AD171" s="9"/>
+    </row>
+    <row r="172" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -9619,8 +10521,12 @@
       <c r="X172" s="9"/>
       <c r="Y172" s="9"/>
       <c r="Z172" s="9"/>
-    </row>
-    <row r="173" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA172" s="9"/>
+      <c r="AB172" s="9"/>
+      <c r="AC172" s="9"/>
+      <c r="AD172" s="9"/>
+    </row>
+    <row r="173" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -9645,8 +10551,12 @@
       <c r="X173" s="9"/>
       <c r="Y173" s="9"/>
       <c r="Z173" s="9"/>
-    </row>
-    <row r="174" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA173" s="9"/>
+      <c r="AB173" s="9"/>
+      <c r="AC173" s="9"/>
+      <c r="AD173" s="9"/>
+    </row>
+    <row r="174" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -9671,8 +10581,12 @@
       <c r="X174" s="9"/>
       <c r="Y174" s="9"/>
       <c r="Z174" s="9"/>
-    </row>
-    <row r="175" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA174" s="9"/>
+      <c r="AB174" s="9"/>
+      <c r="AC174" s="9"/>
+      <c r="AD174" s="9"/>
+    </row>
+    <row r="175" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -9697,8 +10611,12 @@
       <c r="X175" s="9"/>
       <c r="Y175" s="9"/>
       <c r="Z175" s="9"/>
-    </row>
-    <row r="176" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA175" s="9"/>
+      <c r="AB175" s="9"/>
+      <c r="AC175" s="9"/>
+      <c r="AD175" s="9"/>
+    </row>
+    <row r="176" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -9723,8 +10641,12 @@
       <c r="X176" s="9"/>
       <c r="Y176" s="9"/>
       <c r="Z176" s="9"/>
-    </row>
-    <row r="177" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA176" s="9"/>
+      <c r="AB176" s="9"/>
+      <c r="AC176" s="9"/>
+      <c r="AD176" s="9"/>
+    </row>
+    <row r="177" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -9749,8 +10671,12 @@
       <c r="X177" s="9"/>
       <c r="Y177" s="9"/>
       <c r="Z177" s="9"/>
-    </row>
-    <row r="178" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA177" s="9"/>
+      <c r="AB177" s="9"/>
+      <c r="AC177" s="9"/>
+      <c r="AD177" s="9"/>
+    </row>
+    <row r="178" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -9775,8 +10701,12 @@
       <c r="X178" s="9"/>
       <c r="Y178" s="9"/>
       <c r="Z178" s="9"/>
-    </row>
-    <row r="179" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA178" s="9"/>
+      <c r="AB178" s="9"/>
+      <c r="AC178" s="9"/>
+      <c r="AD178" s="9"/>
+    </row>
+    <row r="179" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -9801,8 +10731,12 @@
       <c r="X179" s="9"/>
       <c r="Y179" s="9"/>
       <c r="Z179" s="9"/>
-    </row>
-    <row r="180" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA179" s="9"/>
+      <c r="AB179" s="9"/>
+      <c r="AC179" s="9"/>
+      <c r="AD179" s="9"/>
+    </row>
+    <row r="180" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -9827,8 +10761,12 @@
       <c r="X180" s="9"/>
       <c r="Y180" s="9"/>
       <c r="Z180" s="9"/>
-    </row>
-    <row r="181" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA180" s="9"/>
+      <c r="AB180" s="9"/>
+      <c r="AC180" s="9"/>
+      <c r="AD180" s="9"/>
+    </row>
+    <row r="181" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -9853,8 +10791,12 @@
       <c r="X181" s="9"/>
       <c r="Y181" s="9"/>
       <c r="Z181" s="9"/>
-    </row>
-    <row r="182" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA181" s="9"/>
+      <c r="AB181" s="9"/>
+      <c r="AC181" s="9"/>
+      <c r="AD181" s="9"/>
+    </row>
+    <row r="182" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -9879,8 +10821,12 @@
       <c r="X182" s="9"/>
       <c r="Y182" s="9"/>
       <c r="Z182" s="9"/>
-    </row>
-    <row r="183" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA182" s="9"/>
+      <c r="AB182" s="9"/>
+      <c r="AC182" s="9"/>
+      <c r="AD182" s="9"/>
+    </row>
+    <row r="183" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -9905,8 +10851,12 @@
       <c r="X183" s="9"/>
       <c r="Y183" s="9"/>
       <c r="Z183" s="9"/>
-    </row>
-    <row r="184" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA183" s="9"/>
+      <c r="AB183" s="9"/>
+      <c r="AC183" s="9"/>
+      <c r="AD183" s="9"/>
+    </row>
+    <row r="184" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -9931,8 +10881,12 @@
       <c r="X184" s="9"/>
       <c r="Y184" s="9"/>
       <c r="Z184" s="9"/>
-    </row>
-    <row r="185" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA184" s="9"/>
+      <c r="AB184" s="9"/>
+      <c r="AC184" s="9"/>
+      <c r="AD184" s="9"/>
+    </row>
+    <row r="185" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -9957,8 +10911,12 @@
       <c r="X185" s="9"/>
       <c r="Y185" s="9"/>
       <c r="Z185" s="9"/>
-    </row>
-    <row r="186" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA185" s="9"/>
+      <c r="AB185" s="9"/>
+      <c r="AC185" s="9"/>
+      <c r="AD185" s="9"/>
+    </row>
+    <row r="186" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -9983,8 +10941,12 @@
       <c r="X186" s="9"/>
       <c r="Y186" s="9"/>
       <c r="Z186" s="9"/>
-    </row>
-    <row r="187" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA186" s="9"/>
+      <c r="AB186" s="9"/>
+      <c r="AC186" s="9"/>
+      <c r="AD186" s="9"/>
+    </row>
+    <row r="187" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -10009,8 +10971,12 @@
       <c r="X187" s="9"/>
       <c r="Y187" s="9"/>
       <c r="Z187" s="9"/>
-    </row>
-    <row r="188" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA187" s="9"/>
+      <c r="AB187" s="9"/>
+      <c r="AC187" s="9"/>
+      <c r="AD187" s="9"/>
+    </row>
+    <row r="188" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -10035,8 +11001,12 @@
       <c r="X188" s="9"/>
       <c r="Y188" s="9"/>
       <c r="Z188" s="9"/>
-    </row>
-    <row r="189" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA188" s="9"/>
+      <c r="AB188" s="9"/>
+      <c r="AC188" s="9"/>
+      <c r="AD188" s="9"/>
+    </row>
+    <row r="189" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -10061,8 +11031,12 @@
       <c r="X189" s="9"/>
       <c r="Y189" s="9"/>
       <c r="Z189" s="9"/>
-    </row>
-    <row r="190" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA189" s="9"/>
+      <c r="AB189" s="9"/>
+      <c r="AC189" s="9"/>
+      <c r="AD189" s="9"/>
+    </row>
+    <row r="190" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -10087,8 +11061,12 @@
       <c r="X190" s="9"/>
       <c r="Y190" s="9"/>
       <c r="Z190" s="9"/>
-    </row>
-    <row r="191" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA190" s="9"/>
+      <c r="AB190" s="9"/>
+      <c r="AC190" s="9"/>
+      <c r="AD190" s="9"/>
+    </row>
+    <row r="191" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -10113,8 +11091,12 @@
       <c r="X191" s="9"/>
       <c r="Y191" s="9"/>
       <c r="Z191" s="9"/>
-    </row>
-    <row r="192" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA191" s="9"/>
+      <c r="AB191" s="9"/>
+      <c r="AC191" s="9"/>
+      <c r="AD191" s="9"/>
+    </row>
+    <row r="192" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -10139,8 +11121,12 @@
       <c r="X192" s="9"/>
       <c r="Y192" s="9"/>
       <c r="Z192" s="9"/>
-    </row>
-    <row r="193" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA192" s="9"/>
+      <c r="AB192" s="9"/>
+      <c r="AC192" s="9"/>
+      <c r="AD192" s="9"/>
+    </row>
+    <row r="193" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -10165,8 +11151,12 @@
       <c r="X193" s="9"/>
       <c r="Y193" s="9"/>
       <c r="Z193" s="9"/>
-    </row>
-    <row r="194" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA193" s="9"/>
+      <c r="AB193" s="9"/>
+      <c r="AC193" s="9"/>
+      <c r="AD193" s="9"/>
+    </row>
+    <row r="194" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -10191,8 +11181,12 @@
       <c r="X194" s="9"/>
       <c r="Y194" s="9"/>
       <c r="Z194" s="9"/>
-    </row>
-    <row r="195" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA194" s="9"/>
+      <c r="AB194" s="9"/>
+      <c r="AC194" s="9"/>
+      <c r="AD194" s="9"/>
+    </row>
+    <row r="195" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -10217,8 +11211,12 @@
       <c r="X195" s="9"/>
       <c r="Y195" s="9"/>
       <c r="Z195" s="9"/>
-    </row>
-    <row r="196" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA195" s="9"/>
+      <c r="AB195" s="9"/>
+      <c r="AC195" s="9"/>
+      <c r="AD195" s="9"/>
+    </row>
+    <row r="196" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -10243,8 +11241,12 @@
       <c r="X196" s="9"/>
       <c r="Y196" s="9"/>
       <c r="Z196" s="9"/>
-    </row>
-    <row r="197" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA196" s="9"/>
+      <c r="AB196" s="9"/>
+      <c r="AC196" s="9"/>
+      <c r="AD196" s="9"/>
+    </row>
+    <row r="197" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -10269,8 +11271,12 @@
       <c r="X197" s="9"/>
       <c r="Y197" s="9"/>
       <c r="Z197" s="9"/>
-    </row>
-    <row r="198" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA197" s="9"/>
+      <c r="AB197" s="9"/>
+      <c r="AC197" s="9"/>
+      <c r="AD197" s="9"/>
+    </row>
+    <row r="198" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -10295,8 +11301,12 @@
       <c r="X198" s="9"/>
       <c r="Y198" s="9"/>
       <c r="Z198" s="9"/>
-    </row>
-    <row r="199" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA198" s="9"/>
+      <c r="AB198" s="9"/>
+      <c r="AC198" s="9"/>
+      <c r="AD198" s="9"/>
+    </row>
+    <row r="199" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -10321,8 +11331,12 @@
       <c r="X199" s="9"/>
       <c r="Y199" s="9"/>
       <c r="Z199" s="9"/>
-    </row>
-    <row r="200" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="AA199" s="9"/>
+      <c r="AB199" s="9"/>
+      <c r="AC199" s="9"/>
+      <c r="AD199" s="9"/>
+    </row>
+    <row r="200" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -10347,25 +11361,26 @@
       <c r="X200" s="9"/>
       <c r="Y200" s="9"/>
       <c r="Z200" s="9"/>
+      <c r="AA200" s="9"/>
+      <c r="AB200" s="9"/>
+      <c r="AC200" s="9"/>
+      <c r="AD200" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A2:AD200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
-    <mergeCell ref="P1:Z1"/>
+    <mergeCell ref="P1:AC1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:AZ200">
-    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
+  <conditionalFormatting sqref="C3:AD200">
+    <cfRule type="expression" dxfId="2" priority="13" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="14" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
-      <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cert_tracker/Contractor Certifications Tracker Demo.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8882C1C4-7586-47DE-9B4C-C72CFBF891C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17EC675-E6A9-4B28-872F-B7A97E4AB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Tracker" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Tracker!$A$2:$AD$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Tracker!$A$2:$AF$200</definedName>
     <definedName name="ContractorOption" comment="=Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;&quot;&quot;),ROW(Workers!$B:$B)))">Workers!$B$2:INDEX(Workers!$B:$B,LOOKUP(2,1/(Workers!$B:$B&lt;&gt;""),ROW(Workers!$B:$B)))</definedName>
     <definedName name="JobTitleOptions">Workers!$C$2:INDEX(Workers!$C:$C,LOOKUP(2,1/(Workers!$C:$C&lt;&gt;""),ROW(Workers!$C:$C)))</definedName>
   </definedNames>
@@ -43,639 +43,642 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="212">
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Validity (years, 0=none)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Protección Contra Caídas</t>
+  </si>
+  <si>
+    <t>HSE Required</t>
+  </si>
+  <si>
+    <t>Flama Expuesta</t>
+  </si>
+  <si>
+    <t>Espacios Confinados</t>
+  </si>
+  <si>
+    <t>Manejo de Equipo Motorizado</t>
+  </si>
+  <si>
+    <t>Excavación o Zanja</t>
+  </si>
+  <si>
+    <t>Manejo de Tijeras (Scissor Lift)</t>
+  </si>
+  <si>
+    <t>Seguridad Eléctrica</t>
+  </si>
+  <si>
+    <t>Lockout</t>
+  </si>
+  <si>
+    <t>Manejo de Grúas</t>
+  </si>
+  <si>
+    <t>Escaleras</t>
+  </si>
+  <si>
+    <t>Andamios</t>
+  </si>
+  <si>
+    <t>Trabajos con Plomo o Asbesto</t>
+  </si>
+  <si>
+    <t>Comunicación de Riesgos</t>
+  </si>
+  <si>
+    <t>Inducción Jacobs/Lilly</t>
+  </si>
+  <si>
+    <t>Additional Training</t>
+  </si>
+  <si>
+    <t>OSHA 40Hr HAZWOPER</t>
+  </si>
+  <si>
+    <t>OSHA 8Hr Refresher</t>
+  </si>
+  <si>
+    <t>Drilling Safety</t>
+  </si>
+  <si>
+    <t>Utility Locating</t>
+  </si>
+  <si>
+    <t>OSHA 10</t>
+  </si>
+  <si>
+    <t>OSHA 30</t>
+  </si>
+  <si>
+    <t>Rebar Safety</t>
+  </si>
+  <si>
+    <t>Formwork &amp; Shoring</t>
+  </si>
+  <si>
+    <t>Silica Exposure</t>
+  </si>
+  <si>
+    <t>Concrete &amp; Masonry</t>
+  </si>
+  <si>
+    <t>Equipment Training</t>
+  </si>
+  <si>
+    <t>OSHA 30 501</t>
+  </si>
+  <si>
+    <t>OSHA 30 511</t>
+  </si>
+  <si>
+    <t>Estamos mas que bien</t>
+  </si>
+  <si>
+    <t>Contractor Certifications Tracker</t>
+  </si>
+  <si>
+    <t>How to use this workbook</t>
+  </si>
+  <si>
+    <t>1. Add new contractors on the Contractors tab.</t>
+  </si>
+  <si>
+    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
+  </si>
+  <si>
+    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
+  </si>
+  <si>
+    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
+  </si>
+  <si>
+    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
+  </si>
+  <si>
+    <t>Color coding on the Tracker</t>
+  </si>
+  <si>
+    <t>• Red cell     = certification missing (empty)</t>
+  </si>
+  <si>
+    <t>• Yellow cell  = completed, expiring within 60 days</t>
+  </si>
+  <si>
+    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
+  </si>
+  <si>
+    <t>• Green cell   = current</t>
+  </si>
+  <si>
+    <t>Sharing with peers</t>
+  </si>
+  <si>
+    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
+  </si>
+  <si>
+    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
+  </si>
+  <si>
+    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
+  </si>
+  <si>
+    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
+  </si>
+  <si>
+    <t>Contractor Certifications Dashboard</t>
+  </si>
+  <si>
+    <t>Total Contractors</t>
+  </si>
+  <si>
+    <t>Total Workers</t>
+  </si>
+  <si>
+    <t>Active Workers</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Compliance by Certification</t>
+  </si>
+  <si>
+    <t>% Complete</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>Contractor Name</t>
+  </si>
+  <si>
+    <t>Primary Contact</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Workers (count)</t>
+  </si>
+  <si>
+    <t>Stonewall Drilling Services, LLC</t>
+  </si>
+  <si>
+    <t>Juan Pérez Vázquez</t>
+  </si>
+  <si>
+    <t>Drilling / Geotechnical</t>
+  </si>
+  <si>
+    <t>Atlas Concrete Works, Inc.</t>
+  </si>
+  <si>
+    <t>Carla M. Santos Vega</t>
+  </si>
+  <si>
+    <t>Concrete &amp; Foundation</t>
+  </si>
+  <si>
+    <t>PowerLine Electric Corp.</t>
+  </si>
+  <si>
+    <t>Miguel Torres Ramos</t>
+  </si>
+  <si>
+    <t>Electrical &amp; Instrumentation</t>
+  </si>
+  <si>
+    <t>SafePath Excavation, Co.</t>
+  </si>
+  <si>
+    <t>Ana L. Reyes Díaz</t>
+  </si>
+  <si>
+    <t>Excavation &amp; Earthworks</t>
+  </si>
+  <si>
+    <t>SkyHigh Scaffolding Solutions</t>
+  </si>
+  <si>
+    <t>Roberto Díaz Cruz</t>
+  </si>
+  <si>
+    <t>Scaffolding / Access Systems</t>
+  </si>
+  <si>
+    <t>Atlantic Safety Builders, LLC</t>
+  </si>
+  <si>
+    <t>Maria Santos</t>
+  </si>
+  <si>
+    <t>General Construction</t>
+  </si>
+  <si>
+    <t>Demo contractor</t>
+  </si>
+  <si>
+    <t>North Shore Mechanical, Inc.</t>
+  </si>
+  <si>
+    <t>Carlos Rivera</t>
+  </si>
+  <si>
+    <t>Mechanical / Utilities</t>
+  </si>
+  <si>
+    <t>Caribbean Concrete Works</t>
+  </si>
+  <si>
+    <t>Andrea Cruz</t>
+  </si>
+  <si>
+    <t>Concrete and Masonry</t>
+  </si>
+  <si>
+    <t>IronCore Contractors</t>
+  </si>
+  <si>
+    <t>Daniel Perez</t>
+  </si>
+  <si>
+    <t>Structural Steel</t>
+  </si>
+  <si>
+    <t>Coastal Infrastructure LLC</t>
+  </si>
+  <si>
+    <t>Miguel Lopez</t>
+  </si>
+  <si>
+    <t>Civil / Infrastructure</t>
+  </si>
+  <si>
+    <t>Pioneer Site Solutions</t>
+  </si>
+  <si>
+    <t>Anthony Ramos</t>
+  </si>
+  <si>
+    <t>Site Development</t>
+  </si>
+  <si>
+    <t>Worker Name</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Employee Code</t>
+  </si>
+  <si>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Pedro A. Maldonado</t>
+  </si>
+  <si>
+    <t>Lead Driller</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Samuel Ortiz Burgos</t>
+  </si>
+  <si>
+    <t>Driller Helper</t>
+  </si>
+  <si>
+    <t>Luis R. Negrón Ruiz</t>
+  </si>
+  <si>
+    <t>Driller</t>
+  </si>
+  <si>
+    <t>Marta I. Colón</t>
+  </si>
+  <si>
+    <t>Apprentice</t>
+  </si>
+  <si>
+    <t>onboarding</t>
+  </si>
+  <si>
+    <t>Raúl García Molina</t>
+  </si>
+  <si>
+    <t>Foreman</t>
+  </si>
+  <si>
+    <t>Ismael Villa</t>
+  </si>
+  <si>
+    <t>Concrete Finisher</t>
+  </si>
+  <si>
+    <t>Diego Acosta</t>
+  </si>
+  <si>
+    <t>Laborer</t>
+  </si>
+  <si>
+    <t>Javier Méndez Torres</t>
+  </si>
+  <si>
+    <t>Master Electrician</t>
+  </si>
+  <si>
+    <t>Óscar R. Figueroa</t>
+  </si>
+  <si>
+    <t>Electrician</t>
+  </si>
+  <si>
+    <t>Edwin Ruiz Pagán</t>
+  </si>
+  <si>
+    <t>Apprentice Electrician</t>
+  </si>
+  <si>
+    <t>Antonio Benítez</t>
+  </si>
+  <si>
+    <t>Equipment Operator</t>
+  </si>
+  <si>
+    <t>Fernando Soto</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Rafael Martínez</t>
+  </si>
+  <si>
+    <t>Spotter</t>
+  </si>
+  <si>
+    <t>Gabriel Estévez</t>
+  </si>
+  <si>
+    <t>Scaffold Erector</t>
+  </si>
+  <si>
+    <t>Mateo Villanueva</t>
+  </si>
+  <si>
+    <t>Scaffold Helper</t>
+  </si>
+  <si>
+    <t>Leonardo Benítez</t>
+  </si>
+  <si>
+    <t>John Martinez</t>
+  </si>
+  <si>
+    <t>ASB-001</t>
+  </si>
+  <si>
+    <t>john.martinez@asb.com</t>
+  </si>
+  <si>
+    <t>787-555-0101</t>
+  </si>
+  <si>
+    <t>Luis Gonzalez</t>
+  </si>
+  <si>
+    <t>ASB-002</t>
+  </si>
+  <si>
+    <t>luis.gonzalez@asb.com</t>
+  </si>
+  <si>
+    <t>787-555-0102</t>
+  </si>
+  <si>
+    <t>Maria Torres</t>
+  </si>
+  <si>
+    <t>Safety Officer</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>ASB-003</t>
+  </si>
+  <si>
+    <t>maria.torres@asb.com</t>
+  </si>
+  <si>
+    <t>787-555-0103</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>NSM-001</t>
+  </si>
+  <si>
+    <t>carlos.rivera@nsm.com</t>
+  </si>
+  <si>
+    <t>787-555-0201</t>
+  </si>
+  <si>
+    <t>Javier Morales</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>NSM-002</t>
+  </si>
+  <si>
+    <t>javier.morales@nsm.com</t>
+  </si>
+  <si>
+    <t>787-555-0202</t>
+  </si>
+  <si>
+    <t>Elena Ruiz</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>NSM-003</t>
+  </si>
+  <si>
+    <t>elena.ruiz@nsm.com</t>
+  </si>
+  <si>
+    <t>787-555-0203</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>CCW-001</t>
+  </si>
+  <si>
+    <t>andrea.cruz@ccw.com</t>
+  </si>
+  <si>
+    <t>787-555-0301</t>
+  </si>
+  <si>
+    <t>Pedro Santiago</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
+    <t>CCW-002</t>
+  </si>
+  <si>
+    <t>pedro.santiago@ccw.com</t>
+  </si>
+  <si>
+    <t>787-555-0302</t>
+  </si>
+  <si>
+    <t>Ricardo Vega</t>
+  </si>
+  <si>
+    <t>CCW-003</t>
+  </si>
+  <si>
+    <t>ricardo.vega@ccw.com</t>
+  </si>
+  <si>
+    <t>787-555-0303</t>
+  </si>
+  <si>
+    <t>Welder</t>
+  </si>
+  <si>
+    <t>ICC-001</t>
+  </si>
+  <si>
+    <t>daniel.perez@ironcore.com</t>
+  </si>
+  <si>
+    <t>787-555-0401</t>
+  </si>
+  <si>
+    <t>Sofia Martinez</t>
+  </si>
+  <si>
+    <t>Inspector</t>
+  </si>
+  <si>
+    <t>ICC-002</t>
+  </si>
+  <si>
+    <t>sofia.martinez@ironcore.com</t>
+  </si>
+  <si>
+    <t>787-555-0402</t>
+  </si>
+  <si>
+    <t>Civil Engineer</t>
+  </si>
+  <si>
+    <t>CIL-001</t>
+  </si>
+  <si>
+    <t>miguel.lopez@coastal.com</t>
+  </si>
+  <si>
+    <t>787-555-0501</t>
+  </si>
+  <si>
+    <t>Valeria Ortiz</t>
+  </si>
+  <si>
+    <t>Surveyor</t>
+  </si>
+  <si>
+    <t>CIL-002</t>
+  </si>
+  <si>
+    <t>valeria.ortiz@coastal.com</t>
+  </si>
+  <si>
+    <t>787-555-0502</t>
+  </si>
+  <si>
+    <t>Site Manager</t>
+  </si>
+  <si>
+    <t>PSS-001</t>
+  </si>
+  <si>
+    <t>anthony.ramos@pss.com</t>
+  </si>
+  <si>
+    <t>787-555-0601</t>
+  </si>
+  <si>
+    <t>Camila Reyes</t>
+  </si>
+  <si>
+    <t>Coordinator</t>
+  </si>
+  <si>
+    <t>PSS-002</t>
+  </si>
+  <si>
+    <t>camila.reyes@pss.com</t>
+  </si>
+  <si>
+    <t>787-555-0602</t>
+  </si>
   <si>
     <t>HSE Required Certifications</t>
   </si>
   <si>
-    <t>Additional Training</t>
-  </si>
-  <si>
-    <t>Contractor</t>
-  </si>
-  <si>
     <t>Worker</t>
   </si>
   <si>
-    <t>Stonewall Drilling Services, LLC</t>
-  </si>
-  <si>
-    <t>Pedro A. Maldonado</t>
-  </si>
-  <si>
-    <t>Samuel Ortiz Burgos</t>
-  </si>
-  <si>
-    <t>Luis R. Negrón Ruiz</t>
-  </si>
-  <si>
-    <t>Marta I. Colón</t>
-  </si>
-  <si>
-    <t>Atlas Concrete Works, Inc.</t>
-  </si>
-  <si>
-    <t>Raúl García Molina</t>
-  </si>
-  <si>
-    <t>Ismael Villa</t>
-  </si>
-  <si>
-    <t>Diego Acosta</t>
-  </si>
-  <si>
-    <t>PowerLine Electric Corp.</t>
-  </si>
-  <si>
-    <t>Javier Méndez Torres</t>
-  </si>
-  <si>
-    <t>Óscar R. Figueroa</t>
-  </si>
-  <si>
-    <t>Edwin Ruiz Pagán</t>
-  </si>
-  <si>
-    <t>SafePath Excavation, Co.</t>
-  </si>
-  <si>
-    <t>Antonio Benítez</t>
-  </si>
-  <si>
-    <t>Fernando Soto</t>
-  </si>
-  <si>
-    <t>Rafael Martínez</t>
-  </si>
-  <si>
-    <t>SkyHigh Scaffolding Solutions</t>
-  </si>
-  <si>
-    <t>Gabriel Estévez</t>
-  </si>
-  <si>
-    <t>Mateo Villanueva</t>
-  </si>
-  <si>
-    <t>Leonardo Benítez</t>
-  </si>
-  <si>
-    <t>Atlantic Safety Builders, LLC</t>
-  </si>
-  <si>
-    <t>John Martinez</t>
-  </si>
-  <si>
-    <t>Luis Gonzalez</t>
-  </si>
-  <si>
-    <t>Maria Torres</t>
-  </si>
-  <si>
-    <t>North Shore Mechanical, Inc.</t>
-  </si>
-  <si>
-    <t>Carlos Rivera</t>
-  </si>
-  <si>
-    <t>Javier Morales</t>
-  </si>
-  <si>
-    <t>Elena Ruiz</t>
-  </si>
-  <si>
-    <t>Caribbean Concrete Works</t>
-  </si>
-  <si>
-    <t>Andrea Cruz</t>
-  </si>
-  <si>
-    <t>Pedro Santiago</t>
-  </si>
-  <si>
-    <t>Ricardo Vega</t>
-  </si>
-  <si>
-    <t>IronCore Contractors</t>
-  </si>
-  <si>
-    <t>Daniel Perez</t>
-  </si>
-  <si>
-    <t>Sofia Martinez</t>
-  </si>
-  <si>
-    <t>Coastal Infrastructure LLC</t>
-  </si>
-  <si>
-    <t>Miguel Lopez</t>
-  </si>
-  <si>
-    <t>Valeria Ortiz</t>
-  </si>
-  <si>
-    <t>Pioneer Site Solutions</t>
-  </si>
-  <si>
-    <t>Anthony Ramos</t>
-  </si>
-  <si>
-    <t>Camila Reyes</t>
-  </si>
-  <si>
-    <t>Cornerstone Industrial Group, Corp</t>
-  </si>
-  <si>
-    <t>Francisco González Carmona</t>
-  </si>
-  <si>
-    <t>Steven Cruz Martínez</t>
-  </si>
-  <si>
-    <t>Contractor Certifications Tracker</t>
-  </si>
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t>1. Add new contractors on the Contractors tab.</t>
-  </si>
-  <si>
-    <t>2. Add workers on the Workers tab. Each worker belongs to one contractor (pick from dropdown).</t>
-  </si>
-  <si>
-    <t>3. Review required certifications on the Certifications tab. Add new ones if HSE adds them.</t>
-  </si>
-  <si>
-    <t>4. On the Tracker tab, enter the completion date for each worker / certification combo.</t>
-  </si>
-  <si>
-    <t>5. The Dashboard tab auto-updates: compliance %, missing certs, expiring soon.</t>
-  </si>
-  <si>
-    <t>Color coding on the Tracker</t>
-  </si>
-  <si>
-    <t>• Red cell     = certification missing (empty)</t>
-  </si>
-  <si>
-    <t>• Yellow cell  = completed, expiring within 60 days</t>
-  </si>
-  <si>
-    <t>• Orange cell  = expired (past validity based on Certifications tab)</t>
-  </si>
-  <si>
-    <t>• Green cell   = current</t>
-  </si>
-  <si>
-    <t>Sharing with peers</t>
-  </si>
-  <si>
-    <t>Save this file to OneDrive or SharePoint and turn on co-authoring so peers can edit simultaneously.</t>
-  </si>
-  <si>
-    <t>Every edit is tracked in Version History (File → Info → Version History).</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>• Validity years in the Certifications tab drive expiration logic. 0 = no expiration.</t>
-  </si>
-  <si>
-    <t>• Dates must be entered as real dates (mm/dd/yyyy), not text.</t>
-  </si>
-  <si>
-    <t>Contractor Certifications Dashboard</t>
-  </si>
-  <si>
-    <t>Total Contractors</t>
-  </si>
-  <si>
-    <t>Total Workers</t>
-  </si>
-  <si>
-    <t>Active Workers</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>Compliance by Certification</t>
-  </si>
-  <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>% Complete</t>
-  </si>
-  <si>
-    <t>Bar</t>
-  </si>
-  <si>
-    <t>Validity (years, 0=none)</t>
-  </si>
-  <si>
-    <t>Protección Contra Caídas</t>
-  </si>
-  <si>
-    <t>HSE Required</t>
-  </si>
-  <si>
-    <t>Flama Expuesta</t>
-  </si>
-  <si>
-    <t>Espacios Confinados</t>
-  </si>
-  <si>
-    <t>Manejo de Equipo Motorizado</t>
-  </si>
-  <si>
-    <t>Excavación o Zanja</t>
-  </si>
-  <si>
-    <t>Manejo de Tijeras (Scissor Lift)</t>
-  </si>
-  <si>
-    <t>Seguridad Eléctrica</t>
-  </si>
-  <si>
-    <t>Lockout</t>
-  </si>
-  <si>
-    <t>Manejo de Grúas</t>
-  </si>
-  <si>
-    <t>Escaleras</t>
-  </si>
-  <si>
-    <t>Andamios</t>
-  </si>
-  <si>
-    <t>Trabajos con Plomo o Asbesto</t>
-  </si>
-  <si>
-    <t>Comunicación de Riesgos</t>
-  </si>
-  <si>
-    <t>Inducción Jacobs/Lilly</t>
-  </si>
-  <si>
-    <t>OSHA 40Hr HAZWOPER</t>
-  </si>
-  <si>
-    <t>OSHA 8Hr Refresher</t>
-  </si>
-  <si>
-    <t>Drilling Safety</t>
-  </si>
-  <si>
-    <t>Utility Locating</t>
-  </si>
-  <si>
-    <t>OSHA 10</t>
-  </si>
-  <si>
-    <t>OSHA 30</t>
-  </si>
-  <si>
-    <t>Rebar Safety</t>
-  </si>
-  <si>
-    <t>Formwork &amp; Shoring</t>
-  </si>
-  <si>
-    <t>Silica Exposure</t>
-  </si>
-  <si>
-    <t>Concrete &amp; Masonry</t>
-  </si>
-  <si>
-    <t>Equipment Training</t>
-  </si>
-  <si>
-    <t>OSHA 30 501</t>
-  </si>
-  <si>
-    <t>OSHA 30 511</t>
-  </si>
-  <si>
-    <t>Estamos mas que bien</t>
-  </si>
-  <si>
-    <t>Contractor Name</t>
-  </si>
-  <si>
-    <t>Primary Contact</t>
-  </si>
-  <si>
-    <t>Specialty</t>
-  </si>
-  <si>
-    <t>Workers (count)</t>
-  </si>
-  <si>
-    <t>Juan Pérez Vázquez</t>
-  </si>
-  <si>
-    <t>Drilling / Geotechnical</t>
-  </si>
-  <si>
-    <t>Carla M. Santos Vega</t>
-  </si>
-  <si>
-    <t>Concrete &amp; Foundation</t>
-  </si>
-  <si>
-    <t>Miguel Torres Ramos</t>
-  </si>
-  <si>
-    <t>Electrical &amp; Instrumentation</t>
-  </si>
-  <si>
-    <t>Ana L. Reyes Díaz</t>
-  </si>
-  <si>
-    <t>Excavation &amp; Earthworks</t>
-  </si>
-  <si>
-    <t>Roberto Díaz Cruz</t>
-  </si>
-  <si>
-    <t>Scaffolding / Access Systems</t>
-  </si>
-  <si>
-    <t>Maria Santos</t>
-  </si>
-  <si>
-    <t>General Construction</t>
-  </si>
-  <si>
-    <t>Demo contractor</t>
-  </si>
-  <si>
-    <t>Mechanical / Utilities</t>
-  </si>
-  <si>
-    <t>Concrete and Masonry</t>
-  </si>
-  <si>
-    <t>Structural Steel</t>
-  </si>
-  <si>
-    <t>Civil / Infrastructure</t>
-  </si>
-  <si>
-    <t>Site Development</t>
-  </si>
-  <si>
-    <t>Worker Name</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Employee Code</t>
-  </si>
-  <si>
-    <t>Hire Date</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Lead Driller</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Driller Helper</t>
-  </si>
-  <si>
-    <t>Driller</t>
-  </si>
-  <si>
-    <t>Apprentice</t>
-  </si>
-  <si>
-    <t>onboarding</t>
-  </si>
-  <si>
-    <t>Foreman</t>
-  </si>
-  <si>
-    <t>Concrete Finisher</t>
-  </si>
-  <si>
-    <t>Laborer</t>
-  </si>
-  <si>
-    <t>Master Electrician</t>
-  </si>
-  <si>
-    <t>Electrician</t>
-  </si>
-  <si>
-    <t>Apprentice Electrician</t>
-  </si>
-  <si>
-    <t>Equipment Operator</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Spotter</t>
-  </si>
-  <si>
-    <t>Scaffold Erector</t>
-  </si>
-  <si>
-    <t>Scaffold Helper</t>
-  </si>
-  <si>
-    <t>ASB-001</t>
-  </si>
-  <si>
-    <t>john.martinez@asb.com</t>
-  </si>
-  <si>
-    <t>787-555-0101</t>
-  </si>
-  <si>
-    <t>ASB-002</t>
-  </si>
-  <si>
-    <t>luis.gonzalez@asb.com</t>
-  </si>
-  <si>
-    <t>787-555-0102</t>
-  </si>
-  <si>
-    <t>Safety Officer</t>
-  </si>
-  <si>
-    <t>inactive</t>
-  </si>
-  <si>
-    <t>ASB-003</t>
-  </si>
-  <si>
-    <t>maria.torres@asb.com</t>
-  </si>
-  <si>
-    <t>787-555-0103</t>
-  </si>
-  <si>
-    <t>Supervisor</t>
-  </si>
-  <si>
-    <t>NSM-001</t>
-  </si>
-  <si>
-    <t>carlos.rivera@nsm.com</t>
-  </si>
-  <si>
-    <t>787-555-0201</t>
-  </si>
-  <si>
-    <t>Technician</t>
-  </si>
-  <si>
-    <t>NSM-002</t>
-  </si>
-  <si>
-    <t>javier.morales@nsm.com</t>
-  </si>
-  <si>
-    <t>787-555-0202</t>
-  </si>
-  <si>
-    <t>Engineer</t>
-  </si>
-  <si>
-    <t>NSM-003</t>
-  </si>
-  <si>
-    <t>elena.ruiz@nsm.com</t>
-  </si>
-  <si>
-    <t>787-555-0203</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>CCW-001</t>
-  </si>
-  <si>
-    <t>andrea.cruz@ccw.com</t>
-  </si>
-  <si>
-    <t>787-555-0301</t>
-  </si>
-  <si>
-    <t>Mason</t>
-  </si>
-  <si>
-    <t>CCW-002</t>
-  </si>
-  <si>
-    <t>pedro.santiago@ccw.com</t>
-  </si>
-  <si>
-    <t>787-555-0302</t>
-  </si>
-  <si>
-    <t>CCW-003</t>
-  </si>
-  <si>
-    <t>ricardo.vega@ccw.com</t>
-  </si>
-  <si>
-    <t>787-555-0303</t>
-  </si>
-  <si>
-    <t>Welder</t>
-  </si>
-  <si>
-    <t>ICC-001</t>
-  </si>
-  <si>
-    <t>daniel.perez@ironcore.com</t>
-  </si>
-  <si>
-    <t>787-555-0401</t>
-  </si>
-  <si>
-    <t>Inspector</t>
-  </si>
-  <si>
-    <t>ICC-002</t>
-  </si>
-  <si>
-    <t>sofia.martinez@ironcore.com</t>
-  </si>
-  <si>
-    <t>787-555-0402</t>
-  </si>
-  <si>
-    <t>Civil Engineer</t>
-  </si>
-  <si>
-    <t>CIL-001</t>
-  </si>
-  <si>
-    <t>miguel.lopez@coastal.com</t>
-  </si>
-  <si>
-    <t>787-555-0501</t>
-  </si>
-  <si>
-    <t>Surveyor</t>
-  </si>
-  <si>
-    <t>CIL-002</t>
-  </si>
-  <si>
-    <t>valeria.ortiz@coastal.com</t>
-  </si>
-  <si>
-    <t>787-555-0502</t>
-  </si>
-  <si>
-    <t>Site Manager</t>
-  </si>
-  <si>
-    <t>PSS-001</t>
-  </si>
-  <si>
-    <t>anthony.ramos@pss.com</t>
-  </si>
-  <si>
-    <t>787-555-0601</t>
-  </si>
-  <si>
-    <t>Coordinator</t>
-  </si>
-  <si>
-    <t>PSS-002</t>
-  </si>
-  <si>
-    <t>camila.reyes@pss.com</t>
-  </si>
-  <si>
-    <t>787-555-0602</t>
+    <t>joshua Santiago</t>
+  </si>
+  <si>
+    <t>Salvador ribot</t>
+  </si>
+  <si>
+    <t>maldonado Victor</t>
+  </si>
+  <si>
+    <t>Jose Gonzalez</t>
   </si>
 </sst>
 </file>
@@ -686,7 +689,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,6 +760,16 @@
       <color rgb="FF2E7D32"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -782,7 +795,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -850,11 +863,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -883,20 +926,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1299,46 +1347,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="A1" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1346,27 +1394,27 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1374,17 +1422,17 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -1392,17 +1440,17 @@
     </row>
     <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
@@ -1428,89 +1476,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="A1" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="20"/>
+      <c r="A3" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="28"/>
+      <c r="E3" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="G3" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="29">
         <f>COUNTA(Contractors!A2:A50)</f>
         <v>11</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="22">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29">
         <f>COUNTA(Workers!A2:A200)</f>
         <v>31</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="22">
+      <c r="D4" s="28"/>
+      <c r="E4" s="29">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
         <v>25</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="22" t="str">
+      <c r="F4" s="28"/>
+      <c r="G4" s="29" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>04/28/2026</v>
-      </c>
-      <c r="H4" s="20"/>
+        <v>04/29/2026</v>
+      </c>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="A7" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1531,11 +1579,11 @@
         <v>7</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" ref="E9:E36" si="0">IFERROR(C9/(C9+D9),0)</f>
+        <f t="shared" ref="E9:E38" si="0">IFERROR(C9/(C9+D9),0)</f>
         <v>0.77419354838709675</v>
       </c>
       <c r="F9" s="4" t="e">
-        <f t="shared" ref="F9:F36" si="1">REPT(CHAR(9632),ROUND(E9*20,0))</f>
+        <f t="shared" ref="F9:F38" si="1">REPT(CHAR(9632),ROUND(E9*20,0))</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1602,15 +1650,15 @@
       </c>
       <c r="C12" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A12,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C12</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>0.5161290322580645</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F12" s="4" t="e">
         <f t="shared" si="1"/>
@@ -1654,15 +1702,15 @@
       </c>
       <c r="C14" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A14,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C14</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>0.61290322580645162</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="F14" s="4" t="e">
         <f t="shared" si="1"/>
@@ -1732,15 +1780,15 @@
       </c>
       <c r="C17" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A17,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C17</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>0.38709677419354838</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="F17" s="4" t="e">
         <f t="shared" si="1"/>
@@ -1862,15 +1910,15 @@
       </c>
       <c r="C22" s="2">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A22,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D22" s="2">
         <f>COUNTA(Workers!A$2:A$200)-C22</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>0.77419354838709675</v>
+        <v>0.70967741935483875</v>
       </c>
       <c r="F22" s="4" t="e">
         <f t="shared" si="1"/>
@@ -1992,15 +2040,15 @@
       </c>
       <c r="C27" s="11">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A27,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C27</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" s="12">
         <f t="shared" si="0"/>
-        <v>0.4838709677419355</v>
+        <v>0.45161290322580644</v>
       </c>
       <c r="F27" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2122,15 +2170,15 @@
       </c>
       <c r="C32" s="11">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A32,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="11">
         <f>COUNTA(Workers!A$2:A$200)-C32</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="12">
         <f t="shared" si="0"/>
-        <v>0.35483870967741937</v>
+        <v>0.32258064516129031</v>
       </c>
       <c r="F32" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2220,9 +2268,9 @@
         <f>Certifications!A29</f>
         <v>Estamos mas que bien</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="17" t="str">
         <f>Certifications!B29</f>
-        <v>0</v>
+        <v>Additional Training</v>
       </c>
       <c r="C36" s="17">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A36,Tracker!$C$2:$AZ$2,0))),0)</f>
@@ -2241,18 +2289,70 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="21">
+        <f>Certifications!A30</f>
+        <v>0</v>
+      </c>
+      <c r="B37" s="21">
+        <f>Certifications!B30</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="21">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A37,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="21">
+        <f>COUNTA(Workers!A$2:A$200)-C37</f>
+        <v>30</v>
+      </c>
+      <c r="E37" s="22">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F37" s="23" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="24">
+        <f>Certifications!A31</f>
+        <v>0</v>
+      </c>
+      <c r="B38" s="24">
+        <f>Certifications!B31</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="24">
+        <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A38,Tracker!$C$2:$AZ$2,0))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D38" s="24">
+        <f>COUNTA(Workers!A$2:A$200)-C38</f>
+        <v>30</v>
+      </c>
+      <c r="E38" s="25">
+        <f t="shared" si="0"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F38" s="26" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="C4:D5"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="G4:H5"/>
     <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
@@ -2283,24 +2383,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2308,10 +2408,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2319,10 +2419,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2330,10 +2430,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2341,10 +2441,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2352,10 +2452,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2363,10 +2463,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2374,10 +2474,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2385,10 +2485,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2396,10 +2496,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2407,10 +2507,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2418,10 +2518,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2429,10 +2529,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2440,10 +2540,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2451,10 +2551,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2462,10 +2562,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2473,10 +2573,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2484,10 +2584,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2495,10 +2595,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2506,10 +2606,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2517,10 +2617,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2528,10 +2628,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2539,10 +2639,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2550,10 +2650,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2561,10 +2661,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2572,10 +2672,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2583,10 +2683,10 @@
     </row>
     <row r="28" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2594,7 +2694,13 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2624,30 +2730,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <f>IF(A2="","",COUNTIF(Workers!B:B,A2))</f>
@@ -2656,13 +2762,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D3">
         <f>IF(A3="","",COUNTIF(Workers!B:B,A3))</f>
@@ -2671,13 +2777,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="D4">
         <f>IF(A4="","",COUNTIF(Workers!B:B,A4))</f>
@@ -2686,13 +2792,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D5">
         <f>IF(A5="","",COUNTIF(Workers!B:B,A5))</f>
@@ -2701,13 +2807,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D6">
         <f>IF(A6="","",COUNTIF(Workers!B:B,A6))</f>
@@ -2716,110 +2822,110 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <f>IF(A7="","",COUNTIF(Workers!B:B,A7))</f>
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D8">
         <f>IF(A8="","",COUNTIF(Workers!B:B,A8))</f>
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D9">
         <f>IF(A9="","",COUNTIF(Workers!B:B,A9))</f>
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D10">
         <f>IF(A10="","",COUNTIF(Workers!B:B,A10))</f>
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="D11">
         <f>IF(A11="","",COUNTIF(Workers!B:B,A11))</f>
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <f>IF(A12="","",COUNTIF(Workers!B:B,A12))</f>
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3070,45 +3176,45 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F2" s="7">
         <v>44270</v>
@@ -3116,16 +3222,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F3" s="7">
         <v>45117</v>
@@ -3133,16 +3239,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F4" s="7">
         <v>44586</v>
@@ -3150,16 +3256,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F5" s="7">
         <v>46054</v>
@@ -3167,16 +3273,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F6" s="7">
         <v>43605</v>
@@ -3184,16 +3290,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F7" s="7">
         <v>44058</v>
@@ -3201,16 +3307,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F8" s="7">
         <v>45597</v>
@@ -3218,16 +3324,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F9" s="7">
         <v>42098</v>
@@ -3235,16 +3341,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F10" s="7">
         <v>44447</v>
@@ -3252,16 +3358,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F11" s="7">
         <v>45940</v>
@@ -3269,16 +3375,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F12" s="7">
         <v>43271</v>
@@ -3286,16 +3392,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F13" s="7">
         <v>44666</v>
@@ -3303,16 +3409,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F14" s="7">
         <v>44985</v>
@@ -3320,16 +3426,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F15" s="7">
         <v>43019</v>
@@ -3337,16 +3443,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="F16" s="7">
         <v>44943</v>
@@ -3354,16 +3460,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F17" s="7">
         <v>46086</v>
@@ -3371,392 +3477,392 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F18" s="7">
         <v>44635</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H18" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="F19" s="7">
         <v>45129</v>
       </c>
       <c r="G19" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="H19" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F20" s="7">
         <v>44505</v>
       </c>
       <c r="G20" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F21" s="7">
         <v>43992</v>
       </c>
       <c r="G21" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="H21" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="F22" s="7">
         <v>44822</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H22" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F23" s="7">
         <v>45303</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F24" s="7">
         <v>44311</v>
       </c>
       <c r="G24" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F25" s="7">
         <v>44971</v>
       </c>
       <c r="G25" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H25" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F26" s="7">
         <v>44073</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F27" s="7">
         <v>44700</v>
       </c>
       <c r="G27" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F28" s="7">
         <v>45202</v>
       </c>
       <c r="G28" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H28" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F29" s="7">
         <v>44207</v>
       </c>
       <c r="G29" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F30" s="7">
         <v>45342</v>
       </c>
       <c r="G30" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H30" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F31" s="7">
         <v>44903</v>
       </c>
       <c r="G31" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F32" s="7">
         <v>44374</v>
       </c>
       <c r="G32" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
@@ -4264,7 +4370,7 @@
       <c r="F200" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C2:C200" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>JobTitleOptions</formula1>
     </dataValidation>
@@ -4285,57 +4391,59 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AD200"/>
+  <dimension ref="A1:AF200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="19" width="14" customWidth="1"/>
-    <col min="20" max="30" width="13" customWidth="1"/>
+    <col min="20" max="32" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="27"/>
-    </row>
-    <row r="2" spans="1:30" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+    </row>
+    <row r="2" spans="1:32" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="C2" s="1" t="str">
         <f>Certifications!A2</f>
@@ -4449,13 +4557,15 @@
         <f>Certifications!A29</f>
         <v>Estamos mas que bien</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="C3" s="9">
         <v>45976</v>
@@ -4523,13 +4633,15 @@
       <c r="AD3" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C4" s="9">
         <v>45797</v>
@@ -4595,13 +4707,15 @@
       <c r="AD4" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="C5" s="9">
         <v>45976</v>
@@ -4663,13 +4777,15 @@
       <c r="AD5" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="C6" s="9">
         <v>45976</v>
@@ -4709,13 +4825,15 @@
       <c r="AD6" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="C7" s="9">
         <v>45976</v>
@@ -4785,13 +4903,15 @@
       <c r="AD7" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="C8" s="9">
         <v>45976</v>
@@ -4855,13 +4975,15 @@
       <c r="AD8" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="C9" s="9">
         <v>45976</v>
@@ -4903,13 +5025,15 @@
       <c r="AD9" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C10" s="9">
         <v>45976</v>
@@ -4965,13 +5089,15 @@
       <c r="AD10" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="9"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="C11" s="9">
         <v>45458</v>
@@ -5023,13 +5149,15 @@
       <c r="AD11" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="9"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="C12" s="9">
         <v>45976</v>
@@ -5071,13 +5199,15 @@
       <c r="AD12" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="9"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="C13" s="9">
         <v>45976</v>
@@ -5139,13 +5269,15 @@
       <c r="AD13" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="9"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C14" s="9">
         <v>45797</v>
@@ -5203,13 +5335,15 @@
       <c r="AD14" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="9"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C15" s="9">
         <v>45458</v>
@@ -5257,13 +5391,15 @@
       <c r="AD15" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="9"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="C16" s="9">
         <v>45976</v>
@@ -5319,13 +5455,15 @@
       <c r="AD16" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="9"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C17" s="9">
         <v>45797</v>
@@ -5379,13 +5517,15 @@
       <c r="AD17" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE17" s="9"/>
+      <c r="AF17" s="9"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="C18" s="9">
         <v>45976</v>
@@ -5423,13 +5563,15 @@
       <c r="AD18" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="9"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="C19" s="9">
         <v>45708</v>
@@ -5493,13 +5635,15 @@
       <c r="AD19" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="9"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="C20" s="9">
         <v>45976</v>
@@ -5553,13 +5697,15 @@
       <c r="AD20" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="9"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C21" s="9">
         <v>45976</v>
@@ -5603,13 +5749,15 @@
       <c r="AD21" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="9"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9">
@@ -5667,13 +5815,15 @@
       <c r="AD22" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="9"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -5723,13 +5873,15 @@
       <c r="AD23" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="9"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="C24" s="9">
         <v>45976</v>
@@ -5793,13 +5945,15 @@
       <c r="AD24" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="9"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C25" s="9">
         <v>45976</v>
@@ -5859,13 +6013,15 @@
       <c r="AD25" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="9"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -5917,13 +6073,15 @@
       <c r="AD26" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE26" s="9"/>
+      <c r="AF26" s="9"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -5965,13 +6123,15 @@
       <c r="AD27" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="9"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C28" s="9">
         <v>45976</v>
@@ -6027,13 +6187,15 @@
       <c r="AD28" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>183</v>
       </c>
       <c r="C29" s="9">
         <v>45976</v>
@@ -6097,13 +6259,15 @@
       <c r="AD29" s="9">
         <v>45828</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9">
@@ -6165,13 +6329,15 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
       <c r="AD30" s="9"/>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="C31" s="9">
         <v>45458</v>
@@ -6225,13 +6391,15 @@
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
       <c r="AD31" s="9"/>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="9"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -6285,13 +6453,15 @@
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
       <c r="AD32" s="9"/>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE32" s="9"/>
+      <c r="AF32" s="9"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -6329,13 +6499,12 @@
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
       <c r="AD33" s="9"/>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -6350,9 +6519,7 @@
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
-      <c r="P34" s="9">
-        <v>46136</v>
-      </c>
+      <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -6367,56 +6534,48 @@
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
       <c r="AD34" s="9"/>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="9"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>48</v>
+        <v>209</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="9">
-        <v>46059</v>
-      </c>
+      <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9">
-        <v>46059</v>
-      </c>
+      <c r="H35" s="9"/>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="9">
-        <v>46059</v>
-      </c>
+      <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
-      <c r="P35" s="9">
-        <v>46136</v>
-      </c>
+      <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
       <c r="T35" s="9"/>
-      <c r="U35" s="9">
-        <v>46341</v>
-      </c>
+      <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="9">
-        <v>46059</v>
-      </c>
+      <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="9"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>210</v>
+      </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -6445,8 +6604,13 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="9"/>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>211</v>
+      </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -6475,8 +6639,10 @@
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
       <c r="AD37" s="9"/>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -6505,8 +6671,10 @@
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
       <c r="AD38" s="9"/>
-    </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="9"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -6535,8 +6703,10 @@
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
       <c r="AD39" s="9"/>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="9"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -6565,8 +6735,10 @@
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
       <c r="AD40" s="9"/>
-    </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE40" s="9"/>
+      <c r="AF40" s="9"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -6595,8 +6767,10 @@
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
       <c r="AD41" s="9"/>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="9"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -6625,8 +6799,10 @@
       <c r="AB42" s="9"/>
       <c r="AC42" s="9"/>
       <c r="AD42" s="9"/>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE42" s="9"/>
+      <c r="AF42" s="9"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -6655,8 +6831,10 @@
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE43" s="9"/>
+      <c r="AF43" s="9"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -6685,8 +6863,10 @@
       <c r="AB44" s="9"/>
       <c r="AC44" s="9"/>
       <c r="AD44" s="9"/>
-    </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE44" s="9"/>
+      <c r="AF44" s="9"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -6715,8 +6895,10 @@
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE45" s="9"/>
+      <c r="AF45" s="9"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -6745,8 +6927,10 @@
       <c r="AB46" s="9"/>
       <c r="AC46" s="9"/>
       <c r="AD46" s="9"/>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE46" s="9"/>
+      <c r="AF46" s="9"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -6775,8 +6959,10 @@
       <c r="AB47" s="9"/>
       <c r="AC47" s="9"/>
       <c r="AD47" s="9"/>
-    </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE47" s="9"/>
+      <c r="AF47" s="9"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -6805,8 +6991,10 @@
       <c r="AB48" s="9"/>
       <c r="AC48" s="9"/>
       <c r="AD48" s="9"/>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE48" s="9"/>
+      <c r="AF48" s="9"/>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -6835,8 +7023,10 @@
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
       <c r="AD49" s="9"/>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE49" s="9"/>
+      <c r="AF49" s="9"/>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -6865,8 +7055,10 @@
       <c r="AB50" s="9"/>
       <c r="AC50" s="9"/>
       <c r="AD50" s="9"/>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE50" s="9"/>
+      <c r="AF50" s="9"/>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -6895,8 +7087,10 @@
       <c r="AB51" s="9"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE51" s="9"/>
+      <c r="AF51" s="9"/>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -6925,8 +7119,10 @@
       <c r="AB52" s="9"/>
       <c r="AC52" s="9"/>
       <c r="AD52" s="9"/>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE52" s="9"/>
+      <c r="AF52" s="9"/>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
@@ -6955,8 +7151,10 @@
       <c r="AB53" s="9"/>
       <c r="AC53" s="9"/>
       <c r="AD53" s="9"/>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE53" s="9"/>
+      <c r="AF53" s="9"/>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
@@ -6985,8 +7183,10 @@
       <c r="AB54" s="9"/>
       <c r="AC54" s="9"/>
       <c r="AD54" s="9"/>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE54" s="9"/>
+      <c r="AF54" s="9"/>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -7015,8 +7215,10 @@
       <c r="AB55" s="9"/>
       <c r="AC55" s="9"/>
       <c r="AD55" s="9"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE55" s="9"/>
+      <c r="AF55" s="9"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -7045,8 +7247,10 @@
       <c r="AB56" s="9"/>
       <c r="AC56" s="9"/>
       <c r="AD56" s="9"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE56" s="9"/>
+      <c r="AF56" s="9"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
@@ -7075,8 +7279,10 @@
       <c r="AB57" s="9"/>
       <c r="AC57" s="9"/>
       <c r="AD57" s="9"/>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE57" s="9"/>
+      <c r="AF57" s="9"/>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -7105,8 +7311,10 @@
       <c r="AB58" s="9"/>
       <c r="AC58" s="9"/>
       <c r="AD58" s="9"/>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE58" s="9"/>
+      <c r="AF58" s="9"/>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -7135,8 +7343,10 @@
       <c r="AB59" s="9"/>
       <c r="AC59" s="9"/>
       <c r="AD59" s="9"/>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE59" s="9"/>
+      <c r="AF59" s="9"/>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
@@ -7165,8 +7375,10 @@
       <c r="AB60" s="9"/>
       <c r="AC60" s="9"/>
       <c r="AD60" s="9"/>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE60" s="9"/>
+      <c r="AF60" s="9"/>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
@@ -7195,8 +7407,10 @@
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
       <c r="AD61" s="9"/>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE61" s="9"/>
+      <c r="AF61" s="9"/>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
@@ -7225,8 +7439,10 @@
       <c r="AB62" s="9"/>
       <c r="AC62" s="9"/>
       <c r="AD62" s="9"/>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE62" s="9"/>
+      <c r="AF62" s="9"/>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -7255,8 +7471,10 @@
       <c r="AB63" s="9"/>
       <c r="AC63" s="9"/>
       <c r="AD63" s="9"/>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE63" s="9"/>
+      <c r="AF63" s="9"/>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
@@ -7285,8 +7503,10 @@
       <c r="AB64" s="9"/>
       <c r="AC64" s="9"/>
       <c r="AD64" s="9"/>
-    </row>
-    <row r="65" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE64" s="9"/>
+      <c r="AF64" s="9"/>
+    </row>
+    <row r="65" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
@@ -7315,8 +7535,10 @@
       <c r="AB65" s="9"/>
       <c r="AC65" s="9"/>
       <c r="AD65" s="9"/>
-    </row>
-    <row r="66" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE65" s="9"/>
+      <c r="AF65" s="9"/>
+    </row>
+    <row r="66" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -7345,8 +7567,10 @@
       <c r="AB66" s="9"/>
       <c r="AC66" s="9"/>
       <c r="AD66" s="9"/>
-    </row>
-    <row r="67" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE66" s="9"/>
+      <c r="AF66" s="9"/>
+    </row>
+    <row r="67" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -7375,8 +7599,10 @@
       <c r="AB67" s="9"/>
       <c r="AC67" s="9"/>
       <c r="AD67" s="9"/>
-    </row>
-    <row r="68" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE67" s="9"/>
+      <c r="AF67" s="9"/>
+    </row>
+    <row r="68" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -7405,8 +7631,10 @@
       <c r="AB68" s="9"/>
       <c r="AC68" s="9"/>
       <c r="AD68" s="9"/>
-    </row>
-    <row r="69" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE68" s="9"/>
+      <c r="AF68" s="9"/>
+    </row>
+    <row r="69" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -7435,8 +7663,10 @@
       <c r="AB69" s="9"/>
       <c r="AC69" s="9"/>
       <c r="AD69" s="9"/>
-    </row>
-    <row r="70" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE69" s="9"/>
+      <c r="AF69" s="9"/>
+    </row>
+    <row r="70" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
@@ -7465,8 +7695,10 @@
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
       <c r="AD70" s="9"/>
-    </row>
-    <row r="71" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE70" s="9"/>
+      <c r="AF70" s="9"/>
+    </row>
+    <row r="71" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
@@ -7495,8 +7727,10 @@
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
       <c r="AD71" s="9"/>
-    </row>
-    <row r="72" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE71" s="9"/>
+      <c r="AF71" s="9"/>
+    </row>
+    <row r="72" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
@@ -7525,8 +7759,10 @@
       <c r="AB72" s="9"/>
       <c r="AC72" s="9"/>
       <c r="AD72" s="9"/>
-    </row>
-    <row r="73" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE72" s="9"/>
+      <c r="AF72" s="9"/>
+    </row>
+    <row r="73" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -7555,8 +7791,10 @@
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
       <c r="AD73" s="9"/>
-    </row>
-    <row r="74" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE73" s="9"/>
+      <c r="AF73" s="9"/>
+    </row>
+    <row r="74" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -7585,8 +7823,10 @@
       <c r="AB74" s="9"/>
       <c r="AC74" s="9"/>
       <c r="AD74" s="9"/>
-    </row>
-    <row r="75" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE74" s="9"/>
+      <c r="AF74" s="9"/>
+    </row>
+    <row r="75" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -7615,8 +7855,10 @@
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
       <c r="AD75" s="9"/>
-    </row>
-    <row r="76" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE75" s="9"/>
+      <c r="AF75" s="9"/>
+    </row>
+    <row r="76" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -7645,8 +7887,10 @@
       <c r="AB76" s="9"/>
       <c r="AC76" s="9"/>
       <c r="AD76" s="9"/>
-    </row>
-    <row r="77" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE76" s="9"/>
+      <c r="AF76" s="9"/>
+    </row>
+    <row r="77" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -7675,8 +7919,10 @@
       <c r="AB77" s="9"/>
       <c r="AC77" s="9"/>
       <c r="AD77" s="9"/>
-    </row>
-    <row r="78" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE77" s="9"/>
+      <c r="AF77" s="9"/>
+    </row>
+    <row r="78" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
@@ -7705,8 +7951,10 @@
       <c r="AB78" s="9"/>
       <c r="AC78" s="9"/>
       <c r="AD78" s="9"/>
-    </row>
-    <row r="79" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE78" s="9"/>
+      <c r="AF78" s="9"/>
+    </row>
+    <row r="79" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
@@ -7735,8 +7983,10 @@
       <c r="AB79" s="9"/>
       <c r="AC79" s="9"/>
       <c r="AD79" s="9"/>
-    </row>
-    <row r="80" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE79" s="9"/>
+      <c r="AF79" s="9"/>
+    </row>
+    <row r="80" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -7765,8 +8015,10 @@
       <c r="AB80" s="9"/>
       <c r="AC80" s="9"/>
       <c r="AD80" s="9"/>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE80" s="9"/>
+      <c r="AF80" s="9"/>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -7795,8 +8047,10 @@
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
       <c r="AD81" s="9"/>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE81" s="9"/>
+      <c r="AF81" s="9"/>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -7825,8 +8079,10 @@
       <c r="AB82" s="9"/>
       <c r="AC82" s="9"/>
       <c r="AD82" s="9"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE82" s="9"/>
+      <c r="AF82" s="9"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
@@ -7855,8 +8111,10 @@
       <c r="AB83" s="9"/>
       <c r="AC83" s="9"/>
       <c r="AD83" s="9"/>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE83" s="9"/>
+      <c r="AF83" s="9"/>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
@@ -7885,8 +8143,10 @@
       <c r="AB84" s="9"/>
       <c r="AC84" s="9"/>
       <c r="AD84" s="9"/>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE84" s="9"/>
+      <c r="AF84" s="9"/>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
@@ -7915,8 +8175,10 @@
       <c r="AB85" s="9"/>
       <c r="AC85" s="9"/>
       <c r="AD85" s="9"/>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE85" s="9"/>
+      <c r="AF85" s="9"/>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
@@ -7945,8 +8207,10 @@
       <c r="AB86" s="9"/>
       <c r="AC86" s="9"/>
       <c r="AD86" s="9"/>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE86" s="9"/>
+      <c r="AF86" s="9"/>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
@@ -7975,8 +8239,10 @@
       <c r="AB87" s="9"/>
       <c r="AC87" s="9"/>
       <c r="AD87" s="9"/>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE87" s="9"/>
+      <c r="AF87" s="9"/>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
@@ -8005,8 +8271,10 @@
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
       <c r="AD88" s="9"/>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE88" s="9"/>
+      <c r="AF88" s="9"/>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
@@ -8035,8 +8303,10 @@
       <c r="AB89" s="9"/>
       <c r="AC89" s="9"/>
       <c r="AD89" s="9"/>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE89" s="9"/>
+      <c r="AF89" s="9"/>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
@@ -8065,8 +8335,10 @@
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
       <c r="AD90" s="9"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE90" s="9"/>
+      <c r="AF90" s="9"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -8095,8 +8367,10 @@
       <c r="AB91" s="9"/>
       <c r="AC91" s="9"/>
       <c r="AD91" s="9"/>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE91" s="9"/>
+      <c r="AF91" s="9"/>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -8125,8 +8399,10 @@
       <c r="AB92" s="9"/>
       <c r="AC92" s="9"/>
       <c r="AD92" s="9"/>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE92" s="9"/>
+      <c r="AF92" s="9"/>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -8155,8 +8431,10 @@
       <c r="AB93" s="9"/>
       <c r="AC93" s="9"/>
       <c r="AD93" s="9"/>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE93" s="9"/>
+      <c r="AF93" s="9"/>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -8185,8 +8463,10 @@
       <c r="AB94" s="9"/>
       <c r="AC94" s="9"/>
       <c r="AD94" s="9"/>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE94" s="9"/>
+      <c r="AF94" s="9"/>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -8215,8 +8495,10 @@
       <c r="AB95" s="9"/>
       <c r="AC95" s="9"/>
       <c r="AD95" s="9"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE95" s="9"/>
+      <c r="AF95" s="9"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -8245,8 +8527,10 @@
       <c r="AB96" s="9"/>
       <c r="AC96" s="9"/>
       <c r="AD96" s="9"/>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE96" s="9"/>
+      <c r="AF96" s="9"/>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -8275,8 +8559,10 @@
       <c r="AB97" s="9"/>
       <c r="AC97" s="9"/>
       <c r="AD97" s="9"/>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE97" s="9"/>
+      <c r="AF97" s="9"/>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -8305,8 +8591,10 @@
       <c r="AB98" s="9"/>
       <c r="AC98" s="9"/>
       <c r="AD98" s="9"/>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE98" s="9"/>
+      <c r="AF98" s="9"/>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -8335,8 +8623,10 @@
       <c r="AB99" s="9"/>
       <c r="AC99" s="9"/>
       <c r="AD99" s="9"/>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE99" s="9"/>
+      <c r="AF99" s="9"/>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -8365,8 +8655,10 @@
       <c r="AB100" s="9"/>
       <c r="AC100" s="9"/>
       <c r="AD100" s="9"/>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE100" s="9"/>
+      <c r="AF100" s="9"/>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -8395,8 +8687,10 @@
       <c r="AB101" s="9"/>
       <c r="AC101" s="9"/>
       <c r="AD101" s="9"/>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE101" s="9"/>
+      <c r="AF101" s="9"/>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -8425,8 +8719,10 @@
       <c r="AB102" s="9"/>
       <c r="AC102" s="9"/>
       <c r="AD102" s="9"/>
-    </row>
-    <row r="103" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE102" s="9"/>
+      <c r="AF102" s="9"/>
+    </row>
+    <row r="103" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -8455,8 +8751,10 @@
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
       <c r="AD103" s="9"/>
-    </row>
-    <row r="104" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE103" s="9"/>
+      <c r="AF103" s="9"/>
+    </row>
+    <row r="104" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -8485,8 +8783,10 @@
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
       <c r="AD104" s="9"/>
-    </row>
-    <row r="105" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE104" s="9"/>
+      <c r="AF104" s="9"/>
+    </row>
+    <row r="105" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
@@ -8515,8 +8815,10 @@
       <c r="AB105" s="9"/>
       <c r="AC105" s="9"/>
       <c r="AD105" s="9"/>
-    </row>
-    <row r="106" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE105" s="9"/>
+      <c r="AF105" s="9"/>
+    </row>
+    <row r="106" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
@@ -8545,8 +8847,10 @@
       <c r="AB106" s="9"/>
       <c r="AC106" s="9"/>
       <c r="AD106" s="9"/>
-    </row>
-    <row r="107" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE106" s="9"/>
+      <c r="AF106" s="9"/>
+    </row>
+    <row r="107" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
@@ -8575,8 +8879,10 @@
       <c r="AB107" s="9"/>
       <c r="AC107" s="9"/>
       <c r="AD107" s="9"/>
-    </row>
-    <row r="108" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE107" s="9"/>
+      <c r="AF107" s="9"/>
+    </row>
+    <row r="108" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
@@ -8605,8 +8911,10 @@
       <c r="AB108" s="9"/>
       <c r="AC108" s="9"/>
       <c r="AD108" s="9"/>
-    </row>
-    <row r="109" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE108" s="9"/>
+      <c r="AF108" s="9"/>
+    </row>
+    <row r="109" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
@@ -8635,8 +8943,10 @@
       <c r="AB109" s="9"/>
       <c r="AC109" s="9"/>
       <c r="AD109" s="9"/>
-    </row>
-    <row r="110" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE109" s="9"/>
+      <c r="AF109" s="9"/>
+    </row>
+    <row r="110" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
@@ -8665,8 +8975,10 @@
       <c r="AB110" s="9"/>
       <c r="AC110" s="9"/>
       <c r="AD110" s="9"/>
-    </row>
-    <row r="111" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE110" s="9"/>
+      <c r="AF110" s="9"/>
+    </row>
+    <row r="111" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -8695,8 +9007,10 @@
       <c r="AB111" s="9"/>
       <c r="AC111" s="9"/>
       <c r="AD111" s="9"/>
-    </row>
-    <row r="112" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE111" s="9"/>
+      <c r="AF111" s="9"/>
+    </row>
+    <row r="112" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -8725,8 +9039,10 @@
       <c r="AB112" s="9"/>
       <c r="AC112" s="9"/>
       <c r="AD112" s="9"/>
-    </row>
-    <row r="113" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE112" s="9"/>
+      <c r="AF112" s="9"/>
+    </row>
+    <row r="113" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -8755,8 +9071,10 @@
       <c r="AB113" s="9"/>
       <c r="AC113" s="9"/>
       <c r="AD113" s="9"/>
-    </row>
-    <row r="114" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE113" s="9"/>
+      <c r="AF113" s="9"/>
+    </row>
+    <row r="114" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -8785,8 +9103,10 @@
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
       <c r="AD114" s="9"/>
-    </row>
-    <row r="115" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE114" s="9"/>
+      <c r="AF114" s="9"/>
+    </row>
+    <row r="115" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -8815,8 +9135,10 @@
       <c r="AB115" s="9"/>
       <c r="AC115" s="9"/>
       <c r="AD115" s="9"/>
-    </row>
-    <row r="116" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE115" s="9"/>
+      <c r="AF115" s="9"/>
+    </row>
+    <row r="116" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -8845,8 +9167,10 @@
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
       <c r="AD116" s="9"/>
-    </row>
-    <row r="117" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE116" s="9"/>
+      <c r="AF116" s="9"/>
+    </row>
+    <row r="117" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -8875,8 +9199,10 @@
       <c r="AB117" s="9"/>
       <c r="AC117" s="9"/>
       <c r="AD117" s="9"/>
-    </row>
-    <row r="118" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE117" s="9"/>
+      <c r="AF117" s="9"/>
+    </row>
+    <row r="118" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -8905,8 +9231,10 @@
       <c r="AB118" s="9"/>
       <c r="AC118" s="9"/>
       <c r="AD118" s="9"/>
-    </row>
-    <row r="119" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE118" s="9"/>
+      <c r="AF118" s="9"/>
+    </row>
+    <row r="119" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -8935,8 +9263,10 @@
       <c r="AB119" s="9"/>
       <c r="AC119" s="9"/>
       <c r="AD119" s="9"/>
-    </row>
-    <row r="120" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE119" s="9"/>
+      <c r="AF119" s="9"/>
+    </row>
+    <row r="120" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -8965,8 +9295,10 @@
       <c r="AB120" s="9"/>
       <c r="AC120" s="9"/>
       <c r="AD120" s="9"/>
-    </row>
-    <row r="121" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE120" s="9"/>
+      <c r="AF120" s="9"/>
+    </row>
+    <row r="121" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -8995,8 +9327,10 @@
       <c r="AB121" s="9"/>
       <c r="AC121" s="9"/>
       <c r="AD121" s="9"/>
-    </row>
-    <row r="122" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE121" s="9"/>
+      <c r="AF121" s="9"/>
+    </row>
+    <row r="122" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -9025,8 +9359,10 @@
       <c r="AB122" s="9"/>
       <c r="AC122" s="9"/>
       <c r="AD122" s="9"/>
-    </row>
-    <row r="123" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE122" s="9"/>
+      <c r="AF122" s="9"/>
+    </row>
+    <row r="123" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -9055,8 +9391,10 @@
       <c r="AB123" s="9"/>
       <c r="AC123" s="9"/>
       <c r="AD123" s="9"/>
-    </row>
-    <row r="124" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE123" s="9"/>
+      <c r="AF123" s="9"/>
+    </row>
+    <row r="124" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -9085,8 +9423,10 @@
       <c r="AB124" s="9"/>
       <c r="AC124" s="9"/>
       <c r="AD124" s="9"/>
-    </row>
-    <row r="125" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE124" s="9"/>
+      <c r="AF124" s="9"/>
+    </row>
+    <row r="125" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -9115,8 +9455,10 @@
       <c r="AB125" s="9"/>
       <c r="AC125" s="9"/>
       <c r="AD125" s="9"/>
-    </row>
-    <row r="126" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE125" s="9"/>
+      <c r="AF125" s="9"/>
+    </row>
+    <row r="126" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -9145,8 +9487,10 @@
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
       <c r="AD126" s="9"/>
-    </row>
-    <row r="127" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE126" s="9"/>
+      <c r="AF126" s="9"/>
+    </row>
+    <row r="127" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -9175,8 +9519,10 @@
       <c r="AB127" s="9"/>
       <c r="AC127" s="9"/>
       <c r="AD127" s="9"/>
-    </row>
-    <row r="128" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE127" s="9"/>
+      <c r="AF127" s="9"/>
+    </row>
+    <row r="128" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -9205,8 +9551,10 @@
       <c r="AB128" s="9"/>
       <c r="AC128" s="9"/>
       <c r="AD128" s="9"/>
-    </row>
-    <row r="129" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE128" s="9"/>
+      <c r="AF128" s="9"/>
+    </row>
+    <row r="129" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -9235,8 +9583,10 @@
       <c r="AB129" s="9"/>
       <c r="AC129" s="9"/>
       <c r="AD129" s="9"/>
-    </row>
-    <row r="130" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE129" s="9"/>
+      <c r="AF129" s="9"/>
+    </row>
+    <row r="130" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -9265,8 +9615,10 @@
       <c r="AB130" s="9"/>
       <c r="AC130" s="9"/>
       <c r="AD130" s="9"/>
-    </row>
-    <row r="131" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE130" s="9"/>
+      <c r="AF130" s="9"/>
+    </row>
+    <row r="131" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -9295,8 +9647,10 @@
       <c r="AB131" s="9"/>
       <c r="AC131" s="9"/>
       <c r="AD131" s="9"/>
-    </row>
-    <row r="132" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE131" s="9"/>
+      <c r="AF131" s="9"/>
+    </row>
+    <row r="132" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -9325,8 +9679,10 @@
       <c r="AB132" s="9"/>
       <c r="AC132" s="9"/>
       <c r="AD132" s="9"/>
-    </row>
-    <row r="133" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE132" s="9"/>
+      <c r="AF132" s="9"/>
+    </row>
+    <row r="133" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -9355,8 +9711,10 @@
       <c r="AB133" s="9"/>
       <c r="AC133" s="9"/>
       <c r="AD133" s="9"/>
-    </row>
-    <row r="134" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE133" s="9"/>
+      <c r="AF133" s="9"/>
+    </row>
+    <row r="134" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -9385,8 +9743,10 @@
       <c r="AB134" s="9"/>
       <c r="AC134" s="9"/>
       <c r="AD134" s="9"/>
-    </row>
-    <row r="135" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE134" s="9"/>
+      <c r="AF134" s="9"/>
+    </row>
+    <row r="135" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -9415,8 +9775,10 @@
       <c r="AB135" s="9"/>
       <c r="AC135" s="9"/>
       <c r="AD135" s="9"/>
-    </row>
-    <row r="136" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE135" s="9"/>
+      <c r="AF135" s="9"/>
+    </row>
+    <row r="136" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -9445,8 +9807,10 @@
       <c r="AB136" s="9"/>
       <c r="AC136" s="9"/>
       <c r="AD136" s="9"/>
-    </row>
-    <row r="137" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE136" s="9"/>
+      <c r="AF136" s="9"/>
+    </row>
+    <row r="137" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -9475,8 +9839,10 @@
       <c r="AB137" s="9"/>
       <c r="AC137" s="9"/>
       <c r="AD137" s="9"/>
-    </row>
-    <row r="138" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE137" s="9"/>
+      <c r="AF137" s="9"/>
+    </row>
+    <row r="138" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -9505,8 +9871,10 @@
       <c r="AB138" s="9"/>
       <c r="AC138" s="9"/>
       <c r="AD138" s="9"/>
-    </row>
-    <row r="139" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE138" s="9"/>
+      <c r="AF138" s="9"/>
+    </row>
+    <row r="139" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -9535,8 +9903,10 @@
       <c r="AB139" s="9"/>
       <c r="AC139" s="9"/>
       <c r="AD139" s="9"/>
-    </row>
-    <row r="140" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE139" s="9"/>
+      <c r="AF139" s="9"/>
+    </row>
+    <row r="140" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -9565,8 +9935,10 @@
       <c r="AB140" s="9"/>
       <c r="AC140" s="9"/>
       <c r="AD140" s="9"/>
-    </row>
-    <row r="141" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE140" s="9"/>
+      <c r="AF140" s="9"/>
+    </row>
+    <row r="141" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -9595,8 +9967,10 @@
       <c r="AB141" s="9"/>
       <c r="AC141" s="9"/>
       <c r="AD141" s="9"/>
-    </row>
-    <row r="142" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE141" s="9"/>
+      <c r="AF141" s="9"/>
+    </row>
+    <row r="142" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -9625,8 +9999,10 @@
       <c r="AB142" s="9"/>
       <c r="AC142" s="9"/>
       <c r="AD142" s="9"/>
-    </row>
-    <row r="143" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE142" s="9"/>
+      <c r="AF142" s="9"/>
+    </row>
+    <row r="143" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -9655,8 +10031,10 @@
       <c r="AB143" s="9"/>
       <c r="AC143" s="9"/>
       <c r="AD143" s="9"/>
-    </row>
-    <row r="144" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE143" s="9"/>
+      <c r="AF143" s="9"/>
+    </row>
+    <row r="144" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -9685,8 +10063,10 @@
       <c r="AB144" s="9"/>
       <c r="AC144" s="9"/>
       <c r="AD144" s="9"/>
-    </row>
-    <row r="145" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE144" s="9"/>
+      <c r="AF144" s="9"/>
+    </row>
+    <row r="145" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -9715,8 +10095,10 @@
       <c r="AB145" s="9"/>
       <c r="AC145" s="9"/>
       <c r="AD145" s="9"/>
-    </row>
-    <row r="146" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE145" s="9"/>
+      <c r="AF145" s="9"/>
+    </row>
+    <row r="146" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -9745,8 +10127,10 @@
       <c r="AB146" s="9"/>
       <c r="AC146" s="9"/>
       <c r="AD146" s="9"/>
-    </row>
-    <row r="147" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE146" s="9"/>
+      <c r="AF146" s="9"/>
+    </row>
+    <row r="147" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -9775,8 +10159,10 @@
       <c r="AB147" s="9"/>
       <c r="AC147" s="9"/>
       <c r="AD147" s="9"/>
-    </row>
-    <row r="148" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE147" s="9"/>
+      <c r="AF147" s="9"/>
+    </row>
+    <row r="148" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -9805,8 +10191,10 @@
       <c r="AB148" s="9"/>
       <c r="AC148" s="9"/>
       <c r="AD148" s="9"/>
-    </row>
-    <row r="149" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE148" s="9"/>
+      <c r="AF148" s="9"/>
+    </row>
+    <row r="149" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -9835,8 +10223,10 @@
       <c r="AB149" s="9"/>
       <c r="AC149" s="9"/>
       <c r="AD149" s="9"/>
-    </row>
-    <row r="150" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE149" s="9"/>
+      <c r="AF149" s="9"/>
+    </row>
+    <row r="150" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -9865,8 +10255,10 @@
       <c r="AB150" s="9"/>
       <c r="AC150" s="9"/>
       <c r="AD150" s="9"/>
-    </row>
-    <row r="151" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE150" s="9"/>
+      <c r="AF150" s="9"/>
+    </row>
+    <row r="151" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -9895,8 +10287,10 @@
       <c r="AB151" s="9"/>
       <c r="AC151" s="9"/>
       <c r="AD151" s="9"/>
-    </row>
-    <row r="152" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE151" s="9"/>
+      <c r="AF151" s="9"/>
+    </row>
+    <row r="152" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -9925,8 +10319,10 @@
       <c r="AB152" s="9"/>
       <c r="AC152" s="9"/>
       <c r="AD152" s="9"/>
-    </row>
-    <row r="153" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE152" s="9"/>
+      <c r="AF152" s="9"/>
+    </row>
+    <row r="153" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -9955,8 +10351,10 @@
       <c r="AB153" s="9"/>
       <c r="AC153" s="9"/>
       <c r="AD153" s="9"/>
-    </row>
-    <row r="154" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE153" s="9"/>
+      <c r="AF153" s="9"/>
+    </row>
+    <row r="154" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -9985,8 +10383,10 @@
       <c r="AB154" s="9"/>
       <c r="AC154" s="9"/>
       <c r="AD154" s="9"/>
-    </row>
-    <row r="155" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE154" s="9"/>
+      <c r="AF154" s="9"/>
+    </row>
+    <row r="155" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -10015,8 +10415,10 @@
       <c r="AB155" s="9"/>
       <c r="AC155" s="9"/>
       <c r="AD155" s="9"/>
-    </row>
-    <row r="156" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE155" s="9"/>
+      <c r="AF155" s="9"/>
+    </row>
+    <row r="156" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -10045,8 +10447,10 @@
       <c r="AB156" s="9"/>
       <c r="AC156" s="9"/>
       <c r="AD156" s="9"/>
-    </row>
-    <row r="157" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE156" s="9"/>
+      <c r="AF156" s="9"/>
+    </row>
+    <row r="157" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -10075,8 +10479,10 @@
       <c r="AB157" s="9"/>
       <c r="AC157" s="9"/>
       <c r="AD157" s="9"/>
-    </row>
-    <row r="158" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE157" s="9"/>
+      <c r="AF157" s="9"/>
+    </row>
+    <row r="158" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -10105,8 +10511,10 @@
       <c r="AB158" s="9"/>
       <c r="AC158" s="9"/>
       <c r="AD158" s="9"/>
-    </row>
-    <row r="159" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE158" s="9"/>
+      <c r="AF158" s="9"/>
+    </row>
+    <row r="159" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -10135,8 +10543,10 @@
       <c r="AB159" s="9"/>
       <c r="AC159" s="9"/>
       <c r="AD159" s="9"/>
-    </row>
-    <row r="160" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE159" s="9"/>
+      <c r="AF159" s="9"/>
+    </row>
+    <row r="160" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -10165,8 +10575,10 @@
       <c r="AB160" s="9"/>
       <c r="AC160" s="9"/>
       <c r="AD160" s="9"/>
-    </row>
-    <row r="161" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE160" s="9"/>
+      <c r="AF160" s="9"/>
+    </row>
+    <row r="161" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -10195,8 +10607,10 @@
       <c r="AB161" s="9"/>
       <c r="AC161" s="9"/>
       <c r="AD161" s="9"/>
-    </row>
-    <row r="162" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE161" s="9"/>
+      <c r="AF161" s="9"/>
+    </row>
+    <row r="162" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -10225,8 +10639,10 @@
       <c r="AB162" s="9"/>
       <c r="AC162" s="9"/>
       <c r="AD162" s="9"/>
-    </row>
-    <row r="163" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE162" s="9"/>
+      <c r="AF162" s="9"/>
+    </row>
+    <row r="163" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -10255,8 +10671,10 @@
       <c r="AB163" s="9"/>
       <c r="AC163" s="9"/>
       <c r="AD163" s="9"/>
-    </row>
-    <row r="164" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE163" s="9"/>
+      <c r="AF163" s="9"/>
+    </row>
+    <row r="164" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
@@ -10285,8 +10703,10 @@
       <c r="AB164" s="9"/>
       <c r="AC164" s="9"/>
       <c r="AD164" s="9"/>
-    </row>
-    <row r="165" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE164" s="9"/>
+      <c r="AF164" s="9"/>
+    </row>
+    <row r="165" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
@@ -10315,8 +10735,10 @@
       <c r="AB165" s="9"/>
       <c r="AC165" s="9"/>
       <c r="AD165" s="9"/>
-    </row>
-    <row r="166" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE165" s="9"/>
+      <c r="AF165" s="9"/>
+    </row>
+    <row r="166" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
@@ -10345,8 +10767,10 @@
       <c r="AB166" s="9"/>
       <c r="AC166" s="9"/>
       <c r="AD166" s="9"/>
-    </row>
-    <row r="167" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE166" s="9"/>
+      <c r="AF166" s="9"/>
+    </row>
+    <row r="167" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
@@ -10375,8 +10799,10 @@
       <c r="AB167" s="9"/>
       <c r="AC167" s="9"/>
       <c r="AD167" s="9"/>
-    </row>
-    <row r="168" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE167" s="9"/>
+      <c r="AF167" s="9"/>
+    </row>
+    <row r="168" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
@@ -10405,8 +10831,10 @@
       <c r="AB168" s="9"/>
       <c r="AC168" s="9"/>
       <c r="AD168" s="9"/>
-    </row>
-    <row r="169" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE168" s="9"/>
+      <c r="AF168" s="9"/>
+    </row>
+    <row r="169" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
@@ -10435,8 +10863,10 @@
       <c r="AB169" s="9"/>
       <c r="AC169" s="9"/>
       <c r="AD169" s="9"/>
-    </row>
-    <row r="170" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE169" s="9"/>
+      <c r="AF169" s="9"/>
+    </row>
+    <row r="170" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -10465,8 +10895,10 @@
       <c r="AB170" s="9"/>
       <c r="AC170" s="9"/>
       <c r="AD170" s="9"/>
-    </row>
-    <row r="171" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE170" s="9"/>
+      <c r="AF170" s="9"/>
+    </row>
+    <row r="171" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
@@ -10495,8 +10927,10 @@
       <c r="AB171" s="9"/>
       <c r="AC171" s="9"/>
       <c r="AD171" s="9"/>
-    </row>
-    <row r="172" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE171" s="9"/>
+      <c r="AF171" s="9"/>
+    </row>
+    <row r="172" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
@@ -10525,8 +10959,10 @@
       <c r="AB172" s="9"/>
       <c r="AC172" s="9"/>
       <c r="AD172" s="9"/>
-    </row>
-    <row r="173" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE172" s="9"/>
+      <c r="AF172" s="9"/>
+    </row>
+    <row r="173" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
@@ -10555,8 +10991,10 @@
       <c r="AB173" s="9"/>
       <c r="AC173" s="9"/>
       <c r="AD173" s="9"/>
-    </row>
-    <row r="174" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE173" s="9"/>
+      <c r="AF173" s="9"/>
+    </row>
+    <row r="174" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
@@ -10585,8 +11023,10 @@
       <c r="AB174" s="9"/>
       <c r="AC174" s="9"/>
       <c r="AD174" s="9"/>
-    </row>
-    <row r="175" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE174" s="9"/>
+      <c r="AF174" s="9"/>
+    </row>
+    <row r="175" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
@@ -10615,8 +11055,10 @@
       <c r="AB175" s="9"/>
       <c r="AC175" s="9"/>
       <c r="AD175" s="9"/>
-    </row>
-    <row r="176" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE175" s="9"/>
+      <c r="AF175" s="9"/>
+    </row>
+    <row r="176" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -10645,8 +11087,10 @@
       <c r="AB176" s="9"/>
       <c r="AC176" s="9"/>
       <c r="AD176" s="9"/>
-    </row>
-    <row r="177" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE176" s="9"/>
+      <c r="AF176" s="9"/>
+    </row>
+    <row r="177" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -10675,8 +11119,10 @@
       <c r="AB177" s="9"/>
       <c r="AC177" s="9"/>
       <c r="AD177" s="9"/>
-    </row>
-    <row r="178" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE177" s="9"/>
+      <c r="AF177" s="9"/>
+    </row>
+    <row r="178" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
@@ -10705,8 +11151,10 @@
       <c r="AB178" s="9"/>
       <c r="AC178" s="9"/>
       <c r="AD178" s="9"/>
-    </row>
-    <row r="179" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE178" s="9"/>
+      <c r="AF178" s="9"/>
+    </row>
+    <row r="179" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
@@ -10735,8 +11183,10 @@
       <c r="AB179" s="9"/>
       <c r="AC179" s="9"/>
       <c r="AD179" s="9"/>
-    </row>
-    <row r="180" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE179" s="9"/>
+      <c r="AF179" s="9"/>
+    </row>
+    <row r="180" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
@@ -10765,8 +11215,10 @@
       <c r="AB180" s="9"/>
       <c r="AC180" s="9"/>
       <c r="AD180" s="9"/>
-    </row>
-    <row r="181" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE180" s="9"/>
+      <c r="AF180" s="9"/>
+    </row>
+    <row r="181" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
@@ -10795,8 +11247,10 @@
       <c r="AB181" s="9"/>
       <c r="AC181" s="9"/>
       <c r="AD181" s="9"/>
-    </row>
-    <row r="182" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE181" s="9"/>
+      <c r="AF181" s="9"/>
+    </row>
+    <row r="182" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
@@ -10825,8 +11279,10 @@
       <c r="AB182" s="9"/>
       <c r="AC182" s="9"/>
       <c r="AD182" s="9"/>
-    </row>
-    <row r="183" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE182" s="9"/>
+      <c r="AF182" s="9"/>
+    </row>
+    <row r="183" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
@@ -10855,8 +11311,10 @@
       <c r="AB183" s="9"/>
       <c r="AC183" s="9"/>
       <c r="AD183" s="9"/>
-    </row>
-    <row r="184" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE183" s="9"/>
+      <c r="AF183" s="9"/>
+    </row>
+    <row r="184" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
@@ -10885,8 +11343,10 @@
       <c r="AB184" s="9"/>
       <c r="AC184" s="9"/>
       <c r="AD184" s="9"/>
-    </row>
-    <row r="185" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE184" s="9"/>
+      <c r="AF184" s="9"/>
+    </row>
+    <row r="185" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
@@ -10915,8 +11375,10 @@
       <c r="AB185" s="9"/>
       <c r="AC185" s="9"/>
       <c r="AD185" s="9"/>
-    </row>
-    <row r="186" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE185" s="9"/>
+      <c r="AF185" s="9"/>
+    </row>
+    <row r="186" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
@@ -10945,8 +11407,10 @@
       <c r="AB186" s="9"/>
       <c r="AC186" s="9"/>
       <c r="AD186" s="9"/>
-    </row>
-    <row r="187" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE186" s="9"/>
+      <c r="AF186" s="9"/>
+    </row>
+    <row r="187" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
@@ -10975,8 +11439,10 @@
       <c r="AB187" s="9"/>
       <c r="AC187" s="9"/>
       <c r="AD187" s="9"/>
-    </row>
-    <row r="188" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE187" s="9"/>
+      <c r="AF187" s="9"/>
+    </row>
+    <row r="188" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -11005,8 +11471,10 @@
       <c r="AB188" s="9"/>
       <c r="AC188" s="9"/>
       <c r="AD188" s="9"/>
-    </row>
-    <row r="189" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE188" s="9"/>
+      <c r="AF188" s="9"/>
+    </row>
+    <row r="189" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -11035,8 +11503,10 @@
       <c r="AB189" s="9"/>
       <c r="AC189" s="9"/>
       <c r="AD189" s="9"/>
-    </row>
-    <row r="190" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE189" s="9"/>
+      <c r="AF189" s="9"/>
+    </row>
+    <row r="190" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -11065,8 +11535,10 @@
       <c r="AB190" s="9"/>
       <c r="AC190" s="9"/>
       <c r="AD190" s="9"/>
-    </row>
-    <row r="191" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE190" s="9"/>
+      <c r="AF190" s="9"/>
+    </row>
+    <row r="191" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
@@ -11095,8 +11567,10 @@
       <c r="AB191" s="9"/>
       <c r="AC191" s="9"/>
       <c r="AD191" s="9"/>
-    </row>
-    <row r="192" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE191" s="9"/>
+      <c r="AF191" s="9"/>
+    </row>
+    <row r="192" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
@@ -11125,8 +11599,10 @@
       <c r="AB192" s="9"/>
       <c r="AC192" s="9"/>
       <c r="AD192" s="9"/>
-    </row>
-    <row r="193" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE192" s="9"/>
+      <c r="AF192" s="9"/>
+    </row>
+    <row r="193" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
@@ -11155,8 +11631,10 @@
       <c r="AB193" s="9"/>
       <c r="AC193" s="9"/>
       <c r="AD193" s="9"/>
-    </row>
-    <row r="194" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE193" s="9"/>
+      <c r="AF193" s="9"/>
+    </row>
+    <row r="194" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
       <c r="E194" s="9"/>
@@ -11185,8 +11663,10 @@
       <c r="AB194" s="9"/>
       <c r="AC194" s="9"/>
       <c r="AD194" s="9"/>
-    </row>
-    <row r="195" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE194" s="9"/>
+      <c r="AF194" s="9"/>
+    </row>
+    <row r="195" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
@@ -11215,8 +11695,10 @@
       <c r="AB195" s="9"/>
       <c r="AC195" s="9"/>
       <c r="AD195" s="9"/>
-    </row>
-    <row r="196" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE195" s="9"/>
+      <c r="AF195" s="9"/>
+    </row>
+    <row r="196" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
       <c r="E196" s="9"/>
@@ -11245,8 +11727,10 @@
       <c r="AB196" s="9"/>
       <c r="AC196" s="9"/>
       <c r="AD196" s="9"/>
-    </row>
-    <row r="197" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE196" s="9"/>
+      <c r="AF196" s="9"/>
+    </row>
+    <row r="197" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
       <c r="E197" s="9"/>
@@ -11275,8 +11759,10 @@
       <c r="AB197" s="9"/>
       <c r="AC197" s="9"/>
       <c r="AD197" s="9"/>
-    </row>
-    <row r="198" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE197" s="9"/>
+      <c r="AF197" s="9"/>
+    </row>
+    <row r="198" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
@@ -11305,8 +11791,10 @@
       <c r="AB198" s="9"/>
       <c r="AC198" s="9"/>
       <c r="AD198" s="9"/>
-    </row>
-    <row r="199" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE198" s="9"/>
+      <c r="AF198" s="9"/>
+    </row>
+    <row r="199" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
@@ -11335,8 +11823,10 @@
       <c r="AB199" s="9"/>
       <c r="AC199" s="9"/>
       <c r="AD199" s="9"/>
-    </row>
-    <row r="200" spans="3:30" x14ac:dyDescent="0.25">
+      <c r="AE199" s="9"/>
+      <c r="AF199" s="9"/>
+    </row>
+    <row r="200" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -11365,24 +11855,27 @@
       <c r="AB200" s="9"/>
       <c r="AC200" s="9"/>
       <c r="AD200" s="9"/>
+      <c r="AE200" s="9"/>
+      <c r="AF200" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AD200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A2:AF200" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="P1:AC1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:AD200">
-    <cfRule type="expression" dxfId="2" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="C3:AF200">
+    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;30,(EDATE(C3,12)-TODAY())&lt;=60)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&gt;60)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/cert_tracker/Contractor Certifications Tracker Demo.xlsx
+++ b/cert_tracker/Contractor Certifications Tracker Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsant\jacobdashboard\cert_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17EC675-E6A9-4B28-872F-B7A97E4AB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14B57C8-BE27-4C4C-BBF0-FF6EF40E3CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="213">
   <si>
     <t>Certification</t>
   </si>
@@ -679,6 +679,9 @@
   </si>
   <si>
     <t>Jose Gonzalez</t>
+  </si>
+  <si>
+    <t>demo</t>
   </si>
 </sst>
 </file>
@@ -933,17 +936,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1347,7 +1350,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="28"/>
@@ -1476,7 +1479,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="28"/>
@@ -1486,40 +1489,40 @@
       <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="32" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="28"/>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D3" s="28"/>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="32" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="28"/>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="32" t="s">
         <v>55</v>
       </c>
       <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="29">
+      <c r="A4" s="31">
         <f>COUNTA(Contractors!A2:A50)</f>
         <v>11</v>
       </c>
       <c r="B4" s="28"/>
-      <c r="C4" s="29">
+      <c r="C4" s="31">
         <f>COUNTA(Workers!A2:A200)</f>
         <v>31</v>
       </c>
       <c r="D4" s="28"/>
-      <c r="E4" s="29">
+      <c r="E4" s="31">
         <f>COUNTIFS(Workers!A2:A200,"&lt;&gt;",Workers!D2:D200,"active")</f>
         <v>25</v>
       </c>
       <c r="F4" s="28"/>
-      <c r="G4" s="29" t="str">
+      <c r="G4" s="31" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
         <v>04/29/2026</v>
       </c>
@@ -1536,7 +1539,7 @@
       <c r="H5" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="30" t="s">
         <v>56</v>
       </c>
       <c r="B7" s="28"/>
@@ -2290,9 +2293,9 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="21">
+      <c r="A37" s="21" t="str">
         <f>Certifications!A30</f>
-        <v>0</v>
+        <v>demo</v>
       </c>
       <c r="B37" s="21">
         <f>Certifications!B30</f>
@@ -2300,15 +2303,15 @@
       </c>
       <c r="C37" s="21">
         <f>IFERROR(COUNTA(INDEX(Tracker!$C$3:$AZ$200,0,MATCH($A37,Tracker!$C$2:$AZ$2,0))),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="21">
         <f>COUNTA(Workers!A$2:A$200)-C37</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E37" s="22">
         <f t="shared" si="0"/>
-        <v>3.2258064516129031E-2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="23" t="e">
         <f t="shared" si="1"/>
@@ -2343,16 +2346,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="C4:D5"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="G4:H5"/>
     <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E26">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
@@ -2372,7 +2375,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2701,6 +2704,11 @@
       </c>
       <c r="C29">
         <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +4411,7 @@
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="27" t="s">
         <v>206</v>
       </c>
       <c r="D1" s="28"/>
@@ -4418,7 +4426,7 @@
       <c r="M1" s="28"/>
       <c r="N1" s="28"/>
       <c r="O1" s="28"/>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="27" t="s">
         <v>19</v>
       </c>
       <c r="Q1" s="28"/>
@@ -4557,7 +4565,10 @@
         <f>Certifications!A29</f>
         <v>Estamos mas que bien</v>
       </c>
-      <c r="AE2" s="1"/>
+      <c r="AE2" s="1" t="str">
+        <f>Certifications!A30</f>
+        <v>demo</v>
+      </c>
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -5166,7 +5177,6 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
       <c r="I12" s="9">
         <v>45797</v>
       </c>
@@ -11864,7 +11874,7 @@
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="P1:AC1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:AF200">
+  <conditionalFormatting sqref="C3:AF11 C12:G12 I12:AF12 C13:AF200">
     <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
       <formula>AND(C3&lt;&gt;"",ISNUMBER(C3),(EDATE(C3,12)-TODAY())&lt;=30)</formula>
     </cfRule>
